--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129716427</v>
+        <v>129727955</v>
       </c>
       <c r="B2" t="n">
-        <v>83036</v>
+        <v>91584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488400</v>
+        <v>489154</v>
       </c>
       <c r="R2" t="n">
-        <v>7144977</v>
+        <v>7144751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,51 +760,51 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727766</v>
+        <v>129727773</v>
       </c>
       <c r="B3" t="n">
-        <v>80209</v>
+        <v>91584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488676</v>
+        <v>488610</v>
       </c>
       <c r="R3" t="n">
-        <v>7144814</v>
+        <v>7144833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,22 +874,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727797</v>
+        <v>129716427</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>83037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488482</v>
+        <v>488400</v>
       </c>
       <c r="R4" t="n">
-        <v>7144891</v>
+        <v>7144977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,11 +980,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -997,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727955</v>
+        <v>129727797</v>
       </c>
       <c r="B5" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489154</v>
+        <v>488482</v>
       </c>
       <c r="R5" t="n">
-        <v>7144751</v>
+        <v>7144891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,6 +1077,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1094,22 +1094,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129727773</v>
+        <v>129726770</v>
       </c>
       <c r="B6" t="n">
-        <v>91583</v>
+        <v>80182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,41 +1117,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488610</v>
+        <v>489064</v>
       </c>
       <c r="R6" t="n">
-        <v>7144833</v>
+        <v>7144843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,14 +1174,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,54 +1195,43 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726770</v>
+        <v>129726758</v>
       </c>
       <c r="B7" t="n">
-        <v>80181</v>
+        <v>82911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489064</v>
+        <v>488417</v>
       </c>
       <c r="R7" t="n">
-        <v>7144843</v>
+        <v>7145102</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,21 +1319,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1363,45 +1335,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726758</v>
+        <v>129727766</v>
       </c>
       <c r="B8" t="n">
-        <v>82910</v>
+        <v>80210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488417</v>
+        <v>488676</v>
       </c>
       <c r="R8" t="n">
-        <v>7145102</v>
+        <v>7144814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,19 +1410,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,18 +1426,44 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>129727952</v>
       </c>
       <c r="B9" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>129716439</v>
       </c>
       <c r="B10" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727776</v>
+        <v>129727782</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488425</v>
+        <v>488694</v>
       </c>
       <c r="R11" t="n">
-        <v>7145015</v>
+        <v>7144925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,52 +1766,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727765</v>
+        <v>129727796</v>
       </c>
       <c r="B12" t="n">
-        <v>80209</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488701</v>
+        <v>488507</v>
       </c>
       <c r="R12" t="n">
-        <v>7144801</v>
+        <v>7144870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1841,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,34 +1850,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1901,45 +1868,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726761</v>
+        <v>129727765</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>80210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488516</v>
+        <v>488701</v>
       </c>
       <c r="R13" t="n">
-        <v>7145014</v>
+        <v>7144801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,19 +1943,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,28 +1959,54 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727801</v>
+        <v>129726781</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>78089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,34 +2014,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488339</v>
+        <v>488365</v>
       </c>
       <c r="R14" t="n">
-        <v>7144937</v>
+        <v>7144983</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,14 +2071,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,22 +2098,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727782</v>
+        <v>129727776</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488694</v>
+        <v>488425</v>
       </c>
       <c r="R15" t="n">
-        <v>7144925</v>
+        <v>7145015</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727796</v>
+        <v>129726761</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,14 +2243,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488507</v>
+        <v>488516</v>
       </c>
       <c r="R16" t="n">
-        <v>7144870</v>
+        <v>7145014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,14 +2280,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,22 +2307,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726781</v>
+        <v>129727801</v>
       </c>
       <c r="B17" t="n">
-        <v>78088</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,34 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488365</v>
+        <v>488339</v>
       </c>
       <c r="R17" t="n">
-        <v>7144983</v>
+        <v>7144937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,19 +2387,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,12 +2409,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         <v>129726774</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129727947</v>
       </c>
       <c r="B19" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129716443</v>
       </c>
       <c r="B20" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>129727768</v>
       </c>
       <c r="B21" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726772</v>
+        <v>129726757</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>83037</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489044</v>
+        <v>488392</v>
       </c>
       <c r="R22" t="n">
-        <v>7144859</v>
+        <v>7145120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726757</v>
+        <v>129726772</v>
       </c>
       <c r="B23" t="n">
-        <v>83036</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488392</v>
+        <v>489044</v>
       </c>
       <c r="R23" t="n">
-        <v>7145120</v>
+        <v>7144859</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,7 +3078,7 @@
         <v>129726762</v>
       </c>
       <c r="B24" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129727950</v>
+        <v>129727946</v>
       </c>
       <c r="B25" t="n">
-        <v>80181</v>
+        <v>91588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,21 +3193,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488374</v>
+        <v>489112</v>
       </c>
       <c r="R25" t="n">
-        <v>7144953</v>
+        <v>7144780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129727946</v>
+        <v>129727950</v>
       </c>
       <c r="B26" t="n">
-        <v>91587</v>
+        <v>80182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,21 +3290,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489112</v>
+        <v>488374</v>
       </c>
       <c r="R26" t="n">
-        <v>7144780</v>
+        <v>7144953</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727786</v>
+        <v>129727772</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>80182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,34 +3387,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489035</v>
+        <v>488470</v>
       </c>
       <c r="R27" t="n">
-        <v>7144832</v>
+        <v>7144960</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,7 +3458,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,8 +3467,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3478,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B28" t="n">
-        <v>80181</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,41 +3522,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R28" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3558,65 +3589,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B29" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,39 +3624,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R29" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,6 +3686,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3703,22 +3703,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726763</v>
+        <v>129727945</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,34 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488626</v>
+        <v>489010</v>
       </c>
       <c r="R30" t="n">
-        <v>7145010</v>
+        <v>7144808</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,49 +3786,40 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129716436</v>
+        <v>129726760</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>88987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,34 +3827,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489031</v>
+        <v>488426</v>
       </c>
       <c r="R31" t="n">
-        <v>7144903</v>
+        <v>7145052</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,9 +3884,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3907,22 +3911,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129727792</v>
+        <v>129726763</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,14 +3954,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488815</v>
+        <v>488626</v>
       </c>
       <c r="R32" t="n">
-        <v>7144788</v>
+        <v>7145010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3987,14 +3991,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4009,22 +4018,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726760</v>
+        <v>129716436</v>
       </c>
       <c r="B33" t="n">
-        <v>88986</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,34 +4041,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488426</v>
+        <v>489031</v>
       </c>
       <c r="R33" t="n">
-        <v>7145052</v>
+        <v>7144903</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4089,19 +4098,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4116,22 +4115,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727945</v>
+        <v>129727792</v>
       </c>
       <c r="B34" t="n">
-        <v>91601</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4139,37 +4138,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489010</v>
+        <v>488815</v>
       </c>
       <c r="R34" t="n">
-        <v>7144808</v>
+        <v>7144788</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4204,35 +4200,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129727802</v>
+        <v>129726765</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>82911</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488268</v>
+        <v>488725</v>
       </c>
       <c r="R35" t="n">
-        <v>7145078</v>
+        <v>7144925</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,14 +4297,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,12 +4324,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4334,7 +4339,7 @@
         <v>129726784</v>
       </c>
       <c r="B36" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4438,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726765</v>
+        <v>129727802</v>
       </c>
       <c r="B37" t="n">
-        <v>82910</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,34 +4454,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488725</v>
+        <v>488268</v>
       </c>
       <c r="R37" t="n">
-        <v>7144925</v>
+        <v>7145078</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4506,19 +4511,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4533,12 +4533,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
         <v>129726771</v>
       </c>
       <c r="B38" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726782</v>
+        <v>129716425</v>
       </c>
       <c r="B39" t="n">
-        <v>83044</v>
+        <v>88987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488365</v>
+        <v>488829</v>
       </c>
       <c r="R39" t="n">
-        <v>7144983</v>
+        <v>7144835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,19 +4716,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,22 +4733,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727959</v>
+        <v>129726780</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>83050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,34 +4756,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488762</v>
+        <v>488414</v>
       </c>
       <c r="R40" t="n">
-        <v>7144801</v>
+        <v>7144975</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4823,9 +4813,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4840,22 +4840,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129727788</v>
+        <v>129726782</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>83045</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,34 +4863,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488989</v>
+        <v>488365</v>
       </c>
       <c r="R41" t="n">
-        <v>7144826</v>
+        <v>7144983</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,14 +4920,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4942,22 +4947,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726780</v>
+        <v>129727959</v>
       </c>
       <c r="B42" t="n">
-        <v>83049</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,34 +4970,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488414</v>
+        <v>488762</v>
       </c>
       <c r="R42" t="n">
-        <v>7144975</v>
+        <v>7144801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,19 +5027,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5049,22 +5044,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129716425</v>
+        <v>129727788</v>
       </c>
       <c r="B43" t="n">
-        <v>88986</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,21 +5067,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5096,10 +5091,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488829</v>
+        <v>488989</v>
       </c>
       <c r="R43" t="n">
-        <v>7144835</v>
+        <v>7144826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5134,6 +5129,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5146,22 +5146,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727781</v>
+        <v>129716437</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>83045</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5169,21 +5169,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488586</v>
+        <v>488533</v>
       </c>
       <c r="R44" t="n">
-        <v>7144955</v>
+        <v>7144953</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,11 +5231,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5248,22 +5243,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727785</v>
+        <v>129727771</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>80182</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5271,34 +5266,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488865</v>
+        <v>488511</v>
       </c>
       <c r="R45" t="n">
-        <v>7144860</v>
+        <v>7144867</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5335,7 +5337,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5344,8 +5346,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5362,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727799</v>
+        <v>129727770</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>80182</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,34 +5401,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488408</v>
+        <v>488674</v>
       </c>
       <c r="R46" t="n">
-        <v>7144970</v>
+        <v>7144814</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5437,7 +5472,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5446,8 +5481,34 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5464,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129716437</v>
+        <v>129727948</v>
       </c>
       <c r="B47" t="n">
-        <v>83044</v>
+        <v>91588</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5475,34 +5536,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488533</v>
+        <v>488739</v>
       </c>
       <c r="R47" t="n">
-        <v>7144953</v>
+        <v>7144803</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,22 +5610,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726775</v>
+        <v>129727781</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5592,14 +5653,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488851</v>
+        <v>488586</v>
       </c>
       <c r="R48" t="n">
-        <v>7144825</v>
+        <v>7144955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5629,19 +5690,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5656,22 +5712,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727777</v>
+        <v>129727785</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,10 +5759,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488483</v>
+        <v>488865</v>
       </c>
       <c r="R49" t="n">
-        <v>7144992</v>
+        <v>7144860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5743,7 +5799,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5770,10 +5826,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727771</v>
+        <v>129727799</v>
       </c>
       <c r="B50" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5781,41 +5837,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488511</v>
+        <v>488408</v>
       </c>
       <c r="R50" t="n">
-        <v>7144867</v>
+        <v>7144970</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5852,7 +5901,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5861,34 +5910,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5905,10 +5928,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727948</v>
+        <v>129726775</v>
       </c>
       <c r="B51" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,34 +5939,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488739</v>
+        <v>488851</v>
       </c>
       <c r="R51" t="n">
-        <v>7144803</v>
+        <v>7144825</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5973,9 +5996,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5990,22 +6023,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727770</v>
+        <v>129727777</v>
       </c>
       <c r="B52" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6013,41 +6046,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488674</v>
+        <v>488483</v>
       </c>
       <c r="R52" t="n">
-        <v>7144814</v>
+        <v>7144992</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6084,7 +6110,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6093,34 +6119,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6137,45 +6137,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716431</v>
+        <v>129727953</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>91970</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488426</v>
+        <v>488400</v>
       </c>
       <c r="R53" t="n">
-        <v>7145034</v>
+        <v>7144968</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>83050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R54" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,11 +6307,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6324,57 +6319,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727953</v>
+        <v>129716431</v>
       </c>
       <c r="B55" t="n">
-        <v>91969</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488400</v>
+        <v>488426</v>
       </c>
       <c r="R55" t="n">
-        <v>7144968</v>
+        <v>7145034</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6421,22 +6416,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716447</v>
+        <v>129727780</v>
       </c>
       <c r="B56" t="n">
-        <v>83049</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6444,21 +6439,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6468,10 +6463,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488731</v>
+        <v>488542</v>
       </c>
       <c r="R56" t="n">
-        <v>7144891</v>
+        <v>7144969</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6506,6 +6501,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,12 +6518,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6533,7 +6533,7 @@
         <v>129727791</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129727800</v>
+        <v>129716430</v>
       </c>
       <c r="B58" t="n">
-        <v>79075</v>
+        <v>91608</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6643,23 +6643,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6667,10 +6663,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488375</v>
+        <v>488835</v>
       </c>
       <c r="R58" t="n">
-        <v>7144951</v>
+        <v>7144824</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,11 +6701,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6722,22 +6713,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716430</v>
+        <v>129716440</v>
       </c>
       <c r="B59" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6765,10 +6756,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488835</v>
+        <v>488547</v>
       </c>
       <c r="R59" t="n">
-        <v>7144824</v>
+        <v>7144971</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6827,10 +6818,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716440</v>
+        <v>129727800</v>
       </c>
       <c r="B60" t="n">
-        <v>91607</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6838,19 +6829,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6858,10 +6853,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488547</v>
+        <v>488375</v>
       </c>
       <c r="R60" t="n">
-        <v>7144971</v>
+        <v>7144951</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6896,6 +6891,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6908,46 +6908,42 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716428</v>
+        <v>129716442</v>
       </c>
       <c r="B61" t="n">
-        <v>92305</v>
+        <v>91608</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6955,10 +6951,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489052</v>
+        <v>488630</v>
       </c>
       <c r="R61" t="n">
-        <v>7144873</v>
+        <v>7145015</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7017,30 +7013,34 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129716442</v>
+        <v>129716428</v>
       </c>
       <c r="B62" t="n">
-        <v>91607</v>
+        <v>92306</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488630</v>
+        <v>489052</v>
       </c>
       <c r="R62" t="n">
-        <v>7145015</v>
+        <v>7144873</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7113,7 +7113,7 @@
         <v>129716423</v>
       </c>
       <c r="B63" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>129726764</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>129727793</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>129727798</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>129716433</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>129727790</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>129716432</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>129727787</v>
       </c>
       <c r="B70" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>129727958</v>
       </c>
       <c r="B71" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129726778</v>
+        <v>129727951</v>
       </c>
       <c r="B72" t="n">
-        <v>79075</v>
+        <v>91886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488522</v>
+        <v>489112</v>
       </c>
       <c r="R72" t="n">
-        <v>7144974</v>
+        <v>7144780</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,19 +8086,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8113,22 +8103,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129716429</v>
+        <v>129727954</v>
       </c>
       <c r="B73" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8136,34 +8126,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488440</v>
+        <v>489143</v>
       </c>
       <c r="R73" t="n">
-        <v>7144976</v>
+        <v>7144773</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,22 +8200,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129727778</v>
+        <v>129726778</v>
       </c>
       <c r="B74" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8253,14 +8243,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488513</v>
+        <v>488522</v>
       </c>
       <c r="R74" t="n">
-        <v>7144973</v>
+        <v>7144974</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,14 +8280,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8312,22 +8307,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726779</v>
+        <v>129716429</v>
       </c>
       <c r="B75" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8355,14 +8350,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488452</v>
+        <v>488440</v>
       </c>
       <c r="R75" t="n">
-        <v>7144979</v>
+        <v>7144976</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8392,19 +8387,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8419,22 +8404,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129727951</v>
+        <v>129727778</v>
       </c>
       <c r="B76" t="n">
-        <v>91885</v>
+        <v>79076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8442,34 +8427,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489112</v>
+        <v>488513</v>
       </c>
       <c r="R76" t="n">
-        <v>7144780</v>
+        <v>7144973</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8504,6 +8489,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8516,22 +8506,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129727954</v>
+        <v>129726779</v>
       </c>
       <c r="B77" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8539,34 +8529,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489143</v>
+        <v>488452</v>
       </c>
       <c r="R77" t="n">
-        <v>7144773</v>
+        <v>7144979</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8596,9 +8586,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
         <v>129716424</v>
       </c>
       <c r="B78" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726777</v>
+        <v>129716434</v>
       </c>
       <c r="B79" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,34 +8733,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488570</v>
+        <v>488618</v>
       </c>
       <c r="R79" t="n">
-        <v>7144960</v>
+        <v>7144922</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8790,19 +8790,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8817,22 +8807,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716445</v>
+        <v>129727957</v>
       </c>
       <c r="B80" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8840,34 +8830,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488685</v>
+        <v>488591</v>
       </c>
       <c r="R80" t="n">
-        <v>7144909</v>
+        <v>7144844</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8914,22 +8904,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129716441</v>
+        <v>129726777</v>
       </c>
       <c r="B81" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8957,14 +8947,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488921</v>
+        <v>488570</v>
       </c>
       <c r="R81" t="n">
-        <v>7144886</v>
+        <v>7144960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8994,9 +8984,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9011,22 +9011,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129716422</v>
+        <v>129716445</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9058,10 +9058,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488767</v>
+        <v>488685</v>
       </c>
       <c r="R82" t="n">
-        <v>7144853</v>
+        <v>7144909</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9120,52 +9120,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129727767</v>
+        <v>129716441</v>
       </c>
       <c r="B83" t="n">
-        <v>80209</v>
+        <v>79076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488658</v>
+        <v>488921</v>
       </c>
       <c r="R83" t="n">
-        <v>7144806</v>
+        <v>7144886</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9200,65 +9193,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129716434</v>
+        <v>129716422</v>
       </c>
       <c r="B84" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9266,21 +9228,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9290,10 +9252,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488618</v>
+        <v>488767</v>
       </c>
       <c r="R84" t="n">
-        <v>7144922</v>
+        <v>7144853</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9355,7 +9317,7 @@
         <v>129727769</v>
       </c>
       <c r="B85" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9487,45 +9449,52 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727957</v>
+        <v>129727767</v>
       </c>
       <c r="B86" t="n">
-        <v>91583</v>
+        <v>80210</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488591</v>
+        <v>488658</v>
       </c>
       <c r="R86" t="n">
-        <v>7144844</v>
+        <v>7144806</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9560,24 +9529,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9587,7 +9587,7 @@
         <v>129726773</v>
       </c>
       <c r="B87" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>129727795</v>
       </c>
       <c r="B88" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>129727794</v>
       </c>
       <c r="B89" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>129727960</v>
       </c>
       <c r="B90" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>129727783</v>
       </c>
       <c r="B91" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>129726769</v>
       </c>
       <c r="B92" t="n">
-        <v>75059</v>
+        <v>75060</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R93" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,19 +10289,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10339,34 +10329,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R94" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10396,9 +10386,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,44 +10413,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>57735</v>
+        <v>92306</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R95" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,32 +10522,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730462</v>
+        <v>129730439</v>
       </c>
       <c r="B96" t="n">
-        <v>92305</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489017</v>
+        <v>488746</v>
       </c>
       <c r="R96" t="n">
-        <v>7144821</v>
+        <v>7144786</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10598,6 +10593,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10627,7 +10627,7 @@
         <v>129730469</v>
       </c>
       <c r="B97" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>129730460</v>
       </c>
       <c r="B98" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>129730457</v>
       </c>
       <c r="B99" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730465</v>
+        <v>129730473</v>
       </c>
       <c r="B100" t="n">
-        <v>80209</v>
+        <v>91584</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488705</v>
+        <v>489028</v>
       </c>
       <c r="R100" t="n">
-        <v>7144862</v>
+        <v>7144803</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,10 +11017,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730449</v>
+        <v>129730474</v>
       </c>
       <c r="B101" t="n">
-        <v>80181</v>
+        <v>91584</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11028,21 +11028,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488414</v>
+        <v>488676</v>
       </c>
       <c r="R101" t="n">
-        <v>7144940</v>
+        <v>7144870</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730473</v>
+        <v>129730449</v>
       </c>
       <c r="B102" t="n">
-        <v>91583</v>
+        <v>80182</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489028</v>
+        <v>488414</v>
       </c>
       <c r="R102" t="n">
-        <v>7144803</v>
+        <v>7144940</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730474</v>
+        <v>129730465</v>
       </c>
       <c r="B103" t="n">
-        <v>91583</v>
+        <v>80210</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488676</v>
+        <v>488705</v>
       </c>
       <c r="R103" t="n">
-        <v>7144870</v>
+        <v>7144862</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>129730451</v>
       </c>
       <c r="B104" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>129730461</v>
       </c>
       <c r="B105" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>129730443</v>
       </c>
       <c r="B106" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>129730441</v>
       </c>
       <c r="B107" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>129730454</v>
       </c>
       <c r="B108" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>79075</v>
+        <v>91602</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R109" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,11 +11874,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,10 +11900,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B110" t="n">
-        <v>91601</v>
+        <v>79076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11916,21 +11911,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11940,10 +11935,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R110" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,6 +11971,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12005,7 +12005,7 @@
         <v>129730450</v>
       </c>
       <c r="B111" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129730448</v>
       </c>
       <c r="B112" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>83049</v>
+        <v>83050</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129730464</v>
       </c>
       <c r="B114" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>129730470</v>
       </c>
       <c r="B115" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730463</v>
+        <v>129730468</v>
       </c>
       <c r="B116" t="n">
-        <v>57735</v>
+        <v>78089</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12508,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488546</v>
+        <v>488763</v>
       </c>
       <c r="R116" t="n">
-        <v>7144950</v>
+        <v>7144808</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12568,11 +12568,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12599,10 +12594,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730468</v>
+        <v>129730463</v>
       </c>
       <c r="B117" t="n">
-        <v>78088</v>
+        <v>57736</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12610,21 +12605,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12634,10 +12629,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488763</v>
+        <v>488546</v>
       </c>
       <c r="R117" t="n">
-        <v>7144808</v>
+        <v>7144950</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12670,6 +12665,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12699,7 +12699,7 @@
         <v>129730458</v>
       </c>
       <c r="B118" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>129730471</v>
       </c>
       <c r="B119" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>129730476</v>
       </c>
       <c r="B120" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12987,30 +12987,34 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730478</v>
+        <v>129730456</v>
       </c>
       <c r="B121" t="n">
-        <v>91607</v>
+        <v>91959</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13018,10 +13022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488436</v>
+        <v>488467</v>
       </c>
       <c r="R121" t="n">
-        <v>7144967</v>
+        <v>7144951</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13080,32 +13084,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730456</v>
+        <v>129730459</v>
       </c>
       <c r="B122" t="n">
-        <v>91958</v>
+        <v>91588</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13115,10 +13119,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488467</v>
+        <v>488604</v>
       </c>
       <c r="R122" t="n">
-        <v>7144951</v>
+        <v>7144985</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13177,10 +13181,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730459</v>
+        <v>129730478</v>
       </c>
       <c r="B123" t="n">
-        <v>91587</v>
+        <v>91608</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13188,23 +13192,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488604</v>
+        <v>488436</v>
       </c>
       <c r="R123" t="n">
-        <v>7144985</v>
+        <v>7144967</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13277,7 +13277,7 @@
         <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>129730446</v>
       </c>
       <c r="B125" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>129730447</v>
       </c>
       <c r="B126" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B127" t="n">
-        <v>83049</v>
+        <v>79076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R127" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B128" t="n">
-        <v>79075</v>
+        <v>83050</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R128" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13762,7 +13762,7 @@
         <v>129730472</v>
       </c>
       <c r="B129" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>129730475</v>
       </c>
       <c r="B130" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>129730440</v>
       </c>
       <c r="B131" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -1664,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727782</v>
+        <v>129727776</v>
       </c>
       <c r="B11" t="n">
         <v>79076</v>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488694</v>
+        <v>488425</v>
       </c>
       <c r="R11" t="n">
-        <v>7144925</v>
+        <v>7145015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,7 +1766,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727796</v>
+        <v>129726761</v>
       </c>
       <c r="B12" t="n">
         <v>79076</v>
@@ -1797,14 +1797,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488507</v>
+        <v>488516</v>
       </c>
       <c r="R12" t="n">
-        <v>7144870</v>
+        <v>7145014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,14 +1834,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,64 +1861,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727765</v>
+        <v>129727801</v>
       </c>
       <c r="B13" t="n">
-        <v>80210</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488701</v>
+        <v>488339</v>
       </c>
       <c r="R13" t="n">
-        <v>7144801</v>
+        <v>7144937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,34 +1957,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2003,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726781</v>
+        <v>129727782</v>
       </c>
       <c r="B14" t="n">
-        <v>78089</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,34 +1986,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488365</v>
+        <v>488694</v>
       </c>
       <c r="R14" t="n">
-        <v>7144983</v>
+        <v>7144925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,19 +2043,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,19 +2065,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727776</v>
+        <v>129727796</v>
       </c>
       <c r="B15" t="n">
         <v>79076</v>
@@ -2145,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488425</v>
+        <v>488507</v>
       </c>
       <c r="R15" t="n">
-        <v>7145015</v>
+        <v>7144870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2152,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,45 +2179,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726761</v>
+        <v>129727765</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>80210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488516</v>
+        <v>488701</v>
       </c>
       <c r="R16" t="n">
-        <v>7145014</v>
+        <v>7144801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,19 +2254,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,28 +2270,54 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727801</v>
+        <v>129726781</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>78089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2325,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488339</v>
+        <v>488365</v>
       </c>
       <c r="R17" t="n">
-        <v>7144937</v>
+        <v>7144983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,14 +2382,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,12 +2409,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B27" t="n">
-        <v>80182</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,41 +3387,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R27" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,65 +3454,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,39 +3489,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R28" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,6 +3551,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3601,22 +3568,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727786</v>
+        <v>129727772</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>80182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,34 +3591,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489035</v>
+        <v>488470</v>
       </c>
       <c r="R29" t="n">
-        <v>7144832</v>
+        <v>7144960</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,7 +3662,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3697,8 +3671,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129716425</v>
+        <v>129726782</v>
       </c>
       <c r="B39" t="n">
-        <v>88987</v>
+        <v>83045</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488829</v>
+        <v>488365</v>
       </c>
       <c r="R39" t="n">
-        <v>7144835</v>
+        <v>7144983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,9 +4716,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4733,22 +4743,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726780</v>
+        <v>129716425</v>
       </c>
       <c r="B40" t="n">
-        <v>83050</v>
+        <v>88987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4756,34 +4766,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488414</v>
+        <v>488829</v>
       </c>
       <c r="R40" t="n">
-        <v>7144975</v>
+        <v>7144835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4813,19 +4823,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4840,22 +4840,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726782</v>
+        <v>129727959</v>
       </c>
       <c r="B41" t="n">
-        <v>83045</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,34 +4863,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488365</v>
+        <v>488762</v>
       </c>
       <c r="R41" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,19 +4920,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4947,19 +4937,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129727959</v>
+        <v>129727788</v>
       </c>
       <c r="B42" t="n">
         <v>79076</v>
@@ -4990,14 +4980,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488762</v>
+        <v>488989</v>
       </c>
       <c r="R42" t="n">
-        <v>7144801</v>
+        <v>7144826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,6 +5022,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5044,22 +5039,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129727788</v>
+        <v>129726780</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5067,34 +5062,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488989</v>
+        <v>488414</v>
       </c>
       <c r="R43" t="n">
-        <v>7144826</v>
+        <v>7144975</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,14 +5119,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,22 +5146,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129716437</v>
+        <v>129727948</v>
       </c>
       <c r="B44" t="n">
-        <v>83045</v>
+        <v>91588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488533</v>
+        <v>488739</v>
       </c>
       <c r="R44" t="n">
-        <v>7144953</v>
+        <v>7144803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5243,22 +5243,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727771</v>
+        <v>129727781</v>
       </c>
       <c r="B45" t="n">
-        <v>80182</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5266,41 +5266,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488511</v>
+        <v>488586</v>
       </c>
       <c r="R45" t="n">
-        <v>7144867</v>
+        <v>7144955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,7 +5330,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5346,34 +5339,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5390,10 +5357,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727770</v>
+        <v>129727785</v>
       </c>
       <c r="B46" t="n">
-        <v>80182</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,41 +5368,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488674</v>
+        <v>488865</v>
       </c>
       <c r="R46" t="n">
-        <v>7144814</v>
+        <v>7144860</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5472,7 +5432,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5481,34 +5441,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5525,10 +5459,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727948</v>
+        <v>129727799</v>
       </c>
       <c r="B47" t="n">
-        <v>91588</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,34 +5470,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488739</v>
+        <v>488408</v>
       </c>
       <c r="R47" t="n">
-        <v>7144803</v>
+        <v>7144970</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,6 +5532,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5610,19 +5549,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727781</v>
+        <v>129726775</v>
       </c>
       <c r="B48" t="n">
         <v>79076</v>
@@ -5653,14 +5592,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488586</v>
+        <v>488851</v>
       </c>
       <c r="R48" t="n">
-        <v>7144955</v>
+        <v>7144825</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5690,14 +5629,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5712,19 +5656,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727785</v>
+        <v>129727777</v>
       </c>
       <c r="B49" t="n">
         <v>79076</v>
@@ -5759,10 +5703,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488865</v>
+        <v>488483</v>
       </c>
       <c r="R49" t="n">
-        <v>7144860</v>
+        <v>7144992</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5799,7 +5743,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5826,10 +5770,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727799</v>
+        <v>129727771</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>80182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5837,34 +5781,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488408</v>
+        <v>488511</v>
       </c>
       <c r="R50" t="n">
-        <v>7144970</v>
+        <v>7144867</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5901,7 +5852,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5910,8 +5861,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5928,10 +5905,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129726775</v>
+        <v>129727770</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>80182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5939,34 +5916,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488851</v>
+        <v>488674</v>
       </c>
       <c r="R51" t="n">
-        <v>7144825</v>
+        <v>7144814</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,19 +5980,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6017,28 +5996,54 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727777</v>
+        <v>129716437</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>83045</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,21 +6051,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488483</v>
+        <v>488533</v>
       </c>
       <c r="R52" t="n">
-        <v>7144992</v>
+        <v>7144953</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,11 +6113,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6125,12 +6125,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129716433</v>
+        <v>129716432</v>
       </c>
       <c r="B67" t="n">
         <v>79076</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488359</v>
+        <v>489065</v>
       </c>
       <c r="R67" t="n">
-        <v>7144987</v>
+        <v>7144852</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7589,6 +7589,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7615,7 +7620,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129727790</v>
+        <v>129727787</v>
       </c>
       <c r="B68" t="n">
         <v>79076</v>
@@ -7650,10 +7655,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488911</v>
+        <v>489024</v>
       </c>
       <c r="R68" t="n">
-        <v>7144836</v>
+        <v>7144841</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7690,7 +7695,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7717,7 +7722,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129716432</v>
+        <v>129727958</v>
       </c>
       <c r="B69" t="n">
         <v>79076</v>
@@ -7748,14 +7753,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489065</v>
+        <v>488796</v>
       </c>
       <c r="R69" t="n">
-        <v>7144852</v>
+        <v>7144792</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7790,11 +7795,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7807,19 +7807,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129727787</v>
+        <v>129716433</v>
       </c>
       <c r="B70" t="n">
         <v>79076</v>
@@ -7854,10 +7854,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489024</v>
+        <v>488359</v>
       </c>
       <c r="R70" t="n">
-        <v>7144841</v>
+        <v>7144987</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7892,11 +7892,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7909,19 +7904,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129727958</v>
+        <v>129727790</v>
       </c>
       <c r="B71" t="n">
         <v>79076</v>
@@ -7952,14 +7947,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488796</v>
+        <v>488911</v>
       </c>
       <c r="R71" t="n">
-        <v>7144792</v>
+        <v>7144836</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7994,6 +7989,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8006,12 +8006,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726773</v>
+        <v>129727795</v>
       </c>
       <c r="B87" t="n">
-        <v>91588</v>
+        <v>79076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489020</v>
+        <v>488737</v>
       </c>
       <c r="R87" t="n">
-        <v>7144867</v>
+        <v>7144797</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,19 +9652,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9679,19 +9674,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727795</v>
+        <v>129727794</v>
       </c>
       <c r="B88" t="n">
         <v>79076</v>
@@ -9726,10 +9721,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488737</v>
+        <v>488763</v>
       </c>
       <c r="R88" t="n">
-        <v>7144797</v>
+        <v>7144775</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9766,7 +9761,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en levande gammal gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9793,7 +9788,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727794</v>
+        <v>129727960</v>
       </c>
       <c r="B89" t="n">
         <v>79076</v>
@@ -9824,14 +9819,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488763</v>
+        <v>488374</v>
       </c>
       <c r="R89" t="n">
-        <v>7144775</v>
+        <v>7144949</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9868,7 +9863,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9883,19 +9878,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727960</v>
+        <v>129727783</v>
       </c>
       <c r="B90" t="n">
         <v>79076</v>
@@ -9926,14 +9921,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488374</v>
+        <v>488709</v>
       </c>
       <c r="R90" t="n">
-        <v>7144949</v>
+        <v>7144911</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9965,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9985,22 +9980,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727783</v>
+        <v>129726773</v>
       </c>
       <c r="B91" t="n">
-        <v>79076</v>
+        <v>91588</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10008,34 +10003,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488709</v>
+        <v>489020</v>
       </c>
       <c r="R91" t="n">
-        <v>7144911</v>
+        <v>7144867</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10065,14 +10060,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På levande gran i gammal granskog.</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10087,12 +10087,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B93" t="n">
-        <v>91584</v>
+        <v>79076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R93" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,9 +10289,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10306,22 +10316,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B94" t="n">
-        <v>79076</v>
+        <v>91584</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10329,34 +10339,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R94" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10386,19 +10396,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,12 +10413,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730468</v>
+        <v>129730463</v>
       </c>
       <c r="B116" t="n">
-        <v>78089</v>
+        <v>57736</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12508,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488763</v>
+        <v>488546</v>
       </c>
       <c r="R116" t="n">
-        <v>7144808</v>
+        <v>7144950</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12568,6 +12568,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12594,10 +12599,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730463</v>
+        <v>129730468</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>78089</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12605,21 +12610,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12629,10 +12634,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488546</v>
+        <v>488763</v>
       </c>
       <c r="R117" t="n">
-        <v>7144950</v>
+        <v>7144808</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12665,11 +12670,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B127" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R127" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B128" t="n">
-        <v>83050</v>
+        <v>79076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R128" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129727955</v>
       </c>
       <c r="B2" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129727773</v>
       </c>
       <c r="B3" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129716427</v>
+        <v>129726770</v>
       </c>
       <c r="B4" t="n">
-        <v>83037</v>
+        <v>80187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488400</v>
+        <v>489064</v>
       </c>
       <c r="R4" t="n">
-        <v>7144977</v>
+        <v>7144843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,11 +975,21 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -988,26 +998,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727797</v>
+        <v>129716427</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>83042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488482</v>
+        <v>488400</v>
       </c>
       <c r="R5" t="n">
-        <v>7144891</v>
+        <v>7144977</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1102,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1094,22 +1114,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726770</v>
+        <v>129726758</v>
       </c>
       <c r="B6" t="n">
-        <v>80182</v>
+        <v>82916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489064</v>
+        <v>488417</v>
       </c>
       <c r="R6" t="n">
-        <v>7144843</v>
+        <v>7145102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,21 +1217,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1228,45 +1233,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726758</v>
+        <v>129727766</v>
       </c>
       <c r="B7" t="n">
-        <v>82911</v>
+        <v>80215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488417</v>
+        <v>488676</v>
       </c>
       <c r="R7" t="n">
-        <v>7145102</v>
+        <v>7144814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,19 +1308,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,70 +1324,89 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129727766</v>
+        <v>129727797</v>
       </c>
       <c r="B8" t="n">
-        <v>80210</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488676</v>
+        <v>488482</v>
       </c>
       <c r="R8" t="n">
-        <v>7144814</v>
+        <v>7144891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1443,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,34 +1452,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,7 +1473,7 @@
         <v>129727952</v>
       </c>
       <c r="B9" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>129716439</v>
       </c>
       <c r="B10" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,45 +1664,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727776</v>
+        <v>129727765</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>80215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488425</v>
+        <v>488701</v>
       </c>
       <c r="R11" t="n">
-        <v>7145015</v>
+        <v>7144801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1746,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,8 +1755,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1766,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726761</v>
+        <v>129727776</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,14 +1830,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488516</v>
+        <v>488425</v>
       </c>
       <c r="R12" t="n">
-        <v>7145014</v>
+        <v>7145015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,19 +1867,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,22 +1889,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727801</v>
+        <v>129726761</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,14 +1932,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488339</v>
+        <v>488516</v>
       </c>
       <c r="R13" t="n">
-        <v>7144937</v>
+        <v>7145014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,14 +1969,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,22 +1996,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727782</v>
+        <v>129727801</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2010,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488694</v>
+        <v>488339</v>
       </c>
       <c r="R14" t="n">
-        <v>7144925</v>
+        <v>7144937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2083,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727796</v>
+        <v>129727782</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488507</v>
+        <v>488694</v>
       </c>
       <c r="R15" t="n">
-        <v>7144870</v>
+        <v>7144925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2185,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,52 +2212,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727765</v>
+        <v>129727796</v>
       </c>
       <c r="B16" t="n">
-        <v>80210</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488701</v>
+        <v>488507</v>
       </c>
       <c r="R16" t="n">
-        <v>7144801</v>
+        <v>7144870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,7 +2287,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,34 +2296,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2317,7 +2317,7 @@
         <v>129726781</v>
       </c>
       <c r="B17" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726774</v>
+        <v>129727947</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2432,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489025</v>
+        <v>488803</v>
       </c>
       <c r="R18" t="n">
-        <v>7144875</v>
+        <v>7144779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,19 +2489,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,22 +2506,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727947</v>
+        <v>129716443</v>
       </c>
       <c r="B19" t="n">
-        <v>91588</v>
+        <v>91589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,34 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488803</v>
+        <v>488470</v>
       </c>
       <c r="R19" t="n">
-        <v>7144779</v>
+        <v>7144975</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129716443</v>
+        <v>129726774</v>
       </c>
       <c r="B20" t="n">
-        <v>91584</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,34 +2626,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488470</v>
+        <v>489025</v>
       </c>
       <c r="R20" t="n">
-        <v>7144975</v>
+        <v>7144875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,9 +2683,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,12 +2710,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
         <v>129726757</v>
       </c>
       <c r="B22" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129726772</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129726762</v>
+        <v>129727950</v>
       </c>
       <c r="B24" t="n">
-        <v>83045</v>
+        <v>80187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,34 +3086,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488626</v>
+        <v>488374</v>
       </c>
       <c r="R24" t="n">
-        <v>7145010</v>
+        <v>7144953</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,19 +3143,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,12 +3160,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3185,7 +3175,7 @@
         <v>129727946</v>
       </c>
       <c r="B25" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129727950</v>
+        <v>129726762</v>
       </c>
       <c r="B26" t="n">
-        <v>80182</v>
+        <v>83050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,34 +3280,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488374</v>
+        <v>488626</v>
       </c>
       <c r="R26" t="n">
-        <v>7144953</v>
+        <v>7145010</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3347,9 +3337,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,22 +3364,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,39 +3387,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R27" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,6 +3449,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3466,22 +3466,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727786</v>
+        <v>129727772</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,34 +3489,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489035</v>
+        <v>488470</v>
       </c>
       <c r="R28" t="n">
-        <v>7144832</v>
+        <v>7144960</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3553,7 +3560,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3562,8 +3569,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3580,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B29" t="n">
-        <v>80182</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,41 +3624,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R29" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3660,55 +3691,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3718,7 +3718,7 @@
         <v>129727945</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>129726760</v>
       </c>
       <c r="B31" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>129726763</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>129716436</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>129727792</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726765</v>
+        <v>129726771</v>
       </c>
       <c r="B35" t="n">
-        <v>82911</v>
+        <v>91613</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,23 +4240,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4264,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488725</v>
+        <v>489056</v>
       </c>
       <c r="R35" t="n">
-        <v>7144925</v>
+        <v>7144853</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4299,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4309,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726784</v>
+        <v>129727802</v>
       </c>
       <c r="B36" t="n">
-        <v>83037</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,34 +4343,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488335</v>
+        <v>488268</v>
       </c>
       <c r="R36" t="n">
-        <v>7144978</v>
+        <v>7145078</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,19 +4400,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4431,22 +4422,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129727802</v>
+        <v>129726765</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>82916</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,34 +4445,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488268</v>
+        <v>488725</v>
       </c>
       <c r="R37" t="n">
-        <v>7145078</v>
+        <v>7144925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4511,14 +4502,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4533,22 +4529,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726771</v>
+        <v>129726784</v>
       </c>
       <c r="B38" t="n">
-        <v>91608</v>
+        <v>83042</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4556,19 +4552,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489056</v>
+        <v>488335</v>
       </c>
       <c r="R38" t="n">
-        <v>7144853</v>
+        <v>7144978</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726782</v>
+        <v>129716425</v>
       </c>
       <c r="B39" t="n">
-        <v>83045</v>
+        <v>88992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488365</v>
+        <v>488829</v>
       </c>
       <c r="R39" t="n">
-        <v>7144983</v>
+        <v>7144835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,19 +4716,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,22 +4733,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129716425</v>
+        <v>129726780</v>
       </c>
       <c r="B40" t="n">
-        <v>88987</v>
+        <v>83055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,34 +4756,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488829</v>
+        <v>488414</v>
       </c>
       <c r="R40" t="n">
-        <v>7144835</v>
+        <v>7144975</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4823,9 +4813,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4840,22 +4840,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129727959</v>
+        <v>129726782</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,34 +4863,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488762</v>
+        <v>488365</v>
       </c>
       <c r="R41" t="n">
-        <v>7144801</v>
+        <v>7144983</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,9 +4920,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4937,22 +4947,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129727788</v>
+        <v>129727959</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4980,14 +4990,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488989</v>
+        <v>488762</v>
       </c>
       <c r="R42" t="n">
-        <v>7144826</v>
+        <v>7144801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,11 +5032,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5039,22 +5044,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726780</v>
+        <v>129727788</v>
       </c>
       <c r="B43" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,34 +5067,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488414</v>
+        <v>488989</v>
       </c>
       <c r="R43" t="n">
-        <v>7144975</v>
+        <v>7144826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5119,19 +5124,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,22 +5146,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727948</v>
+        <v>129727771</v>
       </c>
       <c r="B44" t="n">
-        <v>91588</v>
+        <v>80187</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5169,34 +5169,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488739</v>
+        <v>488511</v>
       </c>
       <c r="R44" t="n">
-        <v>7144803</v>
+        <v>7144867</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,34 +5238,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727781</v>
+        <v>129727948</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5266,34 +5304,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488586</v>
+        <v>488739</v>
       </c>
       <c r="R45" t="n">
-        <v>7144955</v>
+        <v>7144803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5328,11 +5366,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5345,22 +5378,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727785</v>
+        <v>129727770</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5368,34 +5401,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488865</v>
+        <v>488674</v>
       </c>
       <c r="R46" t="n">
-        <v>7144860</v>
+        <v>7144814</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5472,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5441,8 +5481,34 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5459,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727799</v>
+        <v>129727781</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5494,10 +5560,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488408</v>
+        <v>488586</v>
       </c>
       <c r="R47" t="n">
-        <v>7144970</v>
+        <v>7144955</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,10 +5627,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726775</v>
+        <v>129727785</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5592,14 +5658,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488851</v>
+        <v>488865</v>
       </c>
       <c r="R48" t="n">
-        <v>7144825</v>
+        <v>7144860</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5629,19 +5695,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5656,22 +5717,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727777</v>
+        <v>129727799</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5703,10 +5764,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488483</v>
+        <v>488408</v>
       </c>
       <c r="R49" t="n">
-        <v>7144992</v>
+        <v>7144970</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5770,10 +5831,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727771</v>
+        <v>129716437</v>
       </c>
       <c r="B50" t="n">
-        <v>80182</v>
+        <v>83050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5781,41 +5842,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488511</v>
+        <v>488533</v>
       </c>
       <c r="R50" t="n">
-        <v>7144867</v>
+        <v>7144953</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5850,65 +5904,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727770</v>
+        <v>129726775</v>
       </c>
       <c r="B51" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,41 +5939,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488674</v>
+        <v>488851</v>
       </c>
       <c r="R51" t="n">
-        <v>7144814</v>
+        <v>7144825</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5980,14 +5996,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5996,54 +6017,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129716437</v>
+        <v>129727777</v>
       </c>
       <c r="B52" t="n">
-        <v>83045</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,21 +6046,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488533</v>
+        <v>488483</v>
       </c>
       <c r="R52" t="n">
-        <v>7144953</v>
+        <v>7144992</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,6 +6108,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6125,12 +6125,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
         <v>129727953</v>
       </c>
       <c r="B53" t="n">
-        <v>91970</v>
+        <v>91975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>129716447</v>
       </c>
       <c r="B54" t="n">
-        <v>83050</v>
+        <v>83055</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>129716431</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>129727780</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>129727791</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129716430</v>
+        <v>129727800</v>
       </c>
       <c r="B58" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6643,19 +6643,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6663,10 +6667,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488835</v>
+        <v>488375</v>
       </c>
       <c r="R58" t="n">
-        <v>7144824</v>
+        <v>7144951</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6701,6 +6705,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6713,22 +6722,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716440</v>
+        <v>129716430</v>
       </c>
       <c r="B59" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6756,10 +6765,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488547</v>
+        <v>488835</v>
       </c>
       <c r="R59" t="n">
-        <v>7144971</v>
+        <v>7144824</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6818,10 +6827,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129727800</v>
+        <v>129716440</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6829,23 +6838,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6853,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488375</v>
+        <v>488547</v>
       </c>
       <c r="R60" t="n">
-        <v>7144951</v>
+        <v>7144971</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,11 +6896,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6908,42 +6908,46 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716442</v>
+        <v>129716428</v>
       </c>
       <c r="B61" t="n">
-        <v>91608</v>
+        <v>92311</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6951,10 +6955,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488630</v>
+        <v>489052</v>
       </c>
       <c r="R61" t="n">
-        <v>7145015</v>
+        <v>7144873</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,34 +7017,30 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129716428</v>
+        <v>129716442</v>
       </c>
       <c r="B62" t="n">
-        <v>92306</v>
+        <v>91613</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489052</v>
+        <v>488630</v>
       </c>
       <c r="R62" t="n">
-        <v>7144873</v>
+        <v>7145015</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7113,7 +7113,7 @@
         <v>129716423</v>
       </c>
       <c r="B63" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>129726764</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>129727793</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>129727798</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7518,10 +7518,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129716432</v>
+        <v>129716433</v>
       </c>
       <c r="B67" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>489065</v>
+        <v>488359</v>
       </c>
       <c r="R67" t="n">
-        <v>7144852</v>
+        <v>7144987</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7589,11 +7589,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7620,10 +7615,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129727787</v>
+        <v>129727790</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7655,10 +7650,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489024</v>
+        <v>488911</v>
       </c>
       <c r="R68" t="n">
-        <v>7144841</v>
+        <v>7144836</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7695,7 +7690,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gammal gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7722,10 +7717,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129727958</v>
+        <v>129716432</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7753,14 +7748,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488796</v>
+        <v>489065</v>
       </c>
       <c r="R69" t="n">
-        <v>7144792</v>
+        <v>7144852</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7795,6 +7790,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7807,22 +7807,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129716433</v>
+        <v>129727787</v>
       </c>
       <c r="B70" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7854,10 +7854,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488359</v>
+        <v>489024</v>
       </c>
       <c r="R70" t="n">
-        <v>7144987</v>
+        <v>7144841</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7892,6 +7892,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7904,22 +7909,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129727790</v>
+        <v>129727958</v>
       </c>
       <c r="B71" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7947,14 +7952,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488911</v>
+        <v>488796</v>
       </c>
       <c r="R71" t="n">
-        <v>7144836</v>
+        <v>7144792</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7989,11 +7994,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8006,22 +8006,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129727951</v>
+        <v>129726778</v>
       </c>
       <c r="B72" t="n">
-        <v>91886</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489112</v>
+        <v>488522</v>
       </c>
       <c r="R72" t="n">
-        <v>7144780</v>
+        <v>7144974</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,9 +8086,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8103,22 +8113,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129727954</v>
+        <v>129716429</v>
       </c>
       <c r="B73" t="n">
-        <v>91584</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8126,34 +8136,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489143</v>
+        <v>488440</v>
       </c>
       <c r="R73" t="n">
-        <v>7144773</v>
+        <v>7144976</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8200,22 +8210,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129726778</v>
+        <v>129727778</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8243,14 +8253,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488522</v>
+        <v>488513</v>
       </c>
       <c r="R74" t="n">
-        <v>7144974</v>
+        <v>7144973</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8280,19 +8290,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:10</t>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8307,22 +8312,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129716429</v>
+        <v>129726779</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8350,14 +8355,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488440</v>
+        <v>488452</v>
       </c>
       <c r="R75" t="n">
-        <v>7144976</v>
+        <v>7144979</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8387,9 +8392,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8404,22 +8419,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129727778</v>
+        <v>129727951</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>91891</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,34 +8442,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488513</v>
+        <v>489112</v>
       </c>
       <c r="R76" t="n">
-        <v>7144973</v>
+        <v>7144780</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8489,11 +8504,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8506,22 +8516,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726779</v>
+        <v>129727954</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,34 +8539,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488452</v>
+        <v>489143</v>
       </c>
       <c r="R77" t="n">
-        <v>7144979</v>
+        <v>7144773</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8586,19 +8596,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
         <v>129716424</v>
       </c>
       <c r="B78" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>129716434</v>
       </c>
       <c r="B79" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8819,10 +8819,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129727957</v>
+        <v>129727769</v>
       </c>
       <c r="B80" t="n">
-        <v>91584</v>
+        <v>80187</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8830,34 +8830,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488591</v>
+        <v>488758</v>
       </c>
       <c r="R80" t="n">
-        <v>7144844</v>
+        <v>7144774</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8892,34 +8899,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129726777</v>
+        <v>129727957</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8927,34 +8965,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488570</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7144960</v>
+        <v>7144844</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8984,19 +9022,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9011,22 +9039,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129716445</v>
+        <v>129726777</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9054,14 +9082,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488685</v>
+        <v>488570</v>
       </c>
       <c r="R82" t="n">
-        <v>7144909</v>
+        <v>7144960</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9091,9 +9119,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9108,22 +9146,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716441</v>
+        <v>129716445</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9155,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488921</v>
+        <v>488685</v>
       </c>
       <c r="R83" t="n">
-        <v>7144886</v>
+        <v>7144909</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9217,10 +9255,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129716422</v>
+        <v>129716441</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9252,10 +9290,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488767</v>
+        <v>488921</v>
       </c>
       <c r="R84" t="n">
-        <v>7144853</v>
+        <v>7144886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9314,10 +9352,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129727769</v>
+        <v>129716422</v>
       </c>
       <c r="B85" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9325,41 +9363,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488758</v>
+        <v>488767</v>
       </c>
       <c r="R85" t="n">
-        <v>7144774</v>
+        <v>7144853</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9394,55 +9425,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9452,7 +9452,7 @@
         <v>129727767</v>
       </c>
       <c r="B86" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727795</v>
+        <v>129726773</v>
       </c>
       <c r="B87" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488737</v>
+        <v>489020</v>
       </c>
       <c r="R87" t="n">
-        <v>7144797</v>
+        <v>7144867</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,14 +9652,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På en levande gammal gran.</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,22 +9679,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727794</v>
+        <v>129727795</v>
       </c>
       <c r="B88" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9721,10 +9726,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488763</v>
+        <v>488737</v>
       </c>
       <c r="R88" t="n">
-        <v>7144775</v>
+        <v>7144797</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9761,7 +9766,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9788,10 +9793,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727960</v>
+        <v>129727794</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9819,14 +9824,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488374</v>
+        <v>488763</v>
       </c>
       <c r="R89" t="n">
-        <v>7144949</v>
+        <v>7144775</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9863,7 +9868,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9878,22 +9883,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727783</v>
+        <v>129727960</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9921,14 +9926,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488709</v>
+        <v>488374</v>
       </c>
       <c r="R90" t="n">
-        <v>7144911</v>
+        <v>7144949</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9965,7 +9970,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9980,22 +9985,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726773</v>
+        <v>129727783</v>
       </c>
       <c r="B91" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10003,34 +10008,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489020</v>
+        <v>488709</v>
       </c>
       <c r="R91" t="n">
-        <v>7144867</v>
+        <v>7144911</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10060,19 +10065,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10087,12 +10087,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10102,7 +10102,7 @@
         <v>129726769</v>
       </c>
       <c r="B92" t="n">
-        <v>75060</v>
+        <v>75065</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R93" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,19 +10289,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>91584</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10339,34 +10329,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R94" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10396,9 +10386,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,44 +10413,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730462</v>
+        <v>129730439</v>
       </c>
       <c r="B95" t="n">
-        <v>92306</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489017</v>
+        <v>488746</v>
       </c>
       <c r="R95" t="n">
-        <v>7144821</v>
+        <v>7144786</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,6 +10496,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10522,32 +10527,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>92311</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R96" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10593,11 +10598,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10729,7 +10729,7 @@
         <v>129730460</v>
       </c>
       <c r="B98" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>129730457</v>
       </c>
       <c r="B99" t="n">
-        <v>91959</v>
+        <v>91964</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10920,10 +10920,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730473</v>
+        <v>129730449</v>
       </c>
       <c r="B100" t="n">
-        <v>91584</v>
+        <v>80187</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10931,21 +10931,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489028</v>
+        <v>488414</v>
       </c>
       <c r="R100" t="n">
-        <v>7144803</v>
+        <v>7144940</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,10 +11017,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730474</v>
+        <v>129730473</v>
       </c>
       <c r="B101" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488676</v>
+        <v>489028</v>
       </c>
       <c r="R101" t="n">
-        <v>7144870</v>
+        <v>7144803</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730449</v>
+        <v>129730474</v>
       </c>
       <c r="B102" t="n">
-        <v>80182</v>
+        <v>91589</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488414</v>
+        <v>488676</v>
       </c>
       <c r="R102" t="n">
-        <v>7144940</v>
+        <v>7144870</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11214,7 +11214,7 @@
         <v>129730465</v>
       </c>
       <c r="B103" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730451</v>
+        <v>129730461</v>
       </c>
       <c r="B104" t="n">
-        <v>80181</v>
+        <v>91593</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488709</v>
+        <v>488464</v>
       </c>
       <c r="R104" t="n">
-        <v>7144786</v>
+        <v>7144953</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730461</v>
+        <v>129730451</v>
       </c>
       <c r="B105" t="n">
-        <v>91588</v>
+        <v>80186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488464</v>
+        <v>488709</v>
       </c>
       <c r="R105" t="n">
-        <v>7144953</v>
+        <v>7144786</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11806,7 +11806,7 @@
         <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>129730452</v>
       </c>
       <c r="B110" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129730448</v>
       </c>
       <c r="B112" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730467</v>
+        <v>129730464</v>
       </c>
       <c r="B113" t="n">
-        <v>83050</v>
+        <v>57896</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488737</v>
+        <v>488362</v>
       </c>
       <c r="R113" t="n">
-        <v>7144811</v>
+        <v>7144944</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,6 +12272,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12298,10 +12303,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730464</v>
+        <v>129730467</v>
       </c>
       <c r="B114" t="n">
-        <v>57896</v>
+        <v>83055</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12309,21 +12314,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12333,10 +12338,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488362</v>
+        <v>488737</v>
       </c>
       <c r="R114" t="n">
-        <v>7144944</v>
+        <v>7144811</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12369,11 +12374,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12403,7 +12403,7 @@
         <v>129730470</v>
       </c>
       <c r="B115" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>129730468</v>
       </c>
       <c r="B117" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>129730458</v>
       </c>
       <c r="B118" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>129730471</v>
       </c>
       <c r="B119" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>129730476</v>
       </c>
       <c r="B120" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>129730456</v>
       </c>
       <c r="B121" t="n">
-        <v>91959</v>
+        <v>91964</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>129730459</v>
       </c>
       <c r="B122" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>129730478</v>
       </c>
       <c r="B123" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>129730446</v>
       </c>
       <c r="B125" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>129730447</v>
       </c>
       <c r="B126" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B127" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R127" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B128" t="n">
-        <v>79076</v>
+        <v>83055</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R128" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13762,7 +13762,7 @@
         <v>129730472</v>
       </c>
       <c r="B129" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>129730475</v>
       </c>
       <c r="B130" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129716427</v>
+        <v>129726758</v>
       </c>
       <c r="B5" t="n">
-        <v>83042</v>
+        <v>82916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +1040,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488400</v>
+        <v>488417</v>
       </c>
       <c r="R5" t="n">
-        <v>7144977</v>
+        <v>7145102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,9 +1097,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,57 +1124,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726758</v>
+        <v>129727766</v>
       </c>
       <c r="B6" t="n">
-        <v>82916</v>
+        <v>80215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488417</v>
+        <v>488676</v>
       </c>
       <c r="R6" t="n">
-        <v>7145102</v>
+        <v>7144814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,19 +1211,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,70 +1227,89 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727766</v>
+        <v>129727797</v>
       </c>
       <c r="B7" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488676</v>
+        <v>488482</v>
       </c>
       <c r="R7" t="n">
-        <v>7144814</v>
+        <v>7144891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1346,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,34 +1355,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1368,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129727797</v>
+        <v>129716427</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>83042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1403,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488482</v>
+        <v>488400</v>
       </c>
       <c r="R8" t="n">
-        <v>7144891</v>
+        <v>7144977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,11 +1446,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,12 +1458,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1664,52 +1664,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727765</v>
+        <v>129727776</v>
       </c>
       <c r="B11" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488701</v>
+        <v>488425</v>
       </c>
       <c r="R11" t="n">
-        <v>7144801</v>
+        <v>7145015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,34 +1748,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1799,7 +1766,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727776</v>
+        <v>129726761</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1830,14 +1797,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488425</v>
+        <v>488516</v>
       </c>
       <c r="R12" t="n">
-        <v>7145015</v>
+        <v>7145014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,14 +1834,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,19 +1861,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726761</v>
+        <v>129727801</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -1932,14 +1904,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488516</v>
+        <v>488339</v>
       </c>
       <c r="R13" t="n">
-        <v>7145014</v>
+        <v>7144937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,19 +1941,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,19 +1963,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727801</v>
+        <v>129727782</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -2043,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488339</v>
+        <v>488694</v>
       </c>
       <c r="R14" t="n">
-        <v>7144937</v>
+        <v>7144925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,7 +2050,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727782</v>
+        <v>129727796</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2145,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488694</v>
+        <v>488507</v>
       </c>
       <c r="R15" t="n">
-        <v>7144925</v>
+        <v>7144870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2152,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727796</v>
+        <v>129726781</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,34 +2190,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488507</v>
+        <v>488365</v>
       </c>
       <c r="R16" t="n">
-        <v>7144870</v>
+        <v>7144983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,14 +2247,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,57 +2274,64 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726781</v>
+        <v>129727765</v>
       </c>
       <c r="B17" t="n">
-        <v>78094</v>
+        <v>80215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488365</v>
+        <v>488701</v>
       </c>
       <c r="R17" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,19 +2361,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,18 +2377,44 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726774</v>
+        <v>129727768</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,34 +2626,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489025</v>
+        <v>488790</v>
       </c>
       <c r="R20" t="n">
-        <v>7144875</v>
+        <v>7144786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,19 +2695,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:52</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i en grov gammal gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2706,26 +2713,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129727768</v>
+        <v>129726774</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,46 +2765,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488790</v>
+        <v>489025</v>
       </c>
       <c r="R21" t="n">
-        <v>7144786</v>
+        <v>7144875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,14 +2822,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i en grov gammal gran.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,41 +2845,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727786</v>
+        <v>129727772</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,34 +3387,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489035</v>
+        <v>488470</v>
       </c>
       <c r="R27" t="n">
-        <v>7144832</v>
+        <v>7144960</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,7 +3458,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,8 +3467,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3478,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B28" t="n">
-        <v>80187</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,41 +3522,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R28" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3558,65 +3589,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,39 +3624,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R29" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,6 +3686,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3703,12 +3703,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726760</v>
+        <v>129726763</v>
       </c>
       <c r="B31" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,21 +3827,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488426</v>
+        <v>488626</v>
       </c>
       <c r="R31" t="n">
-        <v>7145052</v>
+        <v>7145010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3923,7 +3923,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726763</v>
+        <v>129716436</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3954,14 +3954,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488626</v>
+        <v>489031</v>
       </c>
       <c r="R32" t="n">
-        <v>7145010</v>
+        <v>7144903</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,19 +3991,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,19 +4008,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129716436</v>
+        <v>129727792</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -4065,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489031</v>
+        <v>488815</v>
       </c>
       <c r="R33" t="n">
-        <v>7144903</v>
+        <v>7144788</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4103,6 +4093,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4115,22 +4110,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727792</v>
+        <v>129726760</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>88992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,34 +4133,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488815</v>
+        <v>488426</v>
       </c>
       <c r="R34" t="n">
-        <v>7144788</v>
+        <v>7145052</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4195,14 +4190,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,12 +4217,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129727802</v>
+        <v>129726784</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>83042</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,34 +4343,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488268</v>
+        <v>488335</v>
       </c>
       <c r="R36" t="n">
-        <v>7145078</v>
+        <v>7144978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,14 +4400,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4422,12 +4427,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4541,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726784</v>
+        <v>129727802</v>
       </c>
       <c r="B38" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4552,34 +4557,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488335</v>
+        <v>488268</v>
       </c>
       <c r="R38" t="n">
-        <v>7144978</v>
+        <v>7145078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,19 +4614,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,12 +4636,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726782</v>
+        <v>129727959</v>
       </c>
       <c r="B41" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,34 +4863,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488365</v>
+        <v>488762</v>
       </c>
       <c r="R41" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,19 +4920,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4947,19 +4937,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129727959</v>
+        <v>129727788</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -4990,14 +4980,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488762</v>
+        <v>488989</v>
       </c>
       <c r="R42" t="n">
-        <v>7144801</v>
+        <v>7144826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,6 +5022,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5044,22 +5039,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129727788</v>
+        <v>129726782</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5067,34 +5062,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488989</v>
+        <v>488365</v>
       </c>
       <c r="R43" t="n">
-        <v>7144826</v>
+        <v>7144983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,14 +5119,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,12 +5146,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6137,45 +6137,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129727953</v>
+        <v>129716431</v>
       </c>
       <c r="B53" t="n">
-        <v>91975</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488400</v>
+        <v>488426</v>
       </c>
       <c r="R53" t="n">
-        <v>7144968</v>
+        <v>7145034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129716447</v>
+        <v>129727780</v>
       </c>
       <c r="B54" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488731</v>
+        <v>488542</v>
       </c>
       <c r="R54" t="n">
-        <v>7144891</v>
+        <v>7144969</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,6 +6307,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6319,57 +6324,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129716431</v>
+        <v>129727953</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>91975</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488426</v>
+        <v>488400</v>
       </c>
       <c r="R55" t="n">
-        <v>7145034</v>
+        <v>7144968</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,22 +6421,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6439,21 +6444,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6463,10 +6468,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R56" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6501,11 +6506,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,12 +6518,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6734,30 +6734,34 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716430</v>
+        <v>129716423</v>
       </c>
       <c r="B59" t="n">
-        <v>91613</v>
+        <v>92311</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6765,10 +6769,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488835</v>
+        <v>488296</v>
       </c>
       <c r="R59" t="n">
-        <v>7144824</v>
+        <v>7145038</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6827,7 +6831,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716440</v>
+        <v>129716430</v>
       </c>
       <c r="B60" t="n">
         <v>91613</v>
@@ -6858,10 +6862,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488547</v>
+        <v>488835</v>
       </c>
       <c r="R60" t="n">
-        <v>7144971</v>
+        <v>7144824</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6920,34 +6924,30 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716428</v>
+        <v>129716440</v>
       </c>
       <c r="B61" t="n">
-        <v>92311</v>
+        <v>91613</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>489052</v>
+        <v>488547</v>
       </c>
       <c r="R61" t="n">
-        <v>7144873</v>
+        <v>7144971</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7017,30 +7017,34 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129716442</v>
+        <v>129716428</v>
       </c>
       <c r="B62" t="n">
-        <v>91613</v>
+        <v>92311</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7048,10 +7052,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488630</v>
+        <v>489052</v>
       </c>
       <c r="R62" t="n">
-        <v>7145015</v>
+        <v>7144873</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7110,34 +7114,30 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129716423</v>
+        <v>129716442</v>
       </c>
       <c r="B63" t="n">
-        <v>92311</v>
+        <v>91613</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488296</v>
+        <v>488630</v>
       </c>
       <c r="R63" t="n">
-        <v>7145038</v>
+        <v>7145015</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726764</v>
+        <v>129727793</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7238,14 +7238,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488646</v>
+        <v>488795</v>
       </c>
       <c r="R64" t="n">
-        <v>7144947</v>
+        <v>7144792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,19 +7275,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:36</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7302,19 +7297,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727793</v>
+        <v>129727798</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7349,10 +7344,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488795</v>
+        <v>488442</v>
       </c>
       <c r="R65" t="n">
-        <v>7144792</v>
+        <v>7145001</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7389,7 +7384,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7416,7 +7411,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129727798</v>
+        <v>129726764</v>
       </c>
       <c r="B66" t="n">
         <v>79081</v>
@@ -7447,14 +7442,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488442</v>
+        <v>488646</v>
       </c>
       <c r="R66" t="n">
-        <v>7145001</v>
+        <v>7144947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7484,14 +7479,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal flerskiktad granskog.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,12 +7506,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -9051,45 +9051,52 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129726777</v>
+        <v>129727767</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488570</v>
+        <v>488658</v>
       </c>
       <c r="R82" t="n">
-        <v>7144960</v>
+        <v>7144806</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9119,19 +9126,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9140,25 +9142,51 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716445</v>
+        <v>129726777</v>
       </c>
       <c r="B83" t="n">
         <v>79081</v>
@@ -9189,14 +9217,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488685</v>
+        <v>488570</v>
       </c>
       <c r="R83" t="n">
-        <v>7144909</v>
+        <v>7144960</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9226,9 +9254,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9243,12 +9281,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9449,52 +9487,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727767</v>
+        <v>129716445</v>
       </c>
       <c r="B86" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488658</v>
+        <v>488685</v>
       </c>
       <c r="R86" t="n">
-        <v>7144806</v>
+        <v>7144909</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9529,65 +9560,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726773</v>
+        <v>129727795</v>
       </c>
       <c r="B87" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489020</v>
+        <v>488737</v>
       </c>
       <c r="R87" t="n">
-        <v>7144867</v>
+        <v>7144797</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,19 +9652,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9679,19 +9674,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727795</v>
+        <v>129727794</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -9726,10 +9721,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488737</v>
+        <v>488763</v>
       </c>
       <c r="R88" t="n">
-        <v>7144797</v>
+        <v>7144775</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9766,7 +9761,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en levande gammal gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9793,7 +9788,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727794</v>
+        <v>129727960</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -9824,14 +9819,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488763</v>
+        <v>488374</v>
       </c>
       <c r="R89" t="n">
-        <v>7144775</v>
+        <v>7144949</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9868,7 +9863,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9883,19 +9878,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727960</v>
+        <v>129727783</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9926,14 +9921,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488374</v>
+        <v>488709</v>
       </c>
       <c r="R90" t="n">
-        <v>7144949</v>
+        <v>7144911</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9965,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9985,57 +9980,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727783</v>
+        <v>129726769</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>75065</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488709</v>
+        <v>489064</v>
       </c>
       <c r="R91" t="n">
-        <v>7144911</v>
+        <v>7144843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10065,14 +10060,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På levande gran i gammal granskog.</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,48 +10083,63 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726769</v>
+        <v>129726773</v>
       </c>
       <c r="B92" t="n">
-        <v>75065</v>
+        <v>91593</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10134,10 +10149,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489064</v>
+        <v>489020</v>
       </c>
       <c r="R92" t="n">
-        <v>7144843</v>
+        <v>7144867</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10169,7 +10184,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10179,7 +10194,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10190,21 +10205,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B93" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R93" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,9 +10289,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10306,22 +10316,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10329,34 +10339,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R94" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10386,19 +10396,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,44 +10413,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>92311</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R95" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,32 +10522,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730462</v>
+        <v>129730439</v>
       </c>
       <c r="B96" t="n">
-        <v>92311</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489017</v>
+        <v>488746</v>
       </c>
       <c r="R96" t="n">
-        <v>7144821</v>
+        <v>7144786</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10598,6 +10593,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730461</v>
+        <v>129730451</v>
       </c>
       <c r="B104" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488464</v>
+        <v>488709</v>
       </c>
       <c r="R104" t="n">
-        <v>7144953</v>
+        <v>7144786</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730451</v>
+        <v>129730461</v>
       </c>
       <c r="B105" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488709</v>
+        <v>488464</v>
       </c>
       <c r="R105" t="n">
-        <v>7144786</v>
+        <v>7144953</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B109" t="n">
-        <v>91607</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R109" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,6 +11874,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11900,10 +11905,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>91607</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11911,21 +11916,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11935,10 +11940,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R110" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11971,11 +11976,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12201,10 +12201,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730464</v>
+        <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>57896</v>
+        <v>83055</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488362</v>
+        <v>488737</v>
       </c>
       <c r="R113" t="n">
-        <v>7144944</v>
+        <v>7144811</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,11 +12272,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12303,10 +12298,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730467</v>
+        <v>129730464</v>
       </c>
       <c r="B114" t="n">
-        <v>83055</v>
+        <v>57896</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12314,21 +12309,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12338,10 +12333,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488737</v>
+        <v>488362</v>
       </c>
       <c r="R114" t="n">
-        <v>7144811</v>
+        <v>7144944</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12374,6 +12369,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12696,10 +12696,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730458</v>
+        <v>129730471</v>
       </c>
       <c r="B118" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12707,21 +12707,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>489058</v>
+        <v>488625</v>
       </c>
       <c r="R118" t="n">
-        <v>7144802</v>
+        <v>7144878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12793,10 +12793,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730471</v>
+        <v>129730458</v>
       </c>
       <c r="B119" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12804,21 +12804,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12828,10 +12828,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488625</v>
+        <v>489058</v>
       </c>
       <c r="R119" t="n">
-        <v>7144878</v>
+        <v>7144802</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12987,34 +12987,30 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730456</v>
+        <v>129730478</v>
       </c>
       <c r="B121" t="n">
-        <v>91964</v>
+        <v>91613</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13022,10 +13018,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488467</v>
+        <v>488436</v>
       </c>
       <c r="R121" t="n">
-        <v>7144951</v>
+        <v>7144967</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13084,32 +13080,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730459</v>
+        <v>129730456</v>
       </c>
       <c r="B122" t="n">
-        <v>91593</v>
+        <v>91964</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13119,10 +13115,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488604</v>
+        <v>488467</v>
       </c>
       <c r="R122" t="n">
-        <v>7144985</v>
+        <v>7144951</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13181,10 +13177,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730478</v>
+        <v>129730459</v>
       </c>
       <c r="B123" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13192,19 +13188,23 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488436</v>
+        <v>488604</v>
       </c>
       <c r="R123" t="n">
-        <v>7144967</v>
+        <v>7144985</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B124" t="n">
-        <v>83050</v>
+        <v>80215</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R124" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B125" t="n">
-        <v>80215</v>
+        <v>83050</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R125" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13759,32 +13759,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730472</v>
+        <v>129730440</v>
       </c>
       <c r="B129" t="n">
-        <v>91589</v>
+        <v>56926</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488622</v>
+        <v>489134</v>
       </c>
       <c r="R129" t="n">
-        <v>7144899</v>
+        <v>7144763</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13830,6 +13830,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13856,7 +13861,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730475</v>
+        <v>129730472</v>
       </c>
       <c r="B130" t="n">
         <v>91589</v>
@@ -13891,10 +13896,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488459</v>
+        <v>488622</v>
       </c>
       <c r="R130" t="n">
-        <v>7144958</v>
+        <v>7144899</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13953,32 +13958,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730440</v>
+        <v>129730475</v>
       </c>
       <c r="B131" t="n">
-        <v>56926</v>
+        <v>91589</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13988,10 +13993,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489134</v>
+        <v>488459</v>
       </c>
       <c r="R131" t="n">
-        <v>7144763</v>
+        <v>7144958</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14024,11 +14029,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129727955</v>
+        <v>129716427</v>
       </c>
       <c r="B2" t="n">
-        <v>91589</v>
+        <v>83042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489154</v>
+        <v>488400</v>
       </c>
       <c r="R2" t="n">
-        <v>7144751</v>
+        <v>7144977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727773</v>
+        <v>129727955</v>
       </c>
       <c r="B3" t="n">
         <v>91589</v>
@@ -801,23 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488610</v>
+        <v>489154</v>
       </c>
       <c r="R3" t="n">
-        <v>7144833</v>
+        <v>7144751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,65 +845,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726770</v>
+        <v>129727773</v>
       </c>
       <c r="B4" t="n">
-        <v>80187</v>
+        <v>91589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489064</v>
+        <v>488610</v>
       </c>
       <c r="R4" t="n">
-        <v>7144843</v>
+        <v>7144833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,19 +944,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,43 +960,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726758</v>
+        <v>129727797</v>
       </c>
       <c r="B5" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488417</v>
+        <v>488482</v>
       </c>
       <c r="R5" t="n">
-        <v>7145102</v>
+        <v>7144891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,19 +1072,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,64 +1094,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129727766</v>
+        <v>129726770</v>
       </c>
       <c r="B6" t="n">
-        <v>80215</v>
+        <v>80187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488676</v>
+        <v>489064</v>
       </c>
       <c r="R6" t="n">
-        <v>7144814</v>
+        <v>7144843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,14 +1174,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,54 +1195,43 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727797</v>
+        <v>129726758</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,34 +1239,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488482</v>
+        <v>488417</v>
       </c>
       <c r="R7" t="n">
-        <v>7144891</v>
+        <v>7145102</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,14 +1296,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,57 +1323,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129716427</v>
+        <v>129727766</v>
       </c>
       <c r="B8" t="n">
-        <v>83042</v>
+        <v>80215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488400</v>
+        <v>488676</v>
       </c>
       <c r="R8" t="n">
-        <v>7144977</v>
+        <v>7144814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,34 +1415,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129727952</v>
+        <v>129716439</v>
       </c>
       <c r="B9" t="n">
-        <v>91891</v>
+        <v>83042</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,34 +1481,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488401</v>
+        <v>488354</v>
       </c>
       <c r="R9" t="n">
-        <v>7144967</v>
+        <v>7144989</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,22 +1555,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129716439</v>
+        <v>129727952</v>
       </c>
       <c r="B10" t="n">
-        <v>83042</v>
+        <v>91891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488354</v>
+        <v>488401</v>
       </c>
       <c r="R10" t="n">
-        <v>7144989</v>
+        <v>7144967</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,12 +1652,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2077,45 +2077,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727796</v>
+        <v>129727765</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488507</v>
+        <v>488701</v>
       </c>
       <c r="R15" t="n">
-        <v>7144870</v>
+        <v>7144801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2159,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,8 +2168,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2286,52 +2319,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727765</v>
+        <v>129727796</v>
       </c>
       <c r="B17" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488701</v>
+        <v>488507</v>
       </c>
       <c r="R17" t="n">
-        <v>7144801</v>
+        <v>7144870</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2368,7 +2394,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,34 +2403,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727947</v>
+        <v>129716443</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2432,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488803</v>
+        <v>488470</v>
       </c>
       <c r="R18" t="n">
-        <v>7144779</v>
+        <v>7144975</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,22 +2506,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129716443</v>
+        <v>129727768</v>
       </c>
       <c r="B19" t="n">
-        <v>91589</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,34 +2529,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488470</v>
+        <v>488790</v>
       </c>
       <c r="R19" t="n">
-        <v>7144975</v>
+        <v>7144786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,6 +2603,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i en grov gammal gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2599,26 +2616,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129727768</v>
+        <v>129727947</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,46 +2668,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488790</v>
+        <v>488803</v>
       </c>
       <c r="R20" t="n">
-        <v>7144786</v>
+        <v>7144779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2700,11 +2730,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i en grov gammal gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2713,41 +2738,16 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B27" t="n">
-        <v>80187</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,41 +3387,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R27" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,65 +3454,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129716435</v>
+        <v>129727772</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>80187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,39 +3489,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488832</v>
+        <v>488470</v>
       </c>
       <c r="R28" t="n">
-        <v>7144827</v>
+        <v>7144960</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,24 +3558,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129727945</v>
+        <v>129726760</v>
       </c>
       <c r="B30" t="n">
-        <v>91607</v>
+        <v>88992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489010</v>
+        <v>488426</v>
       </c>
       <c r="R30" t="n">
-        <v>7144808</v>
+        <v>7145052</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,40 +3783,49 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726763</v>
+        <v>129727945</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91607</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,34 +3833,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488626</v>
+        <v>489010</v>
       </c>
       <c r="R31" t="n">
-        <v>7145010</v>
+        <v>7144808</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3884,46 +3893,37 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129716436</v>
+        <v>129727792</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489031</v>
+        <v>488815</v>
       </c>
       <c r="R32" t="n">
-        <v>7144903</v>
+        <v>7144788</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,6 +3996,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4008,19 +4013,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129727792</v>
+        <v>129726763</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -4051,14 +4056,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488815</v>
+        <v>488626</v>
       </c>
       <c r="R33" t="n">
-        <v>7144788</v>
+        <v>7145010</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4088,14 +4093,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,22 +4120,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726760</v>
+        <v>129716436</v>
       </c>
       <c r="B34" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,34 +4143,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488426</v>
+        <v>489031</v>
       </c>
       <c r="R34" t="n">
-        <v>7145052</v>
+        <v>7144903</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,19 +4200,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,22 +4217,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726771</v>
+        <v>129726765</v>
       </c>
       <c r="B35" t="n">
-        <v>91613</v>
+        <v>82916</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,19 +4240,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4260,10 +4264,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489056</v>
+        <v>488725</v>
       </c>
       <c r="R35" t="n">
-        <v>7144853</v>
+        <v>7144925</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,7 +4299,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4309,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726784</v>
+        <v>129727802</v>
       </c>
       <c r="B36" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,34 +4347,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488335</v>
+        <v>488268</v>
       </c>
       <c r="R36" t="n">
-        <v>7144978</v>
+        <v>7145078</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,19 +4404,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,22 +4426,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726765</v>
+        <v>129726771</v>
       </c>
       <c r="B37" t="n">
-        <v>82916</v>
+        <v>91613</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,23 +4449,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4474,10 +4469,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488725</v>
+        <v>489056</v>
       </c>
       <c r="R37" t="n">
-        <v>7144925</v>
+        <v>7144853</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4504,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4514,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,10 +4541,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129727802</v>
+        <v>129726784</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>83042</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,34 +4552,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488268</v>
+        <v>488335</v>
       </c>
       <c r="R38" t="n">
-        <v>7145078</v>
+        <v>7144978</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,14 +4609,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,22 +4636,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129716425</v>
+        <v>129726782</v>
       </c>
       <c r="B39" t="n">
-        <v>88992</v>
+        <v>83050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488829</v>
+        <v>488365</v>
       </c>
       <c r="R39" t="n">
-        <v>7144835</v>
+        <v>7144983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,9 +4716,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4733,22 +4743,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726780</v>
+        <v>129716425</v>
       </c>
       <c r="B40" t="n">
-        <v>83055</v>
+        <v>88992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4756,34 +4766,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488414</v>
+        <v>488829</v>
       </c>
       <c r="R40" t="n">
-        <v>7144975</v>
+        <v>7144835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4813,19 +4823,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4840,22 +4840,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129727959</v>
+        <v>129726780</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,34 +4863,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488762</v>
+        <v>488414</v>
       </c>
       <c r="R41" t="n">
-        <v>7144801</v>
+        <v>7144975</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,9 +4920,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4937,19 +4947,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129727788</v>
+        <v>129727959</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -4980,14 +4990,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488989</v>
+        <v>488762</v>
       </c>
       <c r="R42" t="n">
-        <v>7144826</v>
+        <v>7144801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,11 +5032,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5039,22 +5044,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726782</v>
+        <v>129727788</v>
       </c>
       <c r="B43" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,34 +5067,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488365</v>
+        <v>488989</v>
       </c>
       <c r="R43" t="n">
-        <v>7144983</v>
+        <v>7144826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5119,19 +5124,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,12 +5146,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727948</v>
+        <v>129727770</v>
       </c>
       <c r="B45" t="n">
-        <v>91593</v>
+        <v>80187</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5304,34 +5304,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488739</v>
+        <v>488674</v>
       </c>
       <c r="R45" t="n">
-        <v>7144803</v>
+        <v>7144814</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5366,34 +5373,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727770</v>
+        <v>129727948</v>
       </c>
       <c r="B46" t="n">
-        <v>80187</v>
+        <v>91593</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,41 +5439,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488674</v>
+        <v>488739</v>
       </c>
       <c r="R46" t="n">
-        <v>7144814</v>
+        <v>7144803</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5470,62 +5501,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727781</v>
+        <v>129727785</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488586</v>
+        <v>488865</v>
       </c>
       <c r="R47" t="n">
-        <v>7144955</v>
+        <v>7144860</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5627,7 +5627,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727785</v>
+        <v>129727799</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488865</v>
+        <v>488408</v>
       </c>
       <c r="R48" t="n">
-        <v>7144860</v>
+        <v>7144970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5729,7 +5729,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727799</v>
+        <v>129726775</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5760,14 +5760,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488408</v>
+        <v>488851</v>
       </c>
       <c r="R49" t="n">
-        <v>7144970</v>
+        <v>7144825</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5797,14 +5797,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,22 +5824,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129716437</v>
+        <v>129727777</v>
       </c>
       <c r="B50" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5842,21 +5847,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5866,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488533</v>
+        <v>488483</v>
       </c>
       <c r="R50" t="n">
-        <v>7144953</v>
+        <v>7144992</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,6 +5909,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5916,22 +5926,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129726775</v>
+        <v>129716437</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5939,34 +5949,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488851</v>
+        <v>488533</v>
       </c>
       <c r="R51" t="n">
-        <v>7144825</v>
+        <v>7144953</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,19 +6006,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6023,19 +6023,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727777</v>
+        <v>129727781</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488483</v>
+        <v>488586</v>
       </c>
       <c r="R52" t="n">
-        <v>7144992</v>
+        <v>7144955</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6137,45 +6137,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716431</v>
+        <v>129727953</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>91975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488426</v>
+        <v>488400</v>
       </c>
       <c r="R53" t="n">
-        <v>7145034</v>
+        <v>7144968</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R54" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,11 +6307,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6324,57 +6319,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727953</v>
+        <v>129727780</v>
       </c>
       <c r="B55" t="n">
-        <v>91975</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488400</v>
+        <v>488542</v>
       </c>
       <c r="R55" t="n">
-        <v>7144968</v>
+        <v>7144969</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6409,6 +6404,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6421,22 +6421,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716447</v>
+        <v>129716431</v>
       </c>
       <c r="B56" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488731</v>
+        <v>488426</v>
       </c>
       <c r="R56" t="n">
-        <v>7144891</v>
+        <v>7145034</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6530,32 +6530,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727791</v>
+        <v>129716428</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>92311</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488907</v>
+        <v>489052</v>
       </c>
       <c r="R57" t="n">
-        <v>7144779</v>
+        <v>7144873</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6603,11 +6603,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6620,44 +6615,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129727800</v>
+        <v>129716423</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>92311</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6667,10 +6662,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488375</v>
+        <v>488296</v>
       </c>
       <c r="R58" t="n">
-        <v>7144951</v>
+        <v>7145038</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,11 +6700,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6722,46 +6712,42 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716423</v>
+        <v>129716430</v>
       </c>
       <c r="B59" t="n">
-        <v>92311</v>
+        <v>91613</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6769,10 +6755,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488296</v>
+        <v>488835</v>
       </c>
       <c r="R59" t="n">
-        <v>7145038</v>
+        <v>7144824</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6831,7 +6817,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716430</v>
+        <v>129716440</v>
       </c>
       <c r="B60" t="n">
         <v>91613</v>
@@ -6862,10 +6848,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488835</v>
+        <v>488547</v>
       </c>
       <c r="R60" t="n">
-        <v>7144824</v>
+        <v>7144971</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6924,7 +6910,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716440</v>
+        <v>129716442</v>
       </c>
       <c r="B61" t="n">
         <v>91613</v>
@@ -6955,10 +6941,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488547</v>
+        <v>488630</v>
       </c>
       <c r="R61" t="n">
-        <v>7144971</v>
+        <v>7145015</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7017,32 +7003,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129716428</v>
+        <v>129727791</v>
       </c>
       <c r="B62" t="n">
-        <v>92311</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7052,10 +7038,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489052</v>
+        <v>488907</v>
       </c>
       <c r="R62" t="n">
-        <v>7144873</v>
+        <v>7144779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7090,6 +7076,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7102,22 +7093,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129716442</v>
+        <v>129727800</v>
       </c>
       <c r="B63" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7125,19 +7116,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7145,10 +7140,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488630</v>
+        <v>488375</v>
       </c>
       <c r="R63" t="n">
-        <v>7145015</v>
+        <v>7144951</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7183,6 +7178,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7195,19 +7195,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129727793</v>
+        <v>129726764</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7238,14 +7238,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488795</v>
+        <v>488646</v>
       </c>
       <c r="R64" t="n">
-        <v>7144792</v>
+        <v>7144947</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,14 +7275,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7297,19 +7302,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727798</v>
+        <v>129727793</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7344,10 +7349,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488442</v>
+        <v>488795</v>
       </c>
       <c r="R65" t="n">
-        <v>7145001</v>
+        <v>7144792</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7384,7 +7389,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På flera granar i gammal flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,7 +7416,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726764</v>
+        <v>129727798</v>
       </c>
       <c r="B66" t="n">
         <v>79081</v>
@@ -7442,14 +7447,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488646</v>
+        <v>488442</v>
       </c>
       <c r="R66" t="n">
-        <v>7144947</v>
+        <v>7145001</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7479,19 +7484,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:36</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,19 +7506,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129716433</v>
+        <v>129727790</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488359</v>
+        <v>488911</v>
       </c>
       <c r="R67" t="n">
-        <v>7144987</v>
+        <v>7144836</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7591,6 +7591,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7603,19 +7608,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129727790</v>
+        <v>129716432</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7650,10 +7655,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488911</v>
+        <v>489065</v>
       </c>
       <c r="R68" t="n">
-        <v>7144836</v>
+        <v>7144852</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7690,7 +7695,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7705,19 +7710,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129716432</v>
+        <v>129727958</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7748,14 +7753,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489065</v>
+        <v>488796</v>
       </c>
       <c r="R69" t="n">
-        <v>7144852</v>
+        <v>7144792</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7790,11 +7795,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7807,19 +7807,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129727787</v>
+        <v>129716433</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7854,10 +7854,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489024</v>
+        <v>488359</v>
       </c>
       <c r="R70" t="n">
-        <v>7144841</v>
+        <v>7144987</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7892,11 +7892,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7909,19 +7904,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129727958</v>
+        <v>129727787</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -7952,14 +7947,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488796</v>
+        <v>489024</v>
       </c>
       <c r="R71" t="n">
-        <v>7144792</v>
+        <v>7144841</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7994,6 +7989,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8006,19 +8006,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129726778</v>
+        <v>129716429</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -8049,14 +8049,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488522</v>
+        <v>488440</v>
       </c>
       <c r="R72" t="n">
-        <v>7144974</v>
+        <v>7144976</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,19 +8086,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8113,22 +8103,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129716429</v>
+        <v>129727951</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>91891</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8136,34 +8126,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488440</v>
+        <v>489112</v>
       </c>
       <c r="R73" t="n">
-        <v>7144976</v>
+        <v>7144780</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8210,22 +8200,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129727778</v>
+        <v>129727954</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8233,34 +8223,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488513</v>
+        <v>489143</v>
       </c>
       <c r="R74" t="n">
-        <v>7144973</v>
+        <v>7144773</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8295,11 +8285,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8312,19 +8297,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726779</v>
+        <v>129726778</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8359,10 +8344,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488452</v>
+        <v>488522</v>
       </c>
       <c r="R75" t="n">
-        <v>7144979</v>
+        <v>7144974</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8394,7 +8379,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8404,7 +8389,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8431,10 +8416,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129727951</v>
+        <v>129727778</v>
       </c>
       <c r="B76" t="n">
-        <v>91891</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8442,34 +8427,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>489112</v>
+        <v>488513</v>
       </c>
       <c r="R76" t="n">
-        <v>7144780</v>
+        <v>7144973</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8504,6 +8489,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8516,22 +8506,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129727954</v>
+        <v>129726779</v>
       </c>
       <c r="B77" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8539,34 +8529,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489143</v>
+        <v>488452</v>
       </c>
       <c r="R77" t="n">
-        <v>7144773</v>
+        <v>7144979</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8596,9 +8586,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129716434</v>
+        <v>129726777</v>
       </c>
       <c r="B79" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,34 +8733,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488618</v>
+        <v>488570</v>
       </c>
       <c r="R79" t="n">
-        <v>7144922</v>
+        <v>7144960</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8790,9 +8790,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8807,22 +8817,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129727769</v>
+        <v>129716445</v>
       </c>
       <c r="B80" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8830,41 +8840,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488758</v>
+        <v>488685</v>
       </c>
       <c r="R80" t="n">
-        <v>7144774</v>
+        <v>7144909</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8899,62 +8902,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727957</v>
+        <v>129716434</v>
       </c>
       <c r="B81" t="n">
         <v>91589</v>
@@ -8985,14 +8957,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488618</v>
       </c>
       <c r="R81" t="n">
-        <v>7144844</v>
+        <v>7144922</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9039,64 +9011,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727767</v>
+        <v>129727957</v>
       </c>
       <c r="B82" t="n">
-        <v>80215</v>
+        <v>91589</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488658</v>
+        <v>488591</v>
       </c>
       <c r="R82" t="n">
-        <v>7144806</v>
+        <v>7144844</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,65 +9096,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726777</v>
+        <v>129727769</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9197,34 +9131,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488570</v>
+        <v>488758</v>
       </c>
       <c r="R83" t="n">
-        <v>7144960</v>
+        <v>7144774</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9254,19 +9195,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9275,18 +9211,44 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9487,45 +9449,52 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129716445</v>
+        <v>129727767</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488685</v>
+        <v>488658</v>
       </c>
       <c r="R86" t="n">
-        <v>7144909</v>
+        <v>7144806</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9560,34 +9529,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727795</v>
+        <v>129726773</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488737</v>
+        <v>489020</v>
       </c>
       <c r="R87" t="n">
-        <v>7144797</v>
+        <v>7144867</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,14 +9652,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På en levande gammal gran.</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,19 +9679,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727794</v>
+        <v>129727960</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -9717,14 +9722,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488763</v>
+        <v>488374</v>
       </c>
       <c r="R88" t="n">
-        <v>7144775</v>
+        <v>7144949</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9761,7 +9766,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9776,19 +9781,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727960</v>
+        <v>129727783</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -9819,14 +9824,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488374</v>
+        <v>488709</v>
       </c>
       <c r="R89" t="n">
-        <v>7144949</v>
+        <v>7144911</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9863,7 +9868,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9878,19 +9883,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727783</v>
+        <v>129727795</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9925,10 +9930,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488709</v>
+        <v>488737</v>
       </c>
       <c r="R90" t="n">
-        <v>7144911</v>
+        <v>7144797</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9965,7 +9970,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9992,45 +9997,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726769</v>
+        <v>129727794</v>
       </c>
       <c r="B91" t="n">
-        <v>75065</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489064</v>
+        <v>488763</v>
       </c>
       <c r="R91" t="n">
-        <v>7144843</v>
+        <v>7144775</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10060,19 +10065,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,63 +10083,48 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726773</v>
+        <v>129726769</v>
       </c>
       <c r="B92" t="n">
-        <v>91593</v>
+        <v>75065</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10149,10 +10134,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489020</v>
+        <v>489064</v>
       </c>
       <c r="R92" t="n">
-        <v>7144867</v>
+        <v>7144843</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10184,7 +10169,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10194,7 +10179,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10205,6 +10190,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R93" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,19 +10289,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10339,34 +10329,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R94" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10396,9 +10386,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,22 +10413,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730462</v>
+        <v>129730469</v>
       </c>
       <c r="B95" t="n">
-        <v>92311</v>
+        <v>57840</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489017</v>
+        <v>488507</v>
       </c>
       <c r="R95" t="n">
-        <v>7144821</v>
+        <v>7144936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,6 +10496,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10522,32 +10527,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>92311</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R96" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10593,11 +10598,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,27 +10624,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730469</v>
+        <v>129730439</v>
       </c>
       <c r="B97" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488507</v>
+        <v>488746</v>
       </c>
       <c r="R97" t="n">
-        <v>7144936</v>
+        <v>7144786</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10920,10 +10920,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730449</v>
+        <v>129730474</v>
       </c>
       <c r="B100" t="n">
-        <v>80187</v>
+        <v>91589</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10931,21 +10931,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488414</v>
+        <v>488676</v>
       </c>
       <c r="R100" t="n">
-        <v>7144940</v>
+        <v>7144870</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730474</v>
+        <v>129730449</v>
       </c>
       <c r="B102" t="n">
-        <v>91589</v>
+        <v>80187</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488676</v>
+        <v>488414</v>
       </c>
       <c r="R102" t="n">
-        <v>7144870</v>
+        <v>7144940</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730451</v>
+        <v>129730443</v>
       </c>
       <c r="B104" t="n">
-        <v>80186</v>
+        <v>57896</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488709</v>
+        <v>488348</v>
       </c>
       <c r="R104" t="n">
-        <v>7144786</v>
+        <v>7144901</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730443</v>
+        <v>129730451</v>
       </c>
       <c r="B106" t="n">
-        <v>57896</v>
+        <v>80186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11513,21 +11513,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488348</v>
+        <v>488709</v>
       </c>
       <c r="R106" t="n">
-        <v>7144901</v>
+        <v>7144786</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>91607</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R109" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,11 +11874,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,10 +11900,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B110" t="n">
-        <v>91607</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11916,21 +11911,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11940,10 +11935,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R110" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,6 +11971,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12696,10 +12696,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730471</v>
+        <v>129730458</v>
       </c>
       <c r="B118" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12707,21 +12707,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488625</v>
+        <v>489058</v>
       </c>
       <c r="R118" t="n">
-        <v>7144878</v>
+        <v>7144802</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12793,10 +12793,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730458</v>
+        <v>129730471</v>
       </c>
       <c r="B119" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12804,21 +12804,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12828,10 +12828,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>489058</v>
+        <v>488625</v>
       </c>
       <c r="R119" t="n">
-        <v>7144802</v>
+        <v>7144878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12987,10 +12987,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730478</v>
+        <v>129730459</v>
       </c>
       <c r="B121" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12998,19 +12998,23 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13018,10 +13022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488436</v>
+        <v>488604</v>
       </c>
       <c r="R121" t="n">
-        <v>7144967</v>
+        <v>7144985</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13080,34 +13084,30 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730456</v>
+        <v>129730478</v>
       </c>
       <c r="B122" t="n">
-        <v>91964</v>
+        <v>91613</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13115,10 +13115,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488467</v>
+        <v>488436</v>
       </c>
       <c r="R122" t="n">
-        <v>7144951</v>
+        <v>7144967</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13177,32 +13177,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730459</v>
+        <v>129730456</v>
       </c>
       <c r="B123" t="n">
-        <v>91593</v>
+        <v>91964</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488604</v>
+        <v>488467</v>
       </c>
       <c r="R123" t="n">
-        <v>7144985</v>
+        <v>7144951</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>80215</v>
+        <v>83050</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R124" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B125" t="n">
-        <v>83050</v>
+        <v>80215</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R125" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R127" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B128" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R128" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13759,32 +13759,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730440</v>
+        <v>129730475</v>
       </c>
       <c r="B129" t="n">
-        <v>56926</v>
+        <v>91589</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>489134</v>
+        <v>488459</v>
       </c>
       <c r="R129" t="n">
-        <v>7144763</v>
+        <v>7144958</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13830,11 +13830,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13958,32 +13953,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730475</v>
+        <v>129730440</v>
       </c>
       <c r="B131" t="n">
-        <v>91589</v>
+        <v>56926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13993,10 +13988,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488459</v>
+        <v>489134</v>
       </c>
       <c r="R131" t="n">
-        <v>7144958</v>
+        <v>7144763</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14029,6 +14024,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129716427</v>
+        <v>129726758</v>
       </c>
       <c r="B2" t="n">
-        <v>83042</v>
+        <v>82916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488400</v>
+        <v>488417</v>
       </c>
       <c r="R2" t="n">
-        <v>7144977</v>
+        <v>7145102</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727955</v>
+        <v>129716427</v>
       </c>
       <c r="B3" t="n">
-        <v>91589</v>
+        <v>83042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489154</v>
+        <v>488400</v>
       </c>
       <c r="R3" t="n">
-        <v>7144751</v>
+        <v>7144977</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727773</v>
+        <v>129726770</v>
       </c>
       <c r="B4" t="n">
-        <v>91589</v>
+        <v>80187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,41 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488610</v>
+        <v>489064</v>
       </c>
       <c r="R4" t="n">
-        <v>7144833</v>
+        <v>7144843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,14 +947,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,44 +968,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1106,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726770</v>
+        <v>129727955</v>
       </c>
       <c r="B6" t="n">
-        <v>80187</v>
+        <v>91589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489064</v>
+        <v>489154</v>
       </c>
       <c r="R6" t="n">
-        <v>7144843</v>
+        <v>7144751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,21 +1171,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1197,41 +1184,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726758</v>
+        <v>129727773</v>
       </c>
       <c r="B7" t="n">
-        <v>82916</v>
+        <v>91589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,34 +1211,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488417</v>
+        <v>488610</v>
       </c>
       <c r="R7" t="n">
-        <v>7145102</v>
+        <v>7144833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,19 +1275,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,18 +1291,44 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129716439</v>
+        <v>129727952</v>
       </c>
       <c r="B9" t="n">
-        <v>83042</v>
+        <v>91891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,34 +1481,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488354</v>
+        <v>488401</v>
       </c>
       <c r="R9" t="n">
-        <v>7144989</v>
+        <v>7144967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,22 +1555,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129727952</v>
+        <v>129716439</v>
       </c>
       <c r="B10" t="n">
-        <v>91891</v>
+        <v>83042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488401</v>
+        <v>488354</v>
       </c>
       <c r="R10" t="n">
-        <v>7144967</v>
+        <v>7144989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,22 +1652,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727776</v>
+        <v>129726781</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,34 +1675,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488425</v>
+        <v>488365</v>
       </c>
       <c r="R11" t="n">
-        <v>7145015</v>
+        <v>7144983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,14 +1732,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,19 +1759,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726761</v>
+        <v>129727782</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1797,14 +1802,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488516</v>
+        <v>488694</v>
       </c>
       <c r="R12" t="n">
-        <v>7145014</v>
+        <v>7144925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,19 +1839,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,19 +1861,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727801</v>
+        <v>129727796</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488339</v>
+        <v>488507</v>
       </c>
       <c r="R13" t="n">
-        <v>7144937</v>
+        <v>7144870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,45 +1975,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727782</v>
+        <v>129727765</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488694</v>
+        <v>488701</v>
       </c>
       <c r="R14" t="n">
-        <v>7144925</v>
+        <v>7144801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,8 +2066,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2077,52 +2110,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727765</v>
+        <v>129726761</v>
       </c>
       <c r="B15" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488701</v>
+        <v>488516</v>
       </c>
       <c r="R15" t="n">
-        <v>7144801</v>
+        <v>7145014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,14 +2178,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,54 +2199,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726781</v>
+        <v>129727776</v>
       </c>
       <c r="B16" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,34 +2228,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488365</v>
+        <v>488425</v>
       </c>
       <c r="R16" t="n">
-        <v>7144983</v>
+        <v>7145015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,19 +2285,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2307,19 +2307,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727796</v>
+        <v>129727801</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488507</v>
+        <v>488339</v>
       </c>
       <c r="R17" t="n">
-        <v>7144870</v>
+        <v>7144937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129716443</v>
+        <v>129727768</v>
       </c>
       <c r="B18" t="n">
-        <v>91589</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2432,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488470</v>
+        <v>488790</v>
       </c>
       <c r="R18" t="n">
-        <v>7144975</v>
+        <v>7144786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,6 +2506,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i en grov gammal gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2502,26 +2519,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727768</v>
+        <v>129726774</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,46 +2571,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488790</v>
+        <v>489025</v>
       </c>
       <c r="R19" t="n">
-        <v>7144786</v>
+        <v>7144875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,14 +2628,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i en grov gammal gran.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,41 +2651,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2754,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726774</v>
+        <v>129716443</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,34 +2775,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489025</v>
+        <v>488470</v>
       </c>
       <c r="R21" t="n">
-        <v>7144875</v>
+        <v>7144975</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,19 +2832,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,12 +2849,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129727950</v>
+        <v>129727946</v>
       </c>
       <c r="B24" t="n">
-        <v>80187</v>
+        <v>91593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,21 +3086,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488374</v>
+        <v>489112</v>
       </c>
       <c r="R24" t="n">
-        <v>7144953</v>
+        <v>7144780</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129727946</v>
+        <v>129726762</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>83050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,34 +3183,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489112</v>
+        <v>488626</v>
       </c>
       <c r="R25" t="n">
-        <v>7144780</v>
+        <v>7145010</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,9 +3240,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,22 +3267,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726762</v>
+        <v>129727950</v>
       </c>
       <c r="B26" t="n">
-        <v>83050</v>
+        <v>80187</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,34 +3290,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488626</v>
+        <v>488374</v>
       </c>
       <c r="R26" t="n">
-        <v>7145010</v>
+        <v>7144953</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,19 +3347,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,22 +3364,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129716435</v>
+        <v>129727772</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>80187</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,39 +3387,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488832</v>
+        <v>488470</v>
       </c>
       <c r="R27" t="n">
-        <v>7144827</v>
+        <v>7144960</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,34 +3456,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727772</v>
+        <v>129727786</v>
       </c>
       <c r="B28" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,41 +3522,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488470</v>
+        <v>489035</v>
       </c>
       <c r="R28" t="n">
-        <v>7144960</v>
+        <v>7144832</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3560,7 +3586,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,34 +3595,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727786</v>
+        <v>129716435</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,34 +3624,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489035</v>
+        <v>488832</v>
       </c>
       <c r="R29" t="n">
-        <v>7144832</v>
+        <v>7144827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,11 +3691,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3703,22 +3703,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726760</v>
+        <v>129716436</v>
       </c>
       <c r="B30" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,34 +3726,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488426</v>
+        <v>489031</v>
       </c>
       <c r="R30" t="n">
-        <v>7145052</v>
+        <v>7144903</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,19 +3783,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,22 +3800,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129727945</v>
+        <v>129727792</v>
       </c>
       <c r="B31" t="n">
-        <v>91607</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,37 +3823,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489010</v>
+        <v>488815</v>
       </c>
       <c r="R31" t="n">
-        <v>7144808</v>
+        <v>7144788</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3898,35 +3885,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129727792</v>
+        <v>129727945</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>91607</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,34 +3925,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488815</v>
+        <v>489010</v>
       </c>
       <c r="R32" t="n">
-        <v>7144788</v>
+        <v>7144808</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,39 +3990,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726763</v>
+        <v>129726760</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>88992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,21 +4026,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4060,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488626</v>
+        <v>488426</v>
       </c>
       <c r="R33" t="n">
-        <v>7145010</v>
+        <v>7145052</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4095,7 +4085,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4105,7 +4095,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4132,7 +4122,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129716436</v>
+        <v>129726763</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4163,14 +4153,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489031</v>
+        <v>488626</v>
       </c>
       <c r="R34" t="n">
-        <v>7144903</v>
+        <v>7145010</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,9 +4190,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,22 +4217,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726765</v>
+        <v>129726784</v>
       </c>
       <c r="B35" t="n">
-        <v>82916</v>
+        <v>83042</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,21 +4240,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488725</v>
+        <v>488335</v>
       </c>
       <c r="R35" t="n">
-        <v>7144925</v>
+        <v>7144978</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129727802</v>
+        <v>129726771</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,34 +4347,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488268</v>
+        <v>489056</v>
       </c>
       <c r="R36" t="n">
-        <v>7145078</v>
+        <v>7144853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,14 +4400,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4426,22 +4427,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726771</v>
+        <v>129726765</v>
       </c>
       <c r="B37" t="n">
-        <v>91613</v>
+        <v>82916</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,19 +4450,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4469,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489056</v>
+        <v>488725</v>
       </c>
       <c r="R37" t="n">
-        <v>7144853</v>
+        <v>7144925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4504,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4514,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4541,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726784</v>
+        <v>129727802</v>
       </c>
       <c r="B38" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4552,34 +4557,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488335</v>
+        <v>488268</v>
       </c>
       <c r="R38" t="n">
-        <v>7144978</v>
+        <v>7145078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,19 +4614,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,22 +4636,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726782</v>
+        <v>129726780</v>
       </c>
       <c r="B39" t="n">
-        <v>83050</v>
+        <v>83055</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,21 +4659,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488365</v>
+        <v>488414</v>
       </c>
       <c r="R39" t="n">
-        <v>7144983</v>
+        <v>7144975</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4755,10 +4755,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129716425</v>
+        <v>129727788</v>
       </c>
       <c r="B40" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,21 +4766,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488829</v>
+        <v>488989</v>
       </c>
       <c r="R40" t="n">
-        <v>7144835</v>
+        <v>7144826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4828,6 +4828,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4840,22 +4845,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726780</v>
+        <v>129727959</v>
       </c>
       <c r="B41" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,34 +4868,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488414</v>
+        <v>488762</v>
       </c>
       <c r="R41" t="n">
-        <v>7144975</v>
+        <v>7144801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,19 +4925,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4947,22 +4942,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129727959</v>
+        <v>129716425</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>88992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,34 +4965,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488762</v>
+        <v>488829</v>
       </c>
       <c r="R42" t="n">
-        <v>7144801</v>
+        <v>7144835</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5044,22 +5039,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129727788</v>
+        <v>129726782</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5067,34 +5062,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488989</v>
+        <v>488365</v>
       </c>
       <c r="R43" t="n">
-        <v>7144826</v>
+        <v>7144983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,14 +5119,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,12 +5146,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727948</v>
+        <v>129727781</v>
       </c>
       <c r="B46" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5439,34 +5439,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488739</v>
+        <v>488586</v>
       </c>
       <c r="R46" t="n">
-        <v>7144803</v>
+        <v>7144955</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5501,6 +5501,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5513,19 +5518,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727785</v>
+        <v>129726775</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5556,14 +5561,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488865</v>
+        <v>488851</v>
       </c>
       <c r="R47" t="n">
-        <v>7144860</v>
+        <v>7144825</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5593,14 +5598,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,22 +5625,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727799</v>
+        <v>129727948</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,34 +5648,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488408</v>
+        <v>488739</v>
       </c>
       <c r="R48" t="n">
-        <v>7144970</v>
+        <v>7144803</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5700,11 +5710,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5717,19 +5722,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129726775</v>
+        <v>129727785</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5760,14 +5765,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488851</v>
+        <v>488865</v>
       </c>
       <c r="R49" t="n">
-        <v>7144825</v>
+        <v>7144860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5797,19 +5802,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5824,19 +5824,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727777</v>
+        <v>129727799</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488483</v>
+        <v>488408</v>
       </c>
       <c r="R50" t="n">
-        <v>7144992</v>
+        <v>7144970</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129716437</v>
+        <v>129727777</v>
       </c>
       <c r="B51" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488533</v>
+        <v>488483</v>
       </c>
       <c r="R51" t="n">
-        <v>7144953</v>
+        <v>7144992</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6011,6 +6011,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6023,22 +6028,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727781</v>
+        <v>129716437</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,21 +6051,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488586</v>
+        <v>488533</v>
       </c>
       <c r="R52" t="n">
-        <v>7144955</v>
+        <v>7144953</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,11 +6113,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6125,12 +6125,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727780</v>
+        <v>129716431</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488542</v>
+        <v>488426</v>
       </c>
       <c r="R55" t="n">
-        <v>7144969</v>
+        <v>7145034</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6404,11 +6404,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6421,19 +6416,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716431</v>
+        <v>129727780</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6468,10 +6463,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488426</v>
+        <v>488542</v>
       </c>
       <c r="R56" t="n">
-        <v>7145034</v>
+        <v>7144969</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6506,6 +6501,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,12 +6518,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7003,7 +7003,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129727791</v>
+        <v>129727800</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488907</v>
+        <v>488375</v>
       </c>
       <c r="R62" t="n">
-        <v>7144779</v>
+        <v>7144951</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7105,7 +7105,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129727800</v>
+        <v>129727791</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488375</v>
+        <v>488907</v>
       </c>
       <c r="R63" t="n">
-        <v>7144951</v>
+        <v>7144779</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7518,7 +7518,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129727790</v>
+        <v>129716433</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488911</v>
+        <v>488359</v>
       </c>
       <c r="R67" t="n">
-        <v>7144836</v>
+        <v>7144987</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7591,11 +7591,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7608,12 +7603,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7819,7 +7814,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129716433</v>
+        <v>129727790</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7854,10 +7849,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488359</v>
+        <v>488911</v>
       </c>
       <c r="R70" t="n">
-        <v>7144987</v>
+        <v>7144836</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7892,6 +7887,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7904,12 +7904,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129716429</v>
+        <v>129727954</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488440</v>
+        <v>489143</v>
       </c>
       <c r="R72" t="n">
-        <v>7144976</v>
+        <v>7144773</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8103,22 +8103,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129727951</v>
+        <v>129727778</v>
       </c>
       <c r="B73" t="n">
-        <v>91891</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8126,34 +8126,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489112</v>
+        <v>488513</v>
       </c>
       <c r="R73" t="n">
-        <v>7144780</v>
+        <v>7144973</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8188,6 +8188,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8200,22 +8205,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129727954</v>
+        <v>129716429</v>
       </c>
       <c r="B74" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,34 +8228,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489143</v>
+        <v>488440</v>
       </c>
       <c r="R74" t="n">
-        <v>7144773</v>
+        <v>7144976</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8297,12 +8302,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8416,7 +8421,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129727778</v>
+        <v>129726779</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8447,14 +8452,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488513</v>
+        <v>488452</v>
       </c>
       <c r="R76" t="n">
-        <v>7144973</v>
+        <v>7144979</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8484,14 +8489,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8506,22 +8516,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726779</v>
+        <v>129727951</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>91891</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,34 +8539,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488452</v>
+        <v>489112</v>
       </c>
       <c r="R77" t="n">
-        <v>7144979</v>
+        <v>7144780</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8586,19 +8596,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726777</v>
+        <v>129727769</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,34 +8733,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488570</v>
+        <v>488758</v>
       </c>
       <c r="R79" t="n">
-        <v>7144960</v>
+        <v>7144774</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8790,19 +8797,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8811,28 +8813,54 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716445</v>
+        <v>129716434</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8840,21 +8868,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8864,10 +8892,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488685</v>
+        <v>488618</v>
       </c>
       <c r="R80" t="n">
-        <v>7144909</v>
+        <v>7144922</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8926,7 +8954,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129716434</v>
+        <v>129727957</v>
       </c>
       <c r="B81" t="n">
         <v>91589</v>
@@ -8957,14 +8985,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488618</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7144922</v>
+        <v>7144844</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9011,22 +9039,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727957</v>
+        <v>129716445</v>
       </c>
       <c r="B82" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9034,34 +9062,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488591</v>
+        <v>488685</v>
       </c>
       <c r="R82" t="n">
-        <v>7144844</v>
+        <v>7144909</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9108,22 +9136,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129727769</v>
+        <v>129716441</v>
       </c>
       <c r="B83" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9131,41 +9159,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488758</v>
+        <v>488921</v>
       </c>
       <c r="R83" t="n">
-        <v>7144774</v>
+        <v>7144886</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9200,62 +9221,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129716441</v>
+        <v>129716422</v>
       </c>
       <c r="B84" t="n">
         <v>79081</v>
@@ -9290,10 +9280,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488921</v>
+        <v>488767</v>
       </c>
       <c r="R84" t="n">
-        <v>7144886</v>
+        <v>7144853</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9352,45 +9342,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129716422</v>
+        <v>129727767</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488767</v>
+        <v>488658</v>
       </c>
       <c r="R85" t="n">
-        <v>7144853</v>
+        <v>7144806</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9425,76 +9422,100 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727767</v>
+        <v>129726777</v>
       </c>
       <c r="B86" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488658</v>
+        <v>488570</v>
       </c>
       <c r="R86" t="n">
-        <v>7144806</v>
+        <v>7144960</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9524,14 +9545,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9540,44 +9566,18 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9691,7 +9691,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727960</v>
+        <v>129727795</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -9722,14 +9722,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488374</v>
+        <v>488737</v>
       </c>
       <c r="R88" t="n">
-        <v>7144949</v>
+        <v>7144797</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9781,19 +9781,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727783</v>
+        <v>129727794</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488709</v>
+        <v>488763</v>
       </c>
       <c r="R89" t="n">
-        <v>7144911</v>
+        <v>7144775</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9895,7 +9895,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727795</v>
+        <v>129727960</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9926,14 +9926,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488737</v>
+        <v>488374</v>
       </c>
       <c r="R90" t="n">
-        <v>7144797</v>
+        <v>7144949</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På en levande gammal gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9985,19 +9985,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727794</v>
+        <v>129727783</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488763</v>
+        <v>488709</v>
       </c>
       <c r="R91" t="n">
-        <v>7144775</v>
+        <v>7144911</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10425,10 +10425,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730469</v>
+        <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>57840</v>
+        <v>92311</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488507</v>
+        <v>489017</v>
       </c>
       <c r="R95" t="n">
-        <v>7144936</v>
+        <v>7144821</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,32 +10522,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730462</v>
+        <v>129730439</v>
       </c>
       <c r="B96" t="n">
-        <v>92311</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489017</v>
+        <v>488746</v>
       </c>
       <c r="R96" t="n">
-        <v>7144821</v>
+        <v>7144786</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10598,6 +10593,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,27 +10624,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730439</v>
+        <v>129730469</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488746</v>
+        <v>488507</v>
       </c>
       <c r="R97" t="n">
-        <v>7144786</v>
+        <v>7144936</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10920,10 +10920,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730474</v>
+        <v>129730449</v>
       </c>
       <c r="B100" t="n">
-        <v>91589</v>
+        <v>80187</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10931,21 +10931,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488676</v>
+        <v>488414</v>
       </c>
       <c r="R100" t="n">
-        <v>7144870</v>
+        <v>7144940</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730449</v>
+        <v>129730474</v>
       </c>
       <c r="B102" t="n">
-        <v>80187</v>
+        <v>91589</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488414</v>
+        <v>488676</v>
       </c>
       <c r="R102" t="n">
-        <v>7144940</v>
+        <v>7144870</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730443</v>
+        <v>129730461</v>
       </c>
       <c r="B104" t="n">
-        <v>57896</v>
+        <v>91593</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488348</v>
+        <v>488464</v>
       </c>
       <c r="R104" t="n">
-        <v>7144901</v>
+        <v>7144953</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730461</v>
+        <v>129730451</v>
       </c>
       <c r="B105" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488464</v>
+        <v>488709</v>
       </c>
       <c r="R105" t="n">
-        <v>7144953</v>
+        <v>7144786</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730451</v>
+        <v>129730443</v>
       </c>
       <c r="B106" t="n">
-        <v>80186</v>
+        <v>57896</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11513,21 +11513,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488709</v>
+        <v>488348</v>
       </c>
       <c r="R106" t="n">
-        <v>7144786</v>
+        <v>7144901</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730467</v>
+        <v>129730464</v>
       </c>
       <c r="B113" t="n">
-        <v>83055</v>
+        <v>57896</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488737</v>
+        <v>488362</v>
       </c>
       <c r="R113" t="n">
-        <v>7144811</v>
+        <v>7144944</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,6 +12272,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12298,10 +12303,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730464</v>
+        <v>129730467</v>
       </c>
       <c r="B114" t="n">
-        <v>57896</v>
+        <v>83055</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12309,21 +12314,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12333,10 +12338,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488362</v>
+        <v>488737</v>
       </c>
       <c r="R114" t="n">
-        <v>7144944</v>
+        <v>7144811</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12369,11 +12374,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13084,30 +13084,34 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730478</v>
+        <v>129730456</v>
       </c>
       <c r="B122" t="n">
-        <v>91613</v>
+        <v>91964</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13115,10 +13119,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488436</v>
+        <v>488467</v>
       </c>
       <c r="R122" t="n">
-        <v>7144967</v>
+        <v>7144951</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13177,34 +13181,30 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730456</v>
+        <v>129730478</v>
       </c>
       <c r="B123" t="n">
-        <v>91964</v>
+        <v>91613</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488467</v>
+        <v>488436</v>
       </c>
       <c r="R123" t="n">
-        <v>7144951</v>
+        <v>7144967</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B127" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R127" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R128" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13759,7 +13759,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730475</v>
+        <v>129730472</v>
       </c>
       <c r="B129" t="n">
         <v>91589</v>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488459</v>
+        <v>488622</v>
       </c>
       <c r="R129" t="n">
-        <v>7144958</v>
+        <v>7144899</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730472</v>
+        <v>129730475</v>
       </c>
       <c r="B130" t="n">
         <v>91589</v>
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488622</v>
+        <v>488459</v>
       </c>
       <c r="R130" t="n">
-        <v>7144899</v>
+        <v>7144958</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129726758</v>
+        <v>129716427</v>
       </c>
       <c r="B2" t="n">
-        <v>82916</v>
+        <v>83042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488417</v>
+        <v>488400</v>
       </c>
       <c r="R2" t="n">
-        <v>7145102</v>
+        <v>7144977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129716427</v>
+        <v>129727797</v>
       </c>
       <c r="B3" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488400</v>
+        <v>488482</v>
       </c>
       <c r="R3" t="n">
-        <v>7144977</v>
+        <v>7144891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +845,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,57 +862,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726770</v>
+        <v>129727766</v>
       </c>
       <c r="B4" t="n">
-        <v>80187</v>
+        <v>80215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489064</v>
+        <v>488676</v>
       </c>
       <c r="R4" t="n">
-        <v>7144843</v>
+        <v>7144814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,19 +949,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,43 +965,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727797</v>
+        <v>129727955</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488482</v>
+        <v>489154</v>
       </c>
       <c r="R5" t="n">
-        <v>7144891</v>
+        <v>7144751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1082,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1091,22 +1094,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129727955</v>
+        <v>129727773</v>
       </c>
       <c r="B6" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,16 +1135,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489154</v>
+        <v>488610</v>
       </c>
       <c r="R6" t="n">
-        <v>7144751</v>
+        <v>7144833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,34 +1186,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727773</v>
+        <v>129726758</v>
       </c>
       <c r="B7" t="n">
-        <v>91589</v>
+        <v>82916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,41 +1252,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488610</v>
+        <v>488417</v>
       </c>
       <c r="R7" t="n">
-        <v>7144833</v>
+        <v>7145102</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,14 +1309,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,96 +1330,63 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129727766</v>
+        <v>129726770</v>
       </c>
       <c r="B8" t="n">
-        <v>80215</v>
+        <v>80187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488676</v>
+        <v>489064</v>
       </c>
       <c r="R8" t="n">
-        <v>7144814</v>
+        <v>7144843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,14 +1416,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,44 +1437,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>129727952</v>
       </c>
       <c r="B9" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727782</v>
+        <v>129727776</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488694</v>
+        <v>488425</v>
       </c>
       <c r="R12" t="n">
-        <v>7144925</v>
+        <v>7145015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727796</v>
+        <v>129726761</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -1904,14 +1904,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488507</v>
+        <v>488516</v>
       </c>
       <c r="R13" t="n">
-        <v>7144870</v>
+        <v>7145014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,14 +1941,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,64 +1968,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727765</v>
+        <v>129727801</v>
       </c>
       <c r="B14" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488701</v>
+        <v>488339</v>
       </c>
       <c r="R14" t="n">
-        <v>7144801</v>
+        <v>7144937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2055,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,34 +2064,8 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2110,7 +2082,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726761</v>
+        <v>129727796</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2141,14 +2113,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488516</v>
+        <v>488507</v>
       </c>
       <c r="R15" t="n">
-        <v>7145014</v>
+        <v>7144870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,19 +2150,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,19 +2172,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727776</v>
+        <v>129727782</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2252,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488425</v>
+        <v>488694</v>
       </c>
       <c r="R16" t="n">
-        <v>7145015</v>
+        <v>7144925</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2259,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,45 +2286,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727801</v>
+        <v>129727765</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488339</v>
+        <v>488701</v>
       </c>
       <c r="R17" t="n">
-        <v>7144937</v>
+        <v>7144801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2368,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,8 +2377,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727768</v>
+        <v>129727947</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>91597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,46 +2432,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488790</v>
+        <v>488803</v>
       </c>
       <c r="R18" t="n">
-        <v>7144786</v>
+        <v>7144779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,11 +2494,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i en grov gammal gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2519,51 +2502,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129726774</v>
+        <v>129716443</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,34 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489025</v>
+        <v>488470</v>
       </c>
       <c r="R19" t="n">
-        <v>7144875</v>
+        <v>7144975</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,19 +2586,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129727947</v>
+        <v>129726774</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2678,34 +2626,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488803</v>
+        <v>489025</v>
       </c>
       <c r="R20" t="n">
-        <v>7144779</v>
+        <v>7144875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,9 +2683,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,22 +2710,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129716443</v>
+        <v>129727768</v>
       </c>
       <c r="B21" t="n">
-        <v>91589</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,34 +2733,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488470</v>
+        <v>488790</v>
       </c>
       <c r="R21" t="n">
-        <v>7144975</v>
+        <v>7144786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,6 +2807,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i en grov gammal gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2845,16 +2820,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3078,7 +3078,7 @@
         <v>129727946</v>
       </c>
       <c r="B24" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726762</v>
+        <v>129727950</v>
       </c>
       <c r="B25" t="n">
-        <v>83050</v>
+        <v>80187</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,34 +3183,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488626</v>
+        <v>488374</v>
       </c>
       <c r="R25" t="n">
-        <v>7145010</v>
+        <v>7144953</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,19 +3240,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,22 +3257,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129727950</v>
+        <v>129726762</v>
       </c>
       <c r="B26" t="n">
-        <v>80187</v>
+        <v>83050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,34 +3280,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488374</v>
+        <v>488626</v>
       </c>
       <c r="R26" t="n">
-        <v>7144953</v>
+        <v>7145010</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3347,9 +3337,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,12 +3364,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129716436</v>
+        <v>129727945</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>91611</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,34 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489031</v>
+        <v>489010</v>
       </c>
       <c r="R30" t="n">
-        <v>7144903</v>
+        <v>7144808</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3794,28 +3797,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129727792</v>
+        <v>129726760</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>88996</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,34 +3827,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488815</v>
+        <v>488426</v>
       </c>
       <c r="R31" t="n">
-        <v>7144788</v>
+        <v>7145052</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3880,14 +3884,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3902,22 +3911,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129727945</v>
+        <v>129726763</v>
       </c>
       <c r="B32" t="n">
-        <v>91607</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3925,37 +3934,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489010</v>
+        <v>488626</v>
       </c>
       <c r="R32" t="n">
-        <v>7144808</v>
+        <v>7145010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,40 +3991,49 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726760</v>
+        <v>129716436</v>
       </c>
       <c r="B33" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4026,34 +4041,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488426</v>
+        <v>489031</v>
       </c>
       <c r="R33" t="n">
-        <v>7145052</v>
+        <v>7144903</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4083,19 +4098,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4110,19 +4115,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726763</v>
+        <v>129727792</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -4153,14 +4158,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488626</v>
+        <v>488815</v>
       </c>
       <c r="R34" t="n">
-        <v>7145010</v>
+        <v>7144788</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,19 +4195,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,22 +4217,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726784</v>
+        <v>129726765</v>
       </c>
       <c r="B35" t="n">
-        <v>83042</v>
+        <v>82916</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,21 +4240,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488335</v>
+        <v>488725</v>
       </c>
       <c r="R35" t="n">
-        <v>7144978</v>
+        <v>7144925</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726771</v>
+        <v>129726784</v>
       </c>
       <c r="B36" t="n">
-        <v>91613</v>
+        <v>83042</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,19 +4347,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4367,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489056</v>
+        <v>488335</v>
       </c>
       <c r="R36" t="n">
-        <v>7144853</v>
+        <v>7144978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4406,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4416,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726765</v>
+        <v>129727802</v>
       </c>
       <c r="B37" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,34 +4454,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488725</v>
+        <v>488268</v>
       </c>
       <c r="R37" t="n">
-        <v>7144925</v>
+        <v>7145078</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,19 +4511,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,22 +4533,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129727802</v>
+        <v>129726771</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>91617</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,34 +4556,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488268</v>
+        <v>489056</v>
       </c>
       <c r="R38" t="n">
-        <v>7145078</v>
+        <v>7144853</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,14 +4609,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,12 +4636,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727788</v>
+        <v>129726782</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,34 +4766,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488989</v>
+        <v>488365</v>
       </c>
       <c r="R40" t="n">
-        <v>7144826</v>
+        <v>7144983</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4823,14 +4823,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,12 +4850,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4954,10 +4959,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129716425</v>
+        <v>129727788</v>
       </c>
       <c r="B42" t="n">
-        <v>88992</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,21 +4970,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4989,10 +4994,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488829</v>
+        <v>488989</v>
       </c>
       <c r="R42" t="n">
-        <v>7144835</v>
+        <v>7144826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5027,6 +5032,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5039,22 +5049,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726782</v>
+        <v>129716425</v>
       </c>
       <c r="B43" t="n">
-        <v>83050</v>
+        <v>88996</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,34 +5072,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488365</v>
+        <v>488829</v>
       </c>
       <c r="R43" t="n">
-        <v>7144983</v>
+        <v>7144835</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5119,19 +5129,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,12 +5146,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727770</v>
+        <v>129727785</v>
       </c>
       <c r="B45" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5304,41 +5304,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488674</v>
+        <v>488865</v>
       </c>
       <c r="R45" t="n">
-        <v>7144814</v>
+        <v>7144860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5375,7 +5368,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5384,34 +5377,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5428,7 +5395,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727781</v>
+        <v>129727799</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5463,10 +5430,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488586</v>
+        <v>488408</v>
       </c>
       <c r="R46" t="n">
-        <v>7144955</v>
+        <v>7144970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,10 +5497,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726775</v>
+        <v>129716437</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5541,34 +5508,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488851</v>
+        <v>488533</v>
       </c>
       <c r="R47" t="n">
-        <v>7144825</v>
+        <v>7144953</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,19 +5565,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5625,22 +5582,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727948</v>
+        <v>129727777</v>
       </c>
       <c r="B48" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5648,34 +5605,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488739</v>
+        <v>488483</v>
       </c>
       <c r="R48" t="n">
-        <v>7144803</v>
+        <v>7144992</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5710,6 +5667,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5722,19 +5684,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727785</v>
+        <v>129727781</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5769,10 +5731,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488865</v>
+        <v>488586</v>
       </c>
       <c r="R49" t="n">
-        <v>7144860</v>
+        <v>7144955</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5771,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5836,7 +5798,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727799</v>
+        <v>129726775</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5867,14 +5829,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488408</v>
+        <v>488851</v>
       </c>
       <c r="R50" t="n">
-        <v>7144970</v>
+        <v>7144825</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,14 +5866,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5926,22 +5893,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727777</v>
+        <v>129727948</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,34 +5916,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488483</v>
+        <v>488739</v>
       </c>
       <c r="R51" t="n">
-        <v>7144992</v>
+        <v>7144803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6011,11 +5978,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6028,22 +5990,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129716437</v>
+        <v>129727770</v>
       </c>
       <c r="B52" t="n">
-        <v>83050</v>
+        <v>80187</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,34 +6013,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488533</v>
+        <v>488674</v>
       </c>
       <c r="R52" t="n">
-        <v>7144953</v>
+        <v>7144814</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,69 +6082,100 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129727953</v>
+        <v>129716431</v>
       </c>
       <c r="B53" t="n">
-        <v>91975</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488400</v>
+        <v>488426</v>
       </c>
       <c r="R53" t="n">
-        <v>7144968</v>
+        <v>7145034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,57 +6222,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129716447</v>
+        <v>129727953</v>
       </c>
       <c r="B54" t="n">
-        <v>83055</v>
+        <v>91979</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1467</v>
+        <v>1506</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488731</v>
+        <v>488400</v>
       </c>
       <c r="R54" t="n">
-        <v>7144891</v>
+        <v>7144968</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6319,22 +6319,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129716431</v>
+        <v>129716447</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488426</v>
+        <v>488731</v>
       </c>
       <c r="R55" t="n">
-        <v>7145034</v>
+        <v>7144891</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
         <v>129716428</v>
       </c>
       <c r="B57" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>129716423</v>
       </c>
       <c r="B58" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716430</v>
+        <v>129727791</v>
       </c>
       <c r="B59" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6735,19 +6735,23 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6755,10 +6759,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488835</v>
+        <v>488907</v>
       </c>
       <c r="R59" t="n">
-        <v>7144824</v>
+        <v>7144779</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6793,6 +6797,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6805,22 +6814,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716440</v>
+        <v>129727800</v>
       </c>
       <c r="B60" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6828,19 +6837,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6848,10 +6861,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488547</v>
+        <v>488375</v>
       </c>
       <c r="R60" t="n">
-        <v>7144971</v>
+        <v>7144951</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6886,6 +6899,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6898,22 +6916,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716442</v>
+        <v>129716430</v>
       </c>
       <c r="B61" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6941,10 +6959,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488630</v>
+        <v>488835</v>
       </c>
       <c r="R61" t="n">
-        <v>7145015</v>
+        <v>7144824</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7003,10 +7021,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129727800</v>
+        <v>129716440</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>91617</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7014,23 +7032,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7038,10 +7052,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488375</v>
+        <v>488547</v>
       </c>
       <c r="R62" t="n">
-        <v>7144951</v>
+        <v>7144971</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7076,11 +7090,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7093,22 +7102,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129727791</v>
+        <v>129716442</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>91617</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7116,23 +7125,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7140,10 +7145,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488907</v>
+        <v>488630</v>
       </c>
       <c r="R63" t="n">
-        <v>7144779</v>
+        <v>7145015</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7178,11 +7183,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7195,12 +7195,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7615,7 +7615,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129716432</v>
+        <v>129727790</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>489065</v>
+        <v>488911</v>
       </c>
       <c r="R68" t="n">
-        <v>7144852</v>
+        <v>7144836</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7705,19 +7705,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129727958</v>
+        <v>129727787</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7748,14 +7748,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488796</v>
+        <v>489024</v>
       </c>
       <c r="R69" t="n">
-        <v>7144792</v>
+        <v>7144841</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7790,6 +7790,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7802,19 +7807,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129727790</v>
+        <v>129727958</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7845,14 +7850,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488911</v>
+        <v>488796</v>
       </c>
       <c r="R70" t="n">
-        <v>7144836</v>
+        <v>7144792</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7887,11 +7892,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7904,19 +7904,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129727787</v>
+        <v>129716432</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489024</v>
+        <v>489065</v>
       </c>
       <c r="R71" t="n">
-        <v>7144841</v>
+        <v>7144852</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gammal gran.</t>
+          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8006,12 +8006,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8021,7 +8021,7 @@
         <v>129727954</v>
       </c>
       <c r="B72" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129727778</v>
+        <v>129716429</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488513</v>
+        <v>488440</v>
       </c>
       <c r="R73" t="n">
-        <v>7144973</v>
+        <v>7144976</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8188,11 +8188,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8205,19 +8200,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129716429</v>
+        <v>129727778</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -8252,10 +8247,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488440</v>
+        <v>488513</v>
       </c>
       <c r="R74" t="n">
-        <v>7144976</v>
+        <v>7144973</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,6 +8285,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8302,19 +8302,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726778</v>
+        <v>129726779</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488522</v>
+        <v>488452</v>
       </c>
       <c r="R75" t="n">
-        <v>7144974</v>
+        <v>7144979</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8421,7 +8421,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129726779</v>
+        <v>129726778</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488452</v>
+        <v>488522</v>
       </c>
       <c r="R76" t="n">
-        <v>7144979</v>
+        <v>7144974</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8531,7 +8531,7 @@
         <v>129727951</v>
       </c>
       <c r="B77" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>129716424</v>
       </c>
       <c r="B78" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727769</v>
+        <v>129726777</v>
       </c>
       <c r="B79" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,41 +8733,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488758</v>
+        <v>488570</v>
       </c>
       <c r="R79" t="n">
-        <v>7144774</v>
+        <v>7144960</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8797,14 +8790,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8813,44 +8811,18 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8860,7 +8832,7 @@
         <v>129716434</v>
       </c>
       <c r="B80" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8954,10 +8926,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727957</v>
+        <v>129727769</v>
       </c>
       <c r="B81" t="n">
-        <v>91589</v>
+        <v>80187</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8965,34 +8937,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488758</v>
       </c>
       <c r="R81" t="n">
-        <v>7144844</v>
+        <v>7144774</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9027,34 +9006,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129716445</v>
+        <v>129727957</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9062,34 +9072,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488685</v>
+        <v>488591</v>
       </c>
       <c r="R82" t="n">
-        <v>7144909</v>
+        <v>7144844</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9136,19 +9146,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716441</v>
+        <v>129716445</v>
       </c>
       <c r="B83" t="n">
         <v>79081</v>
@@ -9183,10 +9193,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488921</v>
+        <v>488685</v>
       </c>
       <c r="R83" t="n">
-        <v>7144886</v>
+        <v>7144909</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9245,7 +9255,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129716422</v>
+        <v>129716441</v>
       </c>
       <c r="B84" t="n">
         <v>79081</v>
@@ -9280,10 +9290,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488767</v>
+        <v>488921</v>
       </c>
       <c r="R84" t="n">
-        <v>7144853</v>
+        <v>7144886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9342,52 +9352,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129727767</v>
+        <v>129716422</v>
       </c>
       <c r="B85" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488658</v>
+        <v>488767</v>
       </c>
       <c r="R85" t="n">
-        <v>7144806</v>
+        <v>7144853</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9422,100 +9425,76 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129726777</v>
+        <v>129727767</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488570</v>
+        <v>488658</v>
       </c>
       <c r="R86" t="n">
-        <v>7144960</v>
+        <v>7144806</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9545,19 +9524,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9566,18 +9540,44 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9587,7 +9587,7 @@
         <v>129726773</v>
       </c>
       <c r="B87" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9895,45 +9895,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727960</v>
+        <v>129726769</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>75065</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488374</v>
+        <v>489064</v>
       </c>
       <c r="R90" t="n">
-        <v>7144949</v>
+        <v>7144843</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9963,14 +9963,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9981,23 +9986,38 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727783</v>
+        <v>129727960</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -10028,14 +10048,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488709</v>
+        <v>488374</v>
       </c>
       <c r="R91" t="n">
-        <v>7144911</v>
+        <v>7144949</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10072,7 +10092,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10087,57 +10107,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726769</v>
+        <v>129727783</v>
       </c>
       <c r="B92" t="n">
-        <v>75065</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489064</v>
+        <v>488709</v>
       </c>
       <c r="R92" t="n">
-        <v>7144843</v>
+        <v>7144911</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10167,19 +10187,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10190,41 +10205,26 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B93" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R93" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,9 +10289,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10306,22 +10316,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10329,34 +10339,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R94" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10386,19 +10396,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,44 +10413,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730462</v>
+        <v>129730439</v>
       </c>
       <c r="B95" t="n">
-        <v>92311</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489017</v>
+        <v>488746</v>
       </c>
       <c r="R95" t="n">
-        <v>7144821</v>
+        <v>7144786</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,6 +10496,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10522,27 +10527,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730439</v>
+        <v>129730469</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488746</v>
+        <v>488507</v>
       </c>
       <c r="R96" t="n">
-        <v>7144786</v>
+        <v>7144936</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10597,7 +10602,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,10 +10629,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730469</v>
+        <v>129730462</v>
       </c>
       <c r="B97" t="n">
-        <v>57840</v>
+        <v>92315</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10635,21 +10640,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>3298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10659,10 +10664,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488507</v>
+        <v>489017</v>
       </c>
       <c r="R97" t="n">
-        <v>7144936</v>
+        <v>7144821</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10695,11 +10700,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10729,7 +10729,7 @@
         <v>129730460</v>
       </c>
       <c r="B98" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>129730457</v>
       </c>
       <c r="B99" t="n">
-        <v>91964</v>
+        <v>91968</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>129730473</v>
       </c>
       <c r="B101" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>129730474</v>
       </c>
       <c r="B102" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730461</v>
+        <v>129730451</v>
       </c>
       <c r="B104" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488464</v>
+        <v>488709</v>
       </c>
       <c r="R104" t="n">
-        <v>7144953</v>
+        <v>7144786</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730451</v>
+        <v>129730461</v>
       </c>
       <c r="B105" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488709</v>
+        <v>488464</v>
       </c>
       <c r="R105" t="n">
-        <v>7144786</v>
+        <v>7144953</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11806,7 +11806,7 @@
         <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730464</v>
+        <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>57896</v>
+        <v>83055</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488362</v>
+        <v>488737</v>
       </c>
       <c r="R113" t="n">
-        <v>7144944</v>
+        <v>7144811</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,11 +12272,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12303,10 +12298,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730467</v>
+        <v>129730464</v>
       </c>
       <c r="B114" t="n">
-        <v>83055</v>
+        <v>57896</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12314,21 +12309,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12338,10 +12333,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488737</v>
+        <v>488362</v>
       </c>
       <c r="R114" t="n">
-        <v>7144811</v>
+        <v>7144944</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12374,6 +12369,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12403,7 +12403,7 @@
         <v>129730470</v>
       </c>
       <c r="B115" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>129730458</v>
       </c>
       <c r="B118" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>129730471</v>
       </c>
       <c r="B119" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>129730476</v>
       </c>
       <c r="B120" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12987,32 +12987,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730459</v>
+        <v>129730456</v>
       </c>
       <c r="B121" t="n">
-        <v>91593</v>
+        <v>91968</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13022,10 +13022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488604</v>
+        <v>488467</v>
       </c>
       <c r="R121" t="n">
-        <v>7144985</v>
+        <v>7144951</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13084,32 +13084,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730456</v>
+        <v>129730459</v>
       </c>
       <c r="B122" t="n">
-        <v>91964</v>
+        <v>91597</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13119,10 +13119,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488467</v>
+        <v>488604</v>
       </c>
       <c r="R122" t="n">
-        <v>7144951</v>
+        <v>7144985</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13184,7 +13184,7 @@
         <v>129730478</v>
       </c>
       <c r="B123" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R127" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B128" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R128" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13762,7 +13762,7 @@
         <v>129730472</v>
       </c>
       <c r="B129" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>129730475</v>
       </c>
       <c r="B130" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129716427</v>
       </c>
       <c r="B2" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>129727955</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>129727773</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726758</v>
+        <v>129726770</v>
       </c>
       <c r="B7" t="n">
-        <v>82916</v>
+        <v>80187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488417</v>
+        <v>489064</v>
       </c>
       <c r="R7" t="n">
-        <v>7145102</v>
+        <v>7144843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,6 +1332,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1348,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726770</v>
+        <v>129726758</v>
       </c>
       <c r="B8" t="n">
-        <v>80187</v>
+        <v>82918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489064</v>
+        <v>488417</v>
       </c>
       <c r="R8" t="n">
-        <v>7144843</v>
+        <v>7145102</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,21 +1454,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,7 +1473,7 @@
         <v>129727952</v>
       </c>
       <c r="B9" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>129716439</v>
       </c>
       <c r="B10" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726781</v>
+        <v>129727801</v>
       </c>
       <c r="B11" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,34 +1675,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488365</v>
+        <v>488339</v>
       </c>
       <c r="R11" t="n">
-        <v>7144983</v>
+        <v>7144937</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,19 +1732,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,12 +1754,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1873,45 +1868,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726761</v>
+        <v>129727765</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488516</v>
+        <v>488701</v>
       </c>
       <c r="R13" t="n">
-        <v>7145014</v>
+        <v>7144801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,19 +1943,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,25 +1959,51 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727801</v>
+        <v>129726761</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -2011,14 +2034,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488339</v>
+        <v>488516</v>
       </c>
       <c r="R14" t="n">
-        <v>7144937</v>
+        <v>7145014</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,14 +2071,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,19 +2098,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727796</v>
+        <v>129727782</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2117,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488507</v>
+        <v>488694</v>
       </c>
       <c r="R15" t="n">
-        <v>7144870</v>
+        <v>7144925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2185,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,7 +2212,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727782</v>
+        <v>129727796</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2219,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488694</v>
+        <v>488507</v>
       </c>
       <c r="R16" t="n">
-        <v>7144925</v>
+        <v>7144870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2287,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,52 +2314,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727765</v>
+        <v>129726781</v>
       </c>
       <c r="B17" t="n">
-        <v>80215</v>
+        <v>78094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488701</v>
+        <v>488365</v>
       </c>
       <c r="R17" t="n">
-        <v>7144801</v>
+        <v>7144983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,14 +2382,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,54 +2403,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727947</v>
+        <v>129726774</v>
       </c>
       <c r="B18" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2432,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488803</v>
+        <v>489025</v>
       </c>
       <c r="R18" t="n">
-        <v>7144779</v>
+        <v>7144875</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,9 +2489,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,22 +2516,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129716443</v>
+        <v>129727947</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,34 +2539,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488470</v>
+        <v>488803</v>
       </c>
       <c r="R19" t="n">
-        <v>7144975</v>
+        <v>7144779</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,22 +2613,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726774</v>
+        <v>129716443</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,34 +2636,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489025</v>
+        <v>488470</v>
       </c>
       <c r="R20" t="n">
-        <v>7144875</v>
+        <v>7144975</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,19 +2693,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,12 +2710,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726757</v>
+        <v>129726772</v>
       </c>
       <c r="B22" t="n">
-        <v>83042</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488392</v>
+        <v>489044</v>
       </c>
       <c r="R22" t="n">
-        <v>7145120</v>
+        <v>7144859</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726772</v>
+        <v>129726757</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489044</v>
+        <v>488392</v>
       </c>
       <c r="R23" t="n">
-        <v>7144859</v>
+        <v>7145120</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129727946</v>
+        <v>129727950</v>
       </c>
       <c r="B24" t="n">
-        <v>91597</v>
+        <v>80187</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,21 +3086,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489112</v>
+        <v>488374</v>
       </c>
       <c r="R24" t="n">
-        <v>7144780</v>
+        <v>7144953</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129727950</v>
+        <v>129727946</v>
       </c>
       <c r="B25" t="n">
-        <v>80187</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,21 +3183,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488374</v>
+        <v>489112</v>
       </c>
       <c r="R25" t="n">
-        <v>7144953</v>
+        <v>7144780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3272,7 +3272,7 @@
         <v>129726762</v>
       </c>
       <c r="B26" t="n">
-        <v>83050</v>
+        <v>83052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129727945</v>
+        <v>129716436</v>
       </c>
       <c r="B30" t="n">
-        <v>91611</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489010</v>
+        <v>489031</v>
       </c>
       <c r="R30" t="n">
-        <v>7144808</v>
+        <v>7144903</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,29 +3794,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726760</v>
+        <v>129727792</v>
       </c>
       <c r="B31" t="n">
-        <v>88996</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,34 +3823,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488426</v>
+        <v>488815</v>
       </c>
       <c r="R31" t="n">
-        <v>7145052</v>
+        <v>7144788</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3884,19 +3880,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:49</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,12 +3902,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4030,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129716436</v>
+        <v>129726760</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,34 +4032,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489031</v>
+        <v>488426</v>
       </c>
       <c r="R33" t="n">
-        <v>7144903</v>
+        <v>7145052</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4098,9 +4089,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,22 +4116,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727792</v>
+        <v>129727945</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,34 +4139,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488815</v>
+        <v>489010</v>
       </c>
       <c r="R34" t="n">
-        <v>7144788</v>
+        <v>7144808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,39 +4204,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726765</v>
+        <v>129727802</v>
       </c>
       <c r="B35" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488725</v>
+        <v>488268</v>
       </c>
       <c r="R35" t="n">
-        <v>7144925</v>
+        <v>7145078</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,19 +4297,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,12 +4319,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4339,7 +4334,7 @@
         <v>129726784</v>
       </c>
       <c r="B36" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,10 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129727802</v>
+        <v>129726765</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,34 +4449,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488268</v>
+        <v>488725</v>
       </c>
       <c r="R37" t="n">
-        <v>7145078</v>
+        <v>7144925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4511,14 +4506,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4533,12 +4533,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
         <v>129726771</v>
       </c>
       <c r="B38" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726780</v>
+        <v>129716425</v>
       </c>
       <c r="B39" t="n">
-        <v>83055</v>
+        <v>88998</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488414</v>
+        <v>488829</v>
       </c>
       <c r="R39" t="n">
-        <v>7144975</v>
+        <v>7144835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,19 +4716,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,12 +4733,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4758,7 +4748,7 @@
         <v>129726782</v>
       </c>
       <c r="B40" t="n">
-        <v>83050</v>
+        <v>83052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4852,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129727959</v>
+        <v>129727788</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4893,14 +4883,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488762</v>
+        <v>488989</v>
       </c>
       <c r="R41" t="n">
-        <v>7144801</v>
+        <v>7144826</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4935,6 +4925,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4947,19 +4942,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129727788</v>
+        <v>129727959</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -4990,14 +4985,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488989</v>
+        <v>488762</v>
       </c>
       <c r="R42" t="n">
-        <v>7144826</v>
+        <v>7144801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,11 +5027,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5049,22 +5039,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129716425</v>
+        <v>129726780</v>
       </c>
       <c r="B43" t="n">
-        <v>88996</v>
+        <v>83057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,34 +5062,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488829</v>
+        <v>488414</v>
       </c>
       <c r="R43" t="n">
-        <v>7144835</v>
+        <v>7144975</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5129,9 +5119,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,22 +5146,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727771</v>
+        <v>129727781</v>
       </c>
       <c r="B44" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5169,41 +5169,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488511</v>
+        <v>488586</v>
       </c>
       <c r="R44" t="n">
-        <v>7144867</v>
+        <v>7144955</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5240,7 +5233,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5249,34 +5242,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5395,10 +5362,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727799</v>
+        <v>129716437</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5406,21 +5373,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5430,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488408</v>
+        <v>488533</v>
       </c>
       <c r="R46" t="n">
-        <v>7144970</v>
+        <v>7144953</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5468,11 +5435,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5485,22 +5447,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129716437</v>
+        <v>129726775</v>
       </c>
       <c r="B47" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5508,34 +5470,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488533</v>
+        <v>488851</v>
       </c>
       <c r="R47" t="n">
-        <v>7144953</v>
+        <v>7144825</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5565,9 +5527,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5582,19 +5554,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727777</v>
+        <v>129727799</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5629,10 +5601,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488483</v>
+        <v>488408</v>
       </c>
       <c r="R48" t="n">
-        <v>7144992</v>
+        <v>7144970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5696,10 +5668,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727781</v>
+        <v>129727771</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5707,34 +5679,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488586</v>
+        <v>488511</v>
       </c>
       <c r="R49" t="n">
-        <v>7144955</v>
+        <v>7144867</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5771,7 +5750,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5780,8 +5759,34 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5798,10 +5803,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129726775</v>
+        <v>129727948</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5809,34 +5814,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488851</v>
+        <v>488739</v>
       </c>
       <c r="R50" t="n">
-        <v>7144825</v>
+        <v>7144803</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,19 +5871,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5893,22 +5888,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727948</v>
+        <v>129727770</v>
       </c>
       <c r="B51" t="n">
-        <v>91597</v>
+        <v>80187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,34 +5911,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488739</v>
+        <v>488674</v>
       </c>
       <c r="R51" t="n">
-        <v>7144803</v>
+        <v>7144814</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5978,34 +5980,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727770</v>
+        <v>129727777</v>
       </c>
       <c r="B52" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6013,41 +6046,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488674</v>
+        <v>488483</v>
       </c>
       <c r="R52" t="n">
-        <v>7144814</v>
+        <v>7144992</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6084,7 +6110,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6093,34 +6119,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6234,45 +6234,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727953</v>
+        <v>129727780</v>
       </c>
       <c r="B54" t="n">
-        <v>91979</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488400</v>
+        <v>488542</v>
       </c>
       <c r="R54" t="n">
-        <v>7144968</v>
+        <v>7144969</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,6 +6307,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6319,57 +6324,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129716447</v>
+        <v>129727953</v>
       </c>
       <c r="B55" t="n">
-        <v>83055</v>
+        <v>91981</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1467</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488731</v>
+        <v>488400</v>
       </c>
       <c r="R55" t="n">
-        <v>7144891</v>
+        <v>7144968</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,22 +6421,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6439,21 +6444,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6463,10 +6468,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R56" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6501,11 +6506,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,44 +6518,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129716428</v>
+        <v>129727791</v>
       </c>
       <c r="B57" t="n">
-        <v>92315</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489052</v>
+        <v>488907</v>
       </c>
       <c r="R57" t="n">
-        <v>7144873</v>
+        <v>7144779</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6603,6 +6603,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6615,44 +6620,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129716423</v>
+        <v>129727800</v>
       </c>
       <c r="B58" t="n">
-        <v>92315</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6662,10 +6667,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488296</v>
+        <v>488375</v>
       </c>
       <c r="R58" t="n">
-        <v>7145038</v>
+        <v>7144951</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6700,6 +6705,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6712,44 +6722,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129727791</v>
+        <v>129716428</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6759,10 +6769,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488907</v>
+        <v>489052</v>
       </c>
       <c r="R59" t="n">
-        <v>7144779</v>
+        <v>7144873</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6797,11 +6807,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6814,44 +6819,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129727800</v>
+        <v>129716423</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6861,10 +6866,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488375</v>
+        <v>488296</v>
       </c>
       <c r="R60" t="n">
-        <v>7144951</v>
+        <v>7145038</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6899,11 +6904,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6916,12 +6916,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6931,7 +6931,7 @@
         <v>129716430</v>
       </c>
       <c r="B61" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>129716440</v>
       </c>
       <c r="B62" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>129716442</v>
       </c>
       <c r="B63" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726764</v>
+        <v>129727793</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7238,14 +7238,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488646</v>
+        <v>488795</v>
       </c>
       <c r="R64" t="n">
-        <v>7144947</v>
+        <v>7144792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,19 +7275,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:36</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7302,19 +7297,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727793</v>
+        <v>129727798</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7349,10 +7344,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488795</v>
+        <v>488442</v>
       </c>
       <c r="R65" t="n">
-        <v>7144792</v>
+        <v>7145001</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7389,7 +7384,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7416,7 +7411,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129727798</v>
+        <v>129726764</v>
       </c>
       <c r="B66" t="n">
         <v>79081</v>
@@ -7447,14 +7442,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488442</v>
+        <v>488646</v>
       </c>
       <c r="R66" t="n">
-        <v>7145001</v>
+        <v>7144947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7484,14 +7479,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal flerskiktad granskog.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,19 +7506,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129716433</v>
+        <v>129727790</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488359</v>
+        <v>488911</v>
       </c>
       <c r="R67" t="n">
-        <v>7144987</v>
+        <v>7144836</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7591,6 +7591,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7603,19 +7608,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129727790</v>
+        <v>129727958</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7646,14 +7651,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488911</v>
+        <v>488796</v>
       </c>
       <c r="R68" t="n">
-        <v>7144836</v>
+        <v>7144792</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7688,11 +7693,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7705,19 +7705,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129727787</v>
+        <v>129716433</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>489024</v>
+        <v>488359</v>
       </c>
       <c r="R69" t="n">
-        <v>7144841</v>
+        <v>7144987</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7790,11 +7790,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7807,19 +7802,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129727958</v>
+        <v>129716432</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7850,14 +7845,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488796</v>
+        <v>489065</v>
       </c>
       <c r="R70" t="n">
-        <v>7144792</v>
+        <v>7144852</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7892,6 +7887,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7904,19 +7904,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129716432</v>
+        <v>129727787</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489065</v>
+        <v>489024</v>
       </c>
       <c r="R71" t="n">
-        <v>7144852</v>
+        <v>7144841</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8006,22 +8006,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129727954</v>
+        <v>129727778</v>
       </c>
       <c r="B72" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489143</v>
+        <v>488513</v>
       </c>
       <c r="R72" t="n">
-        <v>7144773</v>
+        <v>7144973</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8091,6 +8091,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8103,22 +8108,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129716429</v>
+        <v>129727951</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>91897</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8126,34 +8131,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488440</v>
+        <v>489112</v>
       </c>
       <c r="R73" t="n">
-        <v>7144976</v>
+        <v>7144780</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8200,22 +8205,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129727778</v>
+        <v>129727954</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,34 +8228,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488513</v>
+        <v>489143</v>
       </c>
       <c r="R74" t="n">
-        <v>7144973</v>
+        <v>7144773</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8285,11 +8290,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8302,19 +8302,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726779</v>
+        <v>129726778</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488452</v>
+        <v>488522</v>
       </c>
       <c r="R75" t="n">
-        <v>7144979</v>
+        <v>7144974</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8421,7 +8421,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129726778</v>
+        <v>129716429</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8452,14 +8452,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488522</v>
+        <v>488440</v>
       </c>
       <c r="R76" t="n">
-        <v>7144974</v>
+        <v>7144976</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8489,19 +8489,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8516,22 +8506,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129727951</v>
+        <v>129726779</v>
       </c>
       <c r="B77" t="n">
-        <v>91895</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8539,34 +8529,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489112</v>
+        <v>488452</v>
       </c>
       <c r="R77" t="n">
-        <v>7144780</v>
+        <v>7144979</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8596,9 +8586,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
         <v>129716424</v>
       </c>
       <c r="B78" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8829,10 +8829,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716434</v>
+        <v>129716445</v>
       </c>
       <c r="B80" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8840,21 +8840,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488618</v>
+        <v>488685</v>
       </c>
       <c r="R80" t="n">
-        <v>7144922</v>
+        <v>7144909</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8926,10 +8926,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727769</v>
+        <v>129716434</v>
       </c>
       <c r="B81" t="n">
-        <v>80187</v>
+        <v>91595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,41 +8937,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488758</v>
+        <v>488618</v>
       </c>
       <c r="R81" t="n">
-        <v>7144774</v>
+        <v>7144922</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9006,65 +8999,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727957</v>
+        <v>129727769</v>
       </c>
       <c r="B82" t="n">
-        <v>91593</v>
+        <v>80187</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9072,34 +9034,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488591</v>
+        <v>488758</v>
       </c>
       <c r="R82" t="n">
-        <v>7144844</v>
+        <v>7144774</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9134,34 +9103,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716445</v>
+        <v>129727957</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,34 +9169,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488685</v>
+        <v>488591</v>
       </c>
       <c r="R83" t="n">
-        <v>7144909</v>
+        <v>7144844</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9243,12 +9243,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726773</v>
+        <v>129727960</v>
       </c>
       <c r="B87" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489020</v>
+        <v>488374</v>
       </c>
       <c r="R87" t="n">
-        <v>7144867</v>
+        <v>7144949</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,19 +9652,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9679,22 +9674,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727795</v>
+        <v>129726773</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9702,34 +9697,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488737</v>
+        <v>489020</v>
       </c>
       <c r="R88" t="n">
-        <v>7144797</v>
+        <v>7144867</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9759,14 +9754,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På en levande gammal gran.</t>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9781,19 +9781,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727794</v>
+        <v>129727795</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488763</v>
+        <v>488737</v>
       </c>
       <c r="R89" t="n">
-        <v>7144775</v>
+        <v>7144797</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9895,45 +9895,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129726769</v>
+        <v>129727794</v>
       </c>
       <c r="B90" t="n">
-        <v>75065</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>489064</v>
+        <v>488763</v>
       </c>
       <c r="R90" t="n">
-        <v>7144843</v>
+        <v>7144775</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9963,19 +9963,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9986,38 +9981,23 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727960</v>
+        <v>129727783</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -10048,14 +10028,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488374</v>
+        <v>488709</v>
       </c>
       <c r="R91" t="n">
-        <v>7144949</v>
+        <v>7144911</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10092,7 +10072,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10107,57 +10087,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129727783</v>
+        <v>129726769</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>75065</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488709</v>
+        <v>489064</v>
       </c>
       <c r="R92" t="n">
-        <v>7144911</v>
+        <v>7144843</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10187,14 +10167,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På levande gran i gammal granskog.</t>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10205,26 +10190,41 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R93" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,19 +10289,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10339,34 +10329,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R94" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10396,9 +10386,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,44 +10413,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R95" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,27 +10522,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730469</v>
+        <v>129730439</v>
       </c>
       <c r="B96" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488507</v>
+        <v>488746</v>
       </c>
       <c r="R96" t="n">
-        <v>7144936</v>
+        <v>7144786</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10602,7 +10597,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10629,10 +10624,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730462</v>
+        <v>129730469</v>
       </c>
       <c r="B97" t="n">
-        <v>92315</v>
+        <v>57840</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10640,21 +10635,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10664,10 +10659,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489017</v>
+        <v>488507</v>
       </c>
       <c r="R97" t="n">
-        <v>7144821</v>
+        <v>7144936</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10700,6 +10695,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10729,7 +10729,7 @@
         <v>129730460</v>
       </c>
       <c r="B98" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>129730457</v>
       </c>
       <c r="B99" t="n">
-        <v>91968</v>
+        <v>91970</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>129730473</v>
       </c>
       <c r="B101" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>129730474</v>
       </c>
       <c r="B102" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730451</v>
+        <v>129730461</v>
       </c>
       <c r="B104" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488709</v>
+        <v>488464</v>
       </c>
       <c r="R104" t="n">
-        <v>7144786</v>
+        <v>7144953</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730461</v>
+        <v>129730451</v>
       </c>
       <c r="B105" t="n">
-        <v>91597</v>
+        <v>80186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488464</v>
+        <v>488709</v>
       </c>
       <c r="R105" t="n">
-        <v>7144953</v>
+        <v>7144786</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B109" t="n">
-        <v>91611</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R109" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,6 +11874,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11900,10 +11905,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11911,21 +11916,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11935,10 +11940,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R110" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11971,11 +11976,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12204,7 +12204,7 @@
         <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>129730470</v>
       </c>
       <c r="B115" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>129730458</v>
       </c>
       <c r="B118" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>129730471</v>
       </c>
       <c r="B119" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>129730476</v>
       </c>
       <c r="B120" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>129730456</v>
       </c>
       <c r="B121" t="n">
-        <v>91968</v>
+        <v>91970</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>129730459</v>
       </c>
       <c r="B122" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>129730478</v>
       </c>
       <c r="B123" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>83050</v>
+        <v>83052</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B127" t="n">
-        <v>83055</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R127" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B128" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R128" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13759,32 +13759,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730472</v>
+        <v>129730440</v>
       </c>
       <c r="B129" t="n">
-        <v>91593</v>
+        <v>56926</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488622</v>
+        <v>489134</v>
       </c>
       <c r="R129" t="n">
-        <v>7144899</v>
+        <v>7144763</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13830,6 +13830,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13856,10 +13861,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730475</v>
+        <v>129730472</v>
       </c>
       <c r="B130" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13891,10 +13896,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488459</v>
+        <v>488622</v>
       </c>
       <c r="R130" t="n">
-        <v>7144958</v>
+        <v>7144899</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13953,32 +13958,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730440</v>
+        <v>129730475</v>
       </c>
       <c r="B131" t="n">
-        <v>56926</v>
+        <v>91595</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13988,10 +13993,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489134</v>
+        <v>488459</v>
       </c>
       <c r="R131" t="n">
-        <v>7144763</v>
+        <v>7144958</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14024,11 +14029,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727797</v>
+        <v>129727955</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488482</v>
+        <v>489154</v>
       </c>
       <c r="R3" t="n">
-        <v>7144891</v>
+        <v>7144751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,11 +845,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -862,51 +857,51 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727766</v>
+        <v>129727773</v>
       </c>
       <c r="B4" t="n">
-        <v>80215</v>
+        <v>91595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -916,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488676</v>
+        <v>488610</v>
       </c>
       <c r="R4" t="n">
-        <v>7144814</v>
+        <v>7144833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,7 +951,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,22 +971,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1009,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727955</v>
+        <v>129726770</v>
       </c>
       <c r="B5" t="n">
-        <v>91595</v>
+        <v>80187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489154</v>
+        <v>489064</v>
       </c>
       <c r="R5" t="n">
-        <v>7144751</v>
+        <v>7144843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1072,21 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1090,26 +1095,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129727773</v>
+        <v>129726758</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>82918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,41 +1137,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488610</v>
+        <v>488417</v>
       </c>
       <c r="R6" t="n">
-        <v>7144833</v>
+        <v>7145102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,14 +1194,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,54 +1215,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726770</v>
+        <v>129727797</v>
       </c>
       <c r="B7" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,34 +1244,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489064</v>
+        <v>488482</v>
       </c>
       <c r="R7" t="n">
-        <v>7144843</v>
+        <v>7144891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,19 +1301,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,76 +1319,68 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726758</v>
+        <v>129727766</v>
       </c>
       <c r="B8" t="n">
-        <v>82918</v>
+        <v>80215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488417</v>
+        <v>488676</v>
       </c>
       <c r="R8" t="n">
-        <v>7145102</v>
+        <v>7144814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,19 +1410,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,18 +1426,44 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727801</v>
+        <v>129727796</v>
       </c>
       <c r="B11" t="n">
         <v>79081</v>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488339</v>
+        <v>488507</v>
       </c>
       <c r="R11" t="n">
-        <v>7144937</v>
+        <v>7144870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727776</v>
+        <v>129726781</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,34 +1777,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488425</v>
+        <v>488365</v>
       </c>
       <c r="R12" t="n">
-        <v>7145015</v>
+        <v>7144983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,14 +1834,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,64 +1861,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727765</v>
+        <v>129727801</v>
       </c>
       <c r="B13" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488701</v>
+        <v>488339</v>
       </c>
       <c r="R13" t="n">
-        <v>7144801</v>
+        <v>7144937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,34 +1957,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2003,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129726761</v>
+        <v>129727776</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -2034,14 +2006,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488516</v>
+        <v>488425</v>
       </c>
       <c r="R14" t="n">
-        <v>7145014</v>
+        <v>7145015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,19 +2043,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,19 +2065,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727782</v>
+        <v>129726761</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2141,14 +2108,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488694</v>
+        <v>488516</v>
       </c>
       <c r="R15" t="n">
-        <v>7144925</v>
+        <v>7145014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,14 +2145,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på björk.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,19 +2172,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727796</v>
+        <v>129727782</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2247,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488507</v>
+        <v>488694</v>
       </c>
       <c r="R16" t="n">
-        <v>7144870</v>
+        <v>7144925</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,7 +2259,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,45 +2286,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726781</v>
+        <v>129727765</v>
       </c>
       <c r="B17" t="n">
-        <v>78094</v>
+        <v>80215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488365</v>
+        <v>488701</v>
       </c>
       <c r="R17" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,19 +2361,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,18 +2377,44 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129716436</v>
+        <v>129726760</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,34 +3726,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489031</v>
+        <v>488426</v>
       </c>
       <c r="R30" t="n">
-        <v>7144903</v>
+        <v>7145052</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,9 +3783,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3800,19 +3810,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129727792</v>
+        <v>129726763</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3843,14 +3853,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488815</v>
+        <v>488626</v>
       </c>
       <c r="R31" t="n">
-        <v>7144788</v>
+        <v>7145010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3880,14 +3890,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3902,22 +3917,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726763</v>
+        <v>129727945</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3925,34 +3940,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488626</v>
+        <v>489010</v>
       </c>
       <c r="R32" t="n">
-        <v>7145010</v>
+        <v>7144808</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3982,49 +4000,40 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726760</v>
+        <v>129716436</v>
       </c>
       <c r="B33" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,34 +4041,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488426</v>
+        <v>489031</v>
       </c>
       <c r="R33" t="n">
-        <v>7145052</v>
+        <v>7144903</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4089,19 +4098,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4116,22 +4115,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727945</v>
+        <v>129727792</v>
       </c>
       <c r="B34" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4139,37 +4138,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489010</v>
+        <v>488815</v>
       </c>
       <c r="R34" t="n">
-        <v>7144808</v>
+        <v>7144788</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4204,25 +4200,29 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129727778</v>
+        <v>129727951</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>91897</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488513</v>
+        <v>489112</v>
       </c>
       <c r="R72" t="n">
-        <v>7144973</v>
+        <v>7144780</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8091,11 +8091,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8108,22 +8103,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129727951</v>
+        <v>129726778</v>
       </c>
       <c r="B73" t="n">
-        <v>91897</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8131,34 +8126,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489112</v>
+        <v>488522</v>
       </c>
       <c r="R73" t="n">
-        <v>7144780</v>
+        <v>7144974</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8188,9 +8183,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8205,22 +8210,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129727954</v>
+        <v>129716429</v>
       </c>
       <c r="B74" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8228,34 +8233,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489143</v>
+        <v>488440</v>
       </c>
       <c r="R74" t="n">
-        <v>7144773</v>
+        <v>7144976</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8302,19 +8307,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726778</v>
+        <v>129726779</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8349,10 +8354,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488522</v>
+        <v>488452</v>
       </c>
       <c r="R75" t="n">
-        <v>7144974</v>
+        <v>7144979</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8384,7 +8389,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8394,7 +8399,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8421,7 +8426,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129716429</v>
+        <v>129727778</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8456,10 +8461,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488440</v>
+        <v>488513</v>
       </c>
       <c r="R76" t="n">
-        <v>7144976</v>
+        <v>7144973</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8494,6 +8499,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8506,22 +8516,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726779</v>
+        <v>129727954</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,34 +8539,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488452</v>
+        <v>489143</v>
       </c>
       <c r="R77" t="n">
-        <v>7144979</v>
+        <v>7144773</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8586,19 +8596,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726777</v>
+        <v>129716434</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,34 +8733,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488570</v>
+        <v>488618</v>
       </c>
       <c r="R79" t="n">
-        <v>7144960</v>
+        <v>7144922</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8790,19 +8790,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8817,22 +8807,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716445</v>
+        <v>129727769</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8840,34 +8830,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488685</v>
+        <v>488758</v>
       </c>
       <c r="R80" t="n">
-        <v>7144909</v>
+        <v>7144774</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8902,31 +8899,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129716434</v>
+        <v>129727957</v>
       </c>
       <c r="B81" t="n">
         <v>91595</v>
@@ -8957,14 +8985,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488618</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7144922</v>
+        <v>7144844</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9011,22 +9039,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727769</v>
+        <v>129716441</v>
       </c>
       <c r="B82" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9034,41 +9062,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488758</v>
+        <v>488921</v>
       </c>
       <c r="R82" t="n">
-        <v>7144774</v>
+        <v>7144886</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9103,65 +9124,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129727957</v>
+        <v>129716422</v>
       </c>
       <c r="B83" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9169,34 +9159,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488591</v>
+        <v>488767</v>
       </c>
       <c r="R83" t="n">
-        <v>7144844</v>
+        <v>7144853</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9243,57 +9233,64 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129716441</v>
+        <v>129727767</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488921</v>
+        <v>488658</v>
       </c>
       <c r="R84" t="n">
-        <v>7144886</v>
+        <v>7144806</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9328,31 +9325,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129716422</v>
+        <v>129726777</v>
       </c>
       <c r="B85" t="n">
         <v>79081</v>
@@ -9383,14 +9411,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488767</v>
+        <v>488570</v>
       </c>
       <c r="R85" t="n">
-        <v>7144853</v>
+        <v>7144960</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9420,9 +9448,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9437,64 +9475,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727767</v>
+        <v>129716445</v>
       </c>
       <c r="B86" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488658</v>
+        <v>488685</v>
       </c>
       <c r="R86" t="n">
-        <v>7144806</v>
+        <v>7144909</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9529,55 +9560,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9686,32 +9686,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129726773</v>
+        <v>129726769</v>
       </c>
       <c r="B88" t="n">
-        <v>91599</v>
+        <v>75065</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489020</v>
+        <v>489064</v>
       </c>
       <c r="R88" t="n">
-        <v>7144867</v>
+        <v>7144843</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9777,6 +9777,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -9793,10 +9808,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727795</v>
+        <v>129726773</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9804,34 +9819,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488737</v>
+        <v>489020</v>
       </c>
       <c r="R89" t="n">
-        <v>7144797</v>
+        <v>7144867</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9861,14 +9876,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På en levande gammal gran.</t>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9883,19 +9903,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727794</v>
+        <v>129727795</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9930,10 +9950,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488763</v>
+        <v>488737</v>
       </c>
       <c r="R90" t="n">
-        <v>7144775</v>
+        <v>7144797</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9990,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9997,7 +10017,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727783</v>
+        <v>129727794</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -10032,10 +10052,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488709</v>
+        <v>488763</v>
       </c>
       <c r="R91" t="n">
-        <v>7144911</v>
+        <v>7144775</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10072,7 +10092,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10099,45 +10119,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726769</v>
+        <v>129727783</v>
       </c>
       <c r="B92" t="n">
-        <v>75065</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489064</v>
+        <v>488709</v>
       </c>
       <c r="R92" t="n">
-        <v>7144843</v>
+        <v>7144911</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10167,19 +10187,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10190,31 +10205,16 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10425,32 +10425,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730462</v>
+        <v>129730439</v>
       </c>
       <c r="B95" t="n">
-        <v>92317</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489017</v>
+        <v>488746</v>
       </c>
       <c r="R95" t="n">
-        <v>7144821</v>
+        <v>7144786</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,6 +10496,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10522,32 +10527,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R96" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10593,11 +10598,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R109" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,11 +11874,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,10 +11900,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B110" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11916,21 +11911,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11940,10 +11935,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R110" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,6 +11971,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727955</v>
+        <v>129727797</v>
       </c>
       <c r="B3" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489154</v>
+        <v>488482</v>
       </c>
       <c r="R3" t="n">
-        <v>7144751</v>
+        <v>7144891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,6 +845,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -857,51 +862,51 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727773</v>
+        <v>129727766</v>
       </c>
       <c r="B4" t="n">
-        <v>91595</v>
+        <v>80215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -911,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488610</v>
+        <v>488676</v>
       </c>
       <c r="R4" t="n">
-        <v>7144833</v>
+        <v>7144814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,7 +956,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,22 +976,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726770</v>
+        <v>129727955</v>
       </c>
       <c r="B5" t="n">
-        <v>80187</v>
+        <v>91595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,34 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489064</v>
+        <v>489154</v>
       </c>
       <c r="R5" t="n">
-        <v>7144843</v>
+        <v>7144751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,21 +1077,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1095,41 +1090,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726758</v>
+        <v>129727773</v>
       </c>
       <c r="B6" t="n">
-        <v>82918</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,34 +1117,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488417</v>
+        <v>488610</v>
       </c>
       <c r="R6" t="n">
-        <v>7145102</v>
+        <v>7144833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,19 +1181,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,28 +1197,54 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727797</v>
+        <v>129726770</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,34 +1252,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488482</v>
+        <v>489064</v>
       </c>
       <c r="R7" t="n">
-        <v>7144891</v>
+        <v>7144843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,14 +1309,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,68 +1332,76 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129727766</v>
+        <v>129726758</v>
       </c>
       <c r="B8" t="n">
-        <v>80215</v>
+        <v>82918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488676</v>
+        <v>488417</v>
       </c>
       <c r="R8" t="n">
-        <v>7144814</v>
+        <v>7145102</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,14 +1431,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,44 +1452,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B27" t="n">
-        <v>80187</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,41 +3387,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R27" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,65 +3454,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727786</v>
+        <v>129727772</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,34 +3489,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489035</v>
+        <v>488470</v>
       </c>
       <c r="R28" t="n">
-        <v>7144832</v>
+        <v>7144960</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3586,7 +3560,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,8 +3569,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,39 +3624,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R29" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,6 +3686,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3703,12 +3703,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129727802</v>
+        <v>129726784</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488268</v>
+        <v>488335</v>
       </c>
       <c r="R35" t="n">
-        <v>7145078</v>
+        <v>7144978</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,14 +4297,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,22 +4324,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726784</v>
+        <v>129726765</v>
       </c>
       <c r="B36" t="n">
-        <v>83044</v>
+        <v>82918</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4342,21 +4347,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4366,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488335</v>
+        <v>488725</v>
       </c>
       <c r="R36" t="n">
-        <v>7144978</v>
+        <v>7144925</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4401,7 +4406,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4411,7 +4416,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726765</v>
+        <v>129726771</v>
       </c>
       <c r="B37" t="n">
-        <v>82918</v>
+        <v>91619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,23 +4454,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4473,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488725</v>
+        <v>489056</v>
       </c>
       <c r="R37" t="n">
-        <v>7144925</v>
+        <v>7144853</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4508,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4518,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4545,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726771</v>
+        <v>129727802</v>
       </c>
       <c r="B38" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4556,30 +4557,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489056</v>
+        <v>488268</v>
       </c>
       <c r="R38" t="n">
-        <v>7144853</v>
+        <v>7145078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,19 +4614,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:58</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,12 +4636,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727781</v>
+        <v>129727799</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488586</v>
+        <v>488408</v>
       </c>
       <c r="R44" t="n">
-        <v>7144955</v>
+        <v>7144970</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727785</v>
+        <v>129727771</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5271,34 +5271,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488865</v>
+        <v>488511</v>
       </c>
       <c r="R45" t="n">
-        <v>7144860</v>
+        <v>7144867</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5335,7 +5342,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5344,8 +5351,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5362,10 +5395,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129716437</v>
+        <v>129727948</v>
       </c>
       <c r="B46" t="n">
-        <v>83052</v>
+        <v>91599</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,34 +5406,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488533</v>
+        <v>488739</v>
       </c>
       <c r="R46" t="n">
-        <v>7144953</v>
+        <v>7144803</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5447,22 +5480,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129726775</v>
+        <v>129727770</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5470,34 +5503,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488851</v>
+        <v>488674</v>
       </c>
       <c r="R47" t="n">
-        <v>7144825</v>
+        <v>7144814</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5527,19 +5567,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5548,25 +5583,51 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727799</v>
+        <v>129727781</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5601,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488408</v>
+        <v>488586</v>
       </c>
       <c r="R48" t="n">
-        <v>7144970</v>
+        <v>7144955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5668,10 +5729,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727771</v>
+        <v>129727785</v>
       </c>
       <c r="B49" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5679,41 +5740,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488511</v>
+        <v>488865</v>
       </c>
       <c r="R49" t="n">
-        <v>7144867</v>
+        <v>7144860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5750,7 +5804,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5759,34 +5813,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5803,10 +5831,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727948</v>
+        <v>129716437</v>
       </c>
       <c r="B50" t="n">
-        <v>91599</v>
+        <v>83052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5814,34 +5842,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488739</v>
+        <v>488533</v>
       </c>
       <c r="R50" t="n">
-        <v>7144803</v>
+        <v>7144953</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,22 +5916,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727770</v>
+        <v>129726775</v>
       </c>
       <c r="B51" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5911,41 +5939,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488674</v>
+        <v>488851</v>
       </c>
       <c r="R51" t="n">
-        <v>7144814</v>
+        <v>7144825</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5975,14 +5996,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5991,44 +6017,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B109" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R109" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,6 +11874,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11900,10 +11905,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11911,21 +11916,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11935,10 +11940,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R110" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11971,11 +11976,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13759,32 +13759,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730440</v>
+        <v>129730472</v>
       </c>
       <c r="B129" t="n">
-        <v>56926</v>
+        <v>91595</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>489134</v>
+        <v>488622</v>
       </c>
       <c r="R129" t="n">
-        <v>7144763</v>
+        <v>7144899</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13830,11 +13830,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13861,7 +13856,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730472</v>
+        <v>129730475</v>
       </c>
       <c r="B130" t="n">
         <v>91595</v>
@@ -13896,10 +13891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488622</v>
+        <v>488459</v>
       </c>
       <c r="R130" t="n">
-        <v>7144899</v>
+        <v>7144958</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13958,32 +13953,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730475</v>
+        <v>129730440</v>
       </c>
       <c r="B131" t="n">
-        <v>91595</v>
+        <v>56926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13993,10 +13988,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488459</v>
+        <v>489134</v>
       </c>
       <c r="R131" t="n">
-        <v>7144958</v>
+        <v>7144763</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14029,6 +14024,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -4229,10 +4229,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726784</v>
+        <v>129727802</v>
       </c>
       <c r="B35" t="n">
-        <v>83044</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488335</v>
+        <v>488268</v>
       </c>
       <c r="R35" t="n">
-        <v>7144978</v>
+        <v>7145078</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,19 +4297,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,22 +4319,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726765</v>
+        <v>129726784</v>
       </c>
       <c r="B36" t="n">
-        <v>82918</v>
+        <v>83044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,21 +4342,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4371,10 +4366,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488725</v>
+        <v>488335</v>
       </c>
       <c r="R36" t="n">
-        <v>7144925</v>
+        <v>7144978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,7 +4401,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4416,7 +4411,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,10 +4438,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726771</v>
+        <v>129726765</v>
       </c>
       <c r="B37" t="n">
-        <v>91619</v>
+        <v>82918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,19 +4449,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4474,10 +4473,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489056</v>
+        <v>488725</v>
       </c>
       <c r="R37" t="n">
-        <v>7144853</v>
+        <v>7144925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4508,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4518,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,10 +4545,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129727802</v>
+        <v>129726771</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,34 +4556,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488268</v>
+        <v>489056</v>
       </c>
       <c r="R38" t="n">
-        <v>7145078</v>
+        <v>7144853</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,14 +4609,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,12 +4636,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129727790</v>
+        <v>129727958</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7549,14 +7549,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488911</v>
+        <v>488796</v>
       </c>
       <c r="R67" t="n">
-        <v>7144836</v>
+        <v>7144792</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7591,11 +7591,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7608,19 +7603,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129727958</v>
+        <v>129716433</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7651,14 +7646,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488796</v>
+        <v>488359</v>
       </c>
       <c r="R68" t="n">
-        <v>7144792</v>
+        <v>7144987</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7705,19 +7700,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129716433</v>
+        <v>129727790</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7752,10 +7747,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488359</v>
+        <v>488911</v>
       </c>
       <c r="R69" t="n">
-        <v>7144987</v>
+        <v>7144836</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7790,6 +7785,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7802,12 +7802,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -13759,32 +13759,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730472</v>
+        <v>129730440</v>
       </c>
       <c r="B129" t="n">
-        <v>91595</v>
+        <v>56926</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488622</v>
+        <v>489134</v>
       </c>
       <c r="R129" t="n">
-        <v>7144899</v>
+        <v>7144763</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13830,6 +13830,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13856,7 +13861,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730475</v>
+        <v>129730472</v>
       </c>
       <c r="B130" t="n">
         <v>91595</v>
@@ -13891,10 +13896,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488459</v>
+        <v>488622</v>
       </c>
       <c r="R130" t="n">
-        <v>7144958</v>
+        <v>7144899</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13953,32 +13958,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730440</v>
+        <v>129730475</v>
       </c>
       <c r="B131" t="n">
-        <v>56926</v>
+        <v>91595</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13988,10 +13993,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489134</v>
+        <v>488459</v>
       </c>
       <c r="R131" t="n">
-        <v>7144763</v>
+        <v>7144958</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14024,11 +14029,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129716427</v>
+        <v>129727955</v>
       </c>
       <c r="B2" t="n">
-        <v>83044</v>
+        <v>91595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488400</v>
+        <v>489154</v>
       </c>
       <c r="R2" t="n">
-        <v>7144977</v>
+        <v>7144751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727797</v>
+        <v>129727773</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488482</v>
+        <v>488610</v>
       </c>
       <c r="R3" t="n">
-        <v>7144891</v>
+        <v>7144833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +854,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran i flerskiktad granskog.</t>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -856,8 +863,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -874,52 +907,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727766</v>
+        <v>129716427</v>
       </c>
       <c r="B4" t="n">
-        <v>80215</v>
+        <v>83044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488676</v>
+        <v>488400</v>
       </c>
       <c r="R4" t="n">
-        <v>7144814</v>
+        <v>7144977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,65 +980,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727955</v>
+        <v>129726770</v>
       </c>
       <c r="B5" t="n">
-        <v>91595</v>
+        <v>80187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489154</v>
+        <v>489064</v>
       </c>
       <c r="R5" t="n">
-        <v>7144751</v>
+        <v>7144843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1072,21 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1090,26 +1095,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129727773</v>
+        <v>129726758</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>82918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,41 +1137,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488610</v>
+        <v>488417</v>
       </c>
       <c r="R6" t="n">
-        <v>7144833</v>
+        <v>7145102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,14 +1194,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,89 +1215,70 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726770</v>
+        <v>129727766</v>
       </c>
       <c r="B7" t="n">
-        <v>80187</v>
+        <v>80215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489064</v>
+        <v>488676</v>
       </c>
       <c r="R7" t="n">
-        <v>7144843</v>
+        <v>7144814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,19 +1308,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,43 +1324,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726758</v>
+        <v>129727797</v>
       </c>
       <c r="B8" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,34 +1379,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488417</v>
+        <v>488482</v>
       </c>
       <c r="R8" t="n">
-        <v>7145102</v>
+        <v>7144891</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,19 +1436,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,12 +1458,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727796</v>
+        <v>129726781</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>78094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,34 +1675,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488507</v>
+        <v>488365</v>
       </c>
       <c r="R11" t="n">
-        <v>7144870</v>
+        <v>7144983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,14 +1732,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,22 +1759,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726781</v>
+        <v>129727776</v>
       </c>
       <c r="B12" t="n">
-        <v>78094</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,34 +1782,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488365</v>
+        <v>488425</v>
       </c>
       <c r="R12" t="n">
-        <v>7144983</v>
+        <v>7145015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,19 +1839,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,19 +1861,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727801</v>
+        <v>129726761</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -1904,14 +1904,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488339</v>
+        <v>488516</v>
       </c>
       <c r="R13" t="n">
-        <v>7144937</v>
+        <v>7145014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,14 +1941,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,19 +1968,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727776</v>
+        <v>129727801</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -2010,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488425</v>
+        <v>488339</v>
       </c>
       <c r="R14" t="n">
-        <v>7145015</v>
+        <v>7144937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2055,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,7 +2082,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129726761</v>
+        <v>129727782</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2108,14 +2113,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488516</v>
+        <v>488694</v>
       </c>
       <c r="R15" t="n">
-        <v>7145014</v>
+        <v>7144925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,19 +2150,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,19 +2172,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727782</v>
+        <v>129727796</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488694</v>
+        <v>488507</v>
       </c>
       <c r="R16" t="n">
-        <v>7144925</v>
+        <v>7144870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129716435</v>
+        <v>129727772</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>80187</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,39 +3387,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488832</v>
+        <v>488470</v>
       </c>
       <c r="R27" t="n">
-        <v>7144827</v>
+        <v>7144960</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,34 +3456,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B28" t="n">
-        <v>80187</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,41 +3522,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R28" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3558,55 +3589,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129726760</v>
+        <v>129727945</v>
       </c>
       <c r="B30" t="n">
-        <v>88998</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,34 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488426</v>
+        <v>489010</v>
       </c>
       <c r="R30" t="n">
-        <v>7145052</v>
+        <v>7144808</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,49 +3786,40 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726763</v>
+        <v>129726760</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,21 +3827,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488626</v>
+        <v>488426</v>
       </c>
       <c r="R31" t="n">
-        <v>7145010</v>
+        <v>7145052</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3892,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3902,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,10 +3923,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129727945</v>
+        <v>129726763</v>
       </c>
       <c r="B32" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,37 +3934,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489010</v>
+        <v>488626</v>
       </c>
       <c r="R32" t="n">
-        <v>7144808</v>
+        <v>7145010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,30 +3991,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129727802</v>
+        <v>129726784</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488268</v>
+        <v>488335</v>
       </c>
       <c r="R35" t="n">
-        <v>7145078</v>
+        <v>7144978</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,14 +4297,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,22 +4324,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726784</v>
+        <v>129726771</v>
       </c>
       <c r="B36" t="n">
-        <v>83044</v>
+        <v>91619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4342,23 +4347,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4366,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488335</v>
+        <v>489056</v>
       </c>
       <c r="R36" t="n">
-        <v>7144978</v>
+        <v>7144853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4401,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4411,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4438,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726765</v>
+        <v>129727802</v>
       </c>
       <c r="B37" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,34 +4450,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488725</v>
+        <v>488268</v>
       </c>
       <c r="R37" t="n">
-        <v>7144925</v>
+        <v>7145078</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4506,19 +4507,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4533,22 +4529,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726771</v>
+        <v>129726765</v>
       </c>
       <c r="B38" t="n">
-        <v>91619</v>
+        <v>82918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4556,19 +4552,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>489056</v>
+        <v>488725</v>
       </c>
       <c r="R38" t="n">
-        <v>7144853</v>
+        <v>7144925</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129716425</v>
+        <v>129726782</v>
       </c>
       <c r="B39" t="n">
-        <v>88998</v>
+        <v>83052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488829</v>
+        <v>488365</v>
       </c>
       <c r="R39" t="n">
-        <v>7144835</v>
+        <v>7144983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,9 +4716,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4733,22 +4743,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129726782</v>
+        <v>129727959</v>
       </c>
       <c r="B40" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4756,34 +4766,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488365</v>
+        <v>488762</v>
       </c>
       <c r="R40" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4813,19 +4823,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4840,12 +4840,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4954,10 +4954,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129727959</v>
+        <v>129726780</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,34 +4965,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488762</v>
+        <v>488414</v>
       </c>
       <c r="R42" t="n">
-        <v>7144801</v>
+        <v>7144975</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,9 +5022,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5039,22 +5049,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726780</v>
+        <v>129716425</v>
       </c>
       <c r="B43" t="n">
-        <v>83057</v>
+        <v>88998</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,34 +5072,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488414</v>
+        <v>488829</v>
       </c>
       <c r="R43" t="n">
-        <v>7144975</v>
+        <v>7144835</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5119,19 +5129,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,22 +5146,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727799</v>
+        <v>129727948</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488408</v>
+        <v>488739</v>
       </c>
       <c r="R44" t="n">
-        <v>7144970</v>
+        <v>7144803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,11 +5231,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5248,12 +5243,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5395,10 +5390,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727948</v>
+        <v>129727770</v>
       </c>
       <c r="B46" t="n">
-        <v>91599</v>
+        <v>80187</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5406,34 +5401,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488739</v>
+        <v>488674</v>
       </c>
       <c r="R46" t="n">
-        <v>7144803</v>
+        <v>7144814</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5468,34 +5470,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727770</v>
+        <v>129727781</v>
       </c>
       <c r="B47" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5503,41 +5536,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488674</v>
+        <v>488586</v>
       </c>
       <c r="R47" t="n">
-        <v>7144814</v>
+        <v>7144955</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5574,7 +5600,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5583,34 +5609,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5627,7 +5627,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727781</v>
+        <v>129727785</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488586</v>
+        <v>488865</v>
       </c>
       <c r="R48" t="n">
-        <v>7144955</v>
+        <v>7144860</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5729,7 +5729,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727785</v>
+        <v>129727799</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5764,10 +5764,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488865</v>
+        <v>488408</v>
       </c>
       <c r="R49" t="n">
-        <v>7144860</v>
+        <v>7144970</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6137,45 +6137,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716431</v>
+        <v>129727953</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>91981</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488426</v>
+        <v>488400</v>
       </c>
       <c r="R53" t="n">
-        <v>7145034</v>
+        <v>7144968</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R54" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,11 +6307,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6324,57 +6319,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727953</v>
+        <v>129716431</v>
       </c>
       <c r="B55" t="n">
-        <v>91981</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488400</v>
+        <v>488426</v>
       </c>
       <c r="R55" t="n">
-        <v>7144968</v>
+        <v>7145034</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6421,22 +6416,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716447</v>
+        <v>129727780</v>
       </c>
       <c r="B56" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6444,21 +6439,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6468,10 +6463,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488731</v>
+        <v>488542</v>
       </c>
       <c r="R56" t="n">
-        <v>7144891</v>
+        <v>7144969</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6506,6 +6501,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,22 +6518,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727791</v>
+        <v>129716430</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,23 +6541,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6565,10 +6561,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488907</v>
+        <v>488835</v>
       </c>
       <c r="R57" t="n">
-        <v>7144779</v>
+        <v>7144824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6603,11 +6599,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6620,22 +6611,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129727800</v>
+        <v>129716440</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>91619</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6643,23 +6634,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6667,10 +6654,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488375</v>
+        <v>488547</v>
       </c>
       <c r="R58" t="n">
-        <v>7144951</v>
+        <v>7144971</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,11 +6692,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6722,46 +6704,42 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716428</v>
+        <v>129716442</v>
       </c>
       <c r="B59" t="n">
-        <v>92317</v>
+        <v>91619</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6769,10 +6747,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489052</v>
+        <v>488630</v>
       </c>
       <c r="R59" t="n">
-        <v>7144873</v>
+        <v>7145015</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6831,7 +6809,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716423</v>
+        <v>129716428</v>
       </c>
       <c r="B60" t="n">
         <v>92317</v>
@@ -6866,10 +6844,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488296</v>
+        <v>489052</v>
       </c>
       <c r="R60" t="n">
-        <v>7145038</v>
+        <v>7144873</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6928,30 +6906,34 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716430</v>
+        <v>129716423</v>
       </c>
       <c r="B61" t="n">
-        <v>91619</v>
+        <v>92317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6959,10 +6941,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488835</v>
+        <v>488296</v>
       </c>
       <c r="R61" t="n">
-        <v>7144824</v>
+        <v>7145038</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,10 +7003,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129716440</v>
+        <v>129727800</v>
       </c>
       <c r="B62" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7032,19 +7014,23 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7052,10 +7038,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488547</v>
+        <v>488375</v>
       </c>
       <c r="R62" t="n">
-        <v>7144971</v>
+        <v>7144951</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7090,6 +7076,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7102,22 +7093,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129716442</v>
+        <v>129727791</v>
       </c>
       <c r="B63" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7125,19 +7116,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7145,10 +7140,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488630</v>
+        <v>488907</v>
       </c>
       <c r="R63" t="n">
-        <v>7145015</v>
+        <v>7144779</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7183,6 +7178,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7195,19 +7195,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129727793</v>
+        <v>129726764</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7238,14 +7238,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488795</v>
+        <v>488646</v>
       </c>
       <c r="R64" t="n">
-        <v>7144792</v>
+        <v>7144947</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,14 +7275,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7297,19 +7302,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727798</v>
+        <v>129727793</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7344,10 +7349,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488442</v>
+        <v>488795</v>
       </c>
       <c r="R65" t="n">
-        <v>7145001</v>
+        <v>7144792</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7384,7 +7389,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På flera granar i gammal flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,7 +7416,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726764</v>
+        <v>129727798</v>
       </c>
       <c r="B66" t="n">
         <v>79081</v>
@@ -7442,14 +7447,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488646</v>
+        <v>488442</v>
       </c>
       <c r="R66" t="n">
-        <v>7144947</v>
+        <v>7145001</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7479,19 +7484,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:36</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,19 +7506,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129727958</v>
+        <v>129716433</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7549,14 +7549,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488796</v>
+        <v>488359</v>
       </c>
       <c r="R67" t="n">
-        <v>7144792</v>
+        <v>7144987</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7603,19 +7603,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129716433</v>
+        <v>129727790</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7650,10 +7650,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488359</v>
+        <v>488911</v>
       </c>
       <c r="R68" t="n">
-        <v>7144987</v>
+        <v>7144836</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7688,6 +7688,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7700,19 +7705,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129727790</v>
+        <v>129716432</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7747,10 +7752,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488911</v>
+        <v>489065</v>
       </c>
       <c r="R69" t="n">
-        <v>7144836</v>
+        <v>7144852</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7787,7 +7792,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7802,19 +7807,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129716432</v>
+        <v>129727787</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7849,10 +7854,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>489065</v>
+        <v>489024</v>
       </c>
       <c r="R70" t="n">
-        <v>7144852</v>
+        <v>7144841</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7889,7 +7894,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ett 30-tal gamla granar rikligt draperade med garnlav.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7904,19 +7909,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129727787</v>
+        <v>129727958</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -7947,14 +7952,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>489024</v>
+        <v>488796</v>
       </c>
       <c r="R71" t="n">
-        <v>7144841</v>
+        <v>7144792</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7989,11 +7994,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8006,22 +8006,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129727951</v>
+        <v>129726778</v>
       </c>
       <c r="B72" t="n">
-        <v>91897</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489112</v>
+        <v>488522</v>
       </c>
       <c r="R72" t="n">
-        <v>7144780</v>
+        <v>7144974</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,9 +8086,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8103,22 +8113,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129726778</v>
+        <v>129727951</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>91897</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8126,34 +8136,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488522</v>
+        <v>489112</v>
       </c>
       <c r="R73" t="n">
-        <v>7144974</v>
+        <v>7144780</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8183,19 +8193,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8210,22 +8210,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129716429</v>
+        <v>129727954</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8233,34 +8233,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488440</v>
+        <v>489143</v>
       </c>
       <c r="R74" t="n">
-        <v>7144976</v>
+        <v>7144773</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8307,19 +8307,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726779</v>
+        <v>129716429</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8350,14 +8350,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488452</v>
+        <v>488440</v>
       </c>
       <c r="R75" t="n">
-        <v>7144979</v>
+        <v>7144976</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8387,19 +8387,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8414,12 +8404,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8528,10 +8518,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129727954</v>
+        <v>129726779</v>
       </c>
       <c r="B77" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8539,34 +8529,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>489143</v>
+        <v>488452</v>
       </c>
       <c r="R77" t="n">
-        <v>7144773</v>
+        <v>7144979</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8596,9 +8586,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129716434</v>
+        <v>129727769</v>
       </c>
       <c r="B79" t="n">
-        <v>91595</v>
+        <v>80187</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,34 +8733,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488618</v>
+        <v>488758</v>
       </c>
       <c r="R79" t="n">
-        <v>7144922</v>
+        <v>7144774</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8795,63 +8802,94 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129727769</v>
+        <v>129727767</v>
       </c>
       <c r="B80" t="n">
-        <v>80187</v>
+        <v>80215</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8861,10 +8899,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488758</v>
+        <v>488658</v>
       </c>
       <c r="R80" t="n">
-        <v>7144774</v>
+        <v>7144806</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8901,7 +8939,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På en gammal levande sälg.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8954,7 +8992,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727957</v>
+        <v>129716434</v>
       </c>
       <c r="B81" t="n">
         <v>91595</v>
@@ -8985,14 +9023,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488618</v>
       </c>
       <c r="R81" t="n">
-        <v>7144844</v>
+        <v>7144922</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9039,22 +9077,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129716441</v>
+        <v>129727957</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9062,34 +9100,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488921</v>
+        <v>488591</v>
       </c>
       <c r="R82" t="n">
-        <v>7144886</v>
+        <v>7144844</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9136,19 +9174,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716422</v>
+        <v>129726777</v>
       </c>
       <c r="B83" t="n">
         <v>79081</v>
@@ -9179,14 +9217,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488767</v>
+        <v>488570</v>
       </c>
       <c r="R83" t="n">
-        <v>7144853</v>
+        <v>7144960</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9216,9 +9254,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9233,64 +9281,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129727767</v>
+        <v>129716445</v>
       </c>
       <c r="B84" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488658</v>
+        <v>488685</v>
       </c>
       <c r="R84" t="n">
-        <v>7144806</v>
+        <v>7144909</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9325,62 +9366,31 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129726777</v>
+        <v>129716441</v>
       </c>
       <c r="B85" t="n">
         <v>79081</v>
@@ -9411,14 +9421,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488570</v>
+        <v>488921</v>
       </c>
       <c r="R85" t="n">
-        <v>7144960</v>
+        <v>7144886</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9448,19 +9458,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9475,19 +9475,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129716445</v>
+        <v>129716422</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488685</v>
+        <v>488767</v>
       </c>
       <c r="R86" t="n">
-        <v>7144909</v>
+        <v>7144853</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9584,7 +9584,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727960</v>
+        <v>129727795</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9615,14 +9615,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488374</v>
+        <v>488737</v>
       </c>
       <c r="R87" t="n">
-        <v>7144949</v>
+        <v>7144797</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,57 +9674,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129726769</v>
+        <v>129727794</v>
       </c>
       <c r="B88" t="n">
-        <v>75065</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489064</v>
+        <v>488763</v>
       </c>
       <c r="R88" t="n">
-        <v>7144843</v>
+        <v>7144775</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9754,19 +9754,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9777,41 +9772,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129726773</v>
+        <v>129727960</v>
       </c>
       <c r="B89" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9819,34 +9799,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>489020</v>
+        <v>488374</v>
       </c>
       <c r="R89" t="n">
-        <v>7144867</v>
+        <v>7144949</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9876,19 +9856,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9903,19 +9878,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727795</v>
+        <v>129727783</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9950,10 +9925,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488737</v>
+        <v>488709</v>
       </c>
       <c r="R90" t="n">
-        <v>7144797</v>
+        <v>7144911</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9990,7 +9965,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På en levande gammal gran.</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10017,45 +9992,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727794</v>
+        <v>129726769</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>75065</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488763</v>
+        <v>489064</v>
       </c>
       <c r="R91" t="n">
-        <v>7144775</v>
+        <v>7144843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10085,14 +10060,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10103,26 +10083,41 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129727783</v>
+        <v>129726773</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10130,34 +10125,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488709</v>
+        <v>489020</v>
       </c>
       <c r="R92" t="n">
-        <v>7144911</v>
+        <v>7144867</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10187,14 +10182,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På levande gran i gammal granskog.</t>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10209,22 +10209,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B93" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R93" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,9 +10289,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10306,22 +10316,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10329,34 +10339,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R94" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10386,19 +10396,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,44 +10413,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R95" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,10 +10522,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730462</v>
+        <v>129730469</v>
       </c>
       <c r="B96" t="n">
-        <v>92317</v>
+        <v>57840</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10538,21 +10533,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489017</v>
+        <v>488507</v>
       </c>
       <c r="R96" t="n">
-        <v>7144821</v>
+        <v>7144936</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10598,6 +10593,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,27 +10624,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730469</v>
+        <v>129730439</v>
       </c>
       <c r="B97" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488507</v>
+        <v>488746</v>
       </c>
       <c r="R97" t="n">
-        <v>7144936</v>
+        <v>7144786</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10920,10 +10920,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730449</v>
+        <v>129730473</v>
       </c>
       <c r="B100" t="n">
-        <v>80187</v>
+        <v>91595</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10931,21 +10931,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488414</v>
+        <v>489028</v>
       </c>
       <c r="R100" t="n">
-        <v>7144940</v>
+        <v>7144803</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,7 +11017,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730473</v>
+        <v>129730474</v>
       </c>
       <c r="B101" t="n">
         <v>91595</v>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489028</v>
+        <v>488676</v>
       </c>
       <c r="R101" t="n">
-        <v>7144803</v>
+        <v>7144870</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730474</v>
+        <v>129730449</v>
       </c>
       <c r="B102" t="n">
-        <v>91595</v>
+        <v>80187</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488676</v>
+        <v>488414</v>
       </c>
       <c r="R102" t="n">
-        <v>7144870</v>
+        <v>7144940</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730461</v>
+        <v>129730443</v>
       </c>
       <c r="B104" t="n">
-        <v>91599</v>
+        <v>57896</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488464</v>
+        <v>488348</v>
       </c>
       <c r="R104" t="n">
-        <v>7144953</v>
+        <v>7144901</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730451</v>
+        <v>129730461</v>
       </c>
       <c r="B105" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488709</v>
+        <v>488464</v>
       </c>
       <c r="R105" t="n">
-        <v>7144786</v>
+        <v>7144953</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730443</v>
+        <v>129730451</v>
       </c>
       <c r="B106" t="n">
-        <v>57896</v>
+        <v>80186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11513,21 +11513,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488348</v>
+        <v>488709</v>
       </c>
       <c r="R106" t="n">
-        <v>7144901</v>
+        <v>7144786</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R109" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,11 +11874,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11905,10 +11900,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B110" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11916,21 +11911,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11940,10 +11935,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R110" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11976,6 +11971,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12987,34 +12987,30 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730456</v>
+        <v>129730478</v>
       </c>
       <c r="B121" t="n">
-        <v>91970</v>
+        <v>91619</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13022,10 +13018,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488467</v>
+        <v>488436</v>
       </c>
       <c r="R121" t="n">
-        <v>7144951</v>
+        <v>7144967</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13084,32 +13080,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730459</v>
+        <v>129730456</v>
       </c>
       <c r="B122" t="n">
-        <v>91599</v>
+        <v>91970</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13119,10 +13115,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488604</v>
+        <v>488467</v>
       </c>
       <c r="R122" t="n">
-        <v>7144985</v>
+        <v>7144951</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13181,10 +13177,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730478</v>
+        <v>129730459</v>
       </c>
       <c r="B123" t="n">
-        <v>91619</v>
+        <v>91599</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13192,19 +13188,23 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488436</v>
+        <v>488604</v>
       </c>
       <c r="R123" t="n">
-        <v>7144967</v>
+        <v>7144985</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13759,32 +13759,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730440</v>
+        <v>129730472</v>
       </c>
       <c r="B129" t="n">
-        <v>56926</v>
+        <v>91595</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>489134</v>
+        <v>488622</v>
       </c>
       <c r="R129" t="n">
-        <v>7144763</v>
+        <v>7144899</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13830,11 +13830,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13861,7 +13856,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730472</v>
+        <v>129730475</v>
       </c>
       <c r="B130" t="n">
         <v>91595</v>
@@ -13896,10 +13891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488622</v>
+        <v>488459</v>
       </c>
       <c r="R130" t="n">
-        <v>7144899</v>
+        <v>7144958</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13958,32 +13953,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730475</v>
+        <v>129730440</v>
       </c>
       <c r="B131" t="n">
-        <v>91595</v>
+        <v>56926</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13993,10 +13988,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>488459</v>
+        <v>489134</v>
       </c>
       <c r="R131" t="n">
-        <v>7144958</v>
+        <v>7144763</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14029,6 +14024,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129727950</v>
+        <v>129727946</v>
       </c>
       <c r="B24" t="n">
-        <v>80187</v>
+        <v>91599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,21 +3086,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488374</v>
+        <v>489112</v>
       </c>
       <c r="R24" t="n">
-        <v>7144953</v>
+        <v>7144780</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129727946</v>
+        <v>129726762</v>
       </c>
       <c r="B25" t="n">
-        <v>91599</v>
+        <v>83052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,34 +3183,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489112</v>
+        <v>488626</v>
       </c>
       <c r="R25" t="n">
-        <v>7144780</v>
+        <v>7145010</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,9 +3240,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,22 +3267,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726762</v>
+        <v>129727950</v>
       </c>
       <c r="B26" t="n">
-        <v>83052</v>
+        <v>80187</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,34 +3290,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488626</v>
+        <v>488374</v>
       </c>
       <c r="R26" t="n">
-        <v>7145010</v>
+        <v>7144953</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,19 +3347,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,12 +3364,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727769</v>
+        <v>129716434</v>
       </c>
       <c r="B79" t="n">
-        <v>80187</v>
+        <v>91595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,41 +8733,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488758</v>
+        <v>488618</v>
       </c>
       <c r="R79" t="n">
-        <v>7144774</v>
+        <v>7144922</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8802,107 +8795,69 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129727767</v>
+        <v>129727957</v>
       </c>
       <c r="B80" t="n">
-        <v>80215</v>
+        <v>91595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488658</v>
+        <v>488591</v>
       </c>
       <c r="R80" t="n">
-        <v>7144806</v>
+        <v>7144844</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8937,65 +8892,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129716434</v>
+        <v>129727769</v>
       </c>
       <c r="B81" t="n">
-        <v>91595</v>
+        <v>80187</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9003,34 +8927,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488618</v>
+        <v>488758</v>
       </c>
       <c r="R81" t="n">
-        <v>7144922</v>
+        <v>7144774</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9065,69 +8996,107 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727957</v>
+        <v>129727767</v>
       </c>
       <c r="B82" t="n">
-        <v>91595</v>
+        <v>80215</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488591</v>
+        <v>488658</v>
       </c>
       <c r="R82" t="n">
-        <v>7144844</v>
+        <v>7144806</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9162,24 +9131,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727795</v>
+        <v>129726773</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488737</v>
+        <v>489020</v>
       </c>
       <c r="R87" t="n">
-        <v>7144797</v>
+        <v>7144867</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,14 +9652,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På en levande gammal gran.</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,19 +9679,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727794</v>
+        <v>129727795</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -9721,10 +9726,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488763</v>
+        <v>488737</v>
       </c>
       <c r="R88" t="n">
-        <v>7144775</v>
+        <v>7144797</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9761,7 +9766,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9788,7 +9793,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727960</v>
+        <v>129727794</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -9819,14 +9824,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488374</v>
+        <v>488763</v>
       </c>
       <c r="R89" t="n">
-        <v>7144949</v>
+        <v>7144775</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9863,7 +9868,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9878,19 +9883,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727783</v>
+        <v>129727960</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9921,14 +9926,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488709</v>
+        <v>488374</v>
       </c>
       <c r="R90" t="n">
-        <v>7144911</v>
+        <v>7144949</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9965,7 +9970,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9980,57 +9985,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726769</v>
+        <v>129727783</v>
       </c>
       <c r="B91" t="n">
-        <v>75065</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489064</v>
+        <v>488709</v>
       </c>
       <c r="R91" t="n">
-        <v>7144843</v>
+        <v>7144911</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10060,19 +10065,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,63 +10083,48 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726773</v>
+        <v>129726769</v>
       </c>
       <c r="B92" t="n">
-        <v>91599</v>
+        <v>75065</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10149,10 +10134,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489020</v>
+        <v>489064</v>
       </c>
       <c r="R92" t="n">
-        <v>7144867</v>
+        <v>7144843</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10184,7 +10169,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10194,7 +10179,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10205,6 +10190,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R93" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,19 +10289,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10339,34 +10329,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R94" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10396,9 +10386,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,12 +10413,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10522,27 +10522,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730469</v>
+        <v>129730439</v>
       </c>
       <c r="B96" t="n">
-        <v>57840</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488507</v>
+        <v>488746</v>
       </c>
       <c r="R96" t="n">
-        <v>7144936</v>
+        <v>7144786</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,27 +10624,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730439</v>
+        <v>129730469</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>57840</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488746</v>
+        <v>488507</v>
       </c>
       <c r="R97" t="n">
-        <v>7144786</v>
+        <v>7144936</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10920,32 +10920,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730473</v>
+        <v>129730465</v>
       </c>
       <c r="B100" t="n">
-        <v>91595</v>
+        <v>80215</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489028</v>
+        <v>488705</v>
       </c>
       <c r="R100" t="n">
-        <v>7144803</v>
+        <v>7144862</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,10 +11017,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730474</v>
+        <v>129730449</v>
       </c>
       <c r="B101" t="n">
-        <v>91595</v>
+        <v>80187</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11028,21 +11028,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488676</v>
+        <v>488414</v>
       </c>
       <c r="R101" t="n">
-        <v>7144870</v>
+        <v>7144940</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730449</v>
+        <v>129730473</v>
       </c>
       <c r="B102" t="n">
-        <v>80187</v>
+        <v>91595</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488414</v>
+        <v>489028</v>
       </c>
       <c r="R102" t="n">
-        <v>7144940</v>
+        <v>7144803</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730465</v>
+        <v>129730474</v>
       </c>
       <c r="B103" t="n">
-        <v>80215</v>
+        <v>91595</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488705</v>
+        <v>488676</v>
       </c>
       <c r="R103" t="n">
-        <v>7144862</v>
+        <v>7144870</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730443</v>
+        <v>129730461</v>
       </c>
       <c r="B104" t="n">
-        <v>57896</v>
+        <v>91599</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488348</v>
+        <v>488464</v>
       </c>
       <c r="R104" t="n">
-        <v>7144901</v>
+        <v>7144953</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730461</v>
+        <v>129730451</v>
       </c>
       <c r="B105" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488464</v>
+        <v>488709</v>
       </c>
       <c r="R105" t="n">
-        <v>7144953</v>
+        <v>7144786</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730451</v>
+        <v>129730443</v>
       </c>
       <c r="B106" t="n">
-        <v>80186</v>
+        <v>57896</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11513,21 +11513,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488709</v>
+        <v>488348</v>
       </c>
       <c r="R106" t="n">
-        <v>7144786</v>
+        <v>7144901</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730463</v>
+        <v>129730468</v>
       </c>
       <c r="B116" t="n">
-        <v>57736</v>
+        <v>78094</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12508,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488546</v>
+        <v>488763</v>
       </c>
       <c r="R116" t="n">
-        <v>7144950</v>
+        <v>7144808</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12568,11 +12568,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12599,10 +12594,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730468</v>
+        <v>129730463</v>
       </c>
       <c r="B117" t="n">
-        <v>78094</v>
+        <v>57736</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12610,21 +12605,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12634,10 +12629,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488763</v>
+        <v>488546</v>
       </c>
       <c r="R117" t="n">
-        <v>7144808</v>
+        <v>7144950</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12670,6 +12665,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12987,10 +12987,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730478</v>
+        <v>129730459</v>
       </c>
       <c r="B121" t="n">
-        <v>91619</v>
+        <v>91599</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12998,19 +12998,23 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13018,10 +13022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488436</v>
+        <v>488604</v>
       </c>
       <c r="R121" t="n">
-        <v>7144967</v>
+        <v>7144985</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13080,34 +13084,30 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730456</v>
+        <v>129730478</v>
       </c>
       <c r="B122" t="n">
-        <v>91970</v>
+        <v>91619</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13115,10 +13115,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488467</v>
+        <v>488436</v>
       </c>
       <c r="R122" t="n">
-        <v>7144951</v>
+        <v>7144967</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13177,32 +13177,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730459</v>
+        <v>129730456</v>
       </c>
       <c r="B123" t="n">
-        <v>91599</v>
+        <v>91970</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488604</v>
+        <v>488467</v>
       </c>
       <c r="R123" t="n">
-        <v>7144985</v>
+        <v>7144951</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B124" t="n">
-        <v>83052</v>
+        <v>80215</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R124" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B125" t="n">
-        <v>80215</v>
+        <v>83052</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R125" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -1664,45 +1664,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726781</v>
+        <v>129727765</v>
       </c>
       <c r="B11" t="n">
-        <v>78094</v>
+        <v>80215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488365</v>
+        <v>488701</v>
       </c>
       <c r="R11" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,19 +1739,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,18 +1755,44 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2286,52 +2314,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727765</v>
+        <v>129726781</v>
       </c>
       <c r="B17" t="n">
-        <v>80215</v>
+        <v>78094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488701</v>
+        <v>488365</v>
       </c>
       <c r="R17" t="n">
-        <v>7144801</v>
+        <v>7144983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,14 +2382,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,54 +2403,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726774</v>
+        <v>129727947</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2432,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489025</v>
+        <v>488803</v>
       </c>
       <c r="R18" t="n">
-        <v>7144875</v>
+        <v>7144779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,19 +2489,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,22 +2506,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727947</v>
+        <v>129716443</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>91595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,34 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488803</v>
+        <v>488470</v>
       </c>
       <c r="R19" t="n">
-        <v>7144779</v>
+        <v>7144975</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129716443</v>
+        <v>129726774</v>
       </c>
       <c r="B20" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,34 +2626,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488470</v>
+        <v>489025</v>
       </c>
       <c r="R20" t="n">
-        <v>7144975</v>
+        <v>7144875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,9 +2683,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,12 +2710,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726772</v>
+        <v>129726757</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>83044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,21 +2872,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489044</v>
+        <v>488392</v>
       </c>
       <c r="R22" t="n">
-        <v>7144859</v>
+        <v>7145120</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129726757</v>
+        <v>129726772</v>
       </c>
       <c r="B23" t="n">
-        <v>83044</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488392</v>
+        <v>489044</v>
       </c>
       <c r="R23" t="n">
-        <v>7145120</v>
+        <v>7144859</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3511,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,39 +3522,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R28" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,6 +3584,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3601,22 +3601,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727786</v>
+        <v>129716435</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,34 +3624,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489035</v>
+        <v>488832</v>
       </c>
       <c r="R29" t="n">
-        <v>7144832</v>
+        <v>7144827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,11 +3691,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3703,12 +3703,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727771</v>
+        <v>129727781</v>
       </c>
       <c r="B45" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5266,41 +5266,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488511</v>
+        <v>488586</v>
       </c>
       <c r="R45" t="n">
-        <v>7144867</v>
+        <v>7144955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,7 +5330,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5346,34 +5339,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5390,10 +5357,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727770</v>
+        <v>129727785</v>
       </c>
       <c r="B46" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5401,41 +5368,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488674</v>
+        <v>488865</v>
       </c>
       <c r="R46" t="n">
-        <v>7144814</v>
+        <v>7144860</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5472,7 +5432,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5481,34 +5441,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5525,7 +5459,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727781</v>
+        <v>129727799</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5560,10 +5494,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488586</v>
+        <v>488408</v>
       </c>
       <c r="R47" t="n">
-        <v>7144955</v>
+        <v>7144970</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5627,10 +5561,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727785</v>
+        <v>129716437</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5638,21 +5572,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5662,10 +5596,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488865</v>
+        <v>488533</v>
       </c>
       <c r="R48" t="n">
-        <v>7144860</v>
+        <v>7144953</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5700,11 +5634,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5717,19 +5646,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727799</v>
+        <v>129726775</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5760,14 +5689,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488408</v>
+        <v>488851</v>
       </c>
       <c r="R49" t="n">
-        <v>7144970</v>
+        <v>7144825</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5797,14 +5726,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5819,22 +5753,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129716437</v>
+        <v>129727777</v>
       </c>
       <c r="B50" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5842,21 +5776,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5866,10 +5800,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488533</v>
+        <v>488483</v>
       </c>
       <c r="R50" t="n">
-        <v>7144953</v>
+        <v>7144992</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,6 +5838,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5916,22 +5855,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129726775</v>
+        <v>129727771</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5939,34 +5878,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488851</v>
+        <v>488511</v>
       </c>
       <c r="R51" t="n">
-        <v>7144825</v>
+        <v>7144867</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,19 +5942,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6017,28 +5958,54 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727777</v>
+        <v>129727770</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6046,34 +6013,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488483</v>
+        <v>488674</v>
       </c>
       <c r="R52" t="n">
-        <v>7144992</v>
+        <v>7144814</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,7 +6084,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6119,8 +6093,34 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6137,45 +6137,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129727953</v>
+        <v>129716431</v>
       </c>
       <c r="B53" t="n">
-        <v>91981</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488400</v>
+        <v>488426</v>
       </c>
       <c r="R53" t="n">
-        <v>7144968</v>
+        <v>7145034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129716447</v>
+        <v>129727780</v>
       </c>
       <c r="B54" t="n">
-        <v>83057</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488731</v>
+        <v>488542</v>
       </c>
       <c r="R54" t="n">
-        <v>7144891</v>
+        <v>7144969</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,6 +6307,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6319,57 +6324,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129716431</v>
+        <v>129727953</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>91981</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488426</v>
+        <v>488400</v>
       </c>
       <c r="R55" t="n">
-        <v>7145034</v>
+        <v>7144968</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,22 +6421,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>83057</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6439,21 +6444,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6463,10 +6468,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R56" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6501,11 +6506,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,22 +6518,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129716430</v>
+        <v>129727791</v>
       </c>
       <c r="B57" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,19 +6541,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6561,10 +6565,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488835</v>
+        <v>488907</v>
       </c>
       <c r="R57" t="n">
-        <v>7144824</v>
+        <v>7144779</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6599,6 +6603,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6611,22 +6620,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129716440</v>
+        <v>129727800</v>
       </c>
       <c r="B58" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6634,19 +6643,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6654,10 +6667,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488547</v>
+        <v>488375</v>
       </c>
       <c r="R58" t="n">
-        <v>7144971</v>
+        <v>7144951</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6692,6 +6705,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6704,19 +6722,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716442</v>
+        <v>129716430</v>
       </c>
       <c r="B59" t="n">
         <v>91619</v>
@@ -6747,10 +6765,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488630</v>
+        <v>488835</v>
       </c>
       <c r="R59" t="n">
-        <v>7145015</v>
+        <v>7144824</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6809,34 +6827,30 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716428</v>
+        <v>129716440</v>
       </c>
       <c r="B60" t="n">
-        <v>92317</v>
+        <v>91619</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6844,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>489052</v>
+        <v>488547</v>
       </c>
       <c r="R60" t="n">
-        <v>7144873</v>
+        <v>7144971</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6906,34 +6920,30 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716423</v>
+        <v>129716442</v>
       </c>
       <c r="B61" t="n">
-        <v>92317</v>
+        <v>91619</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6941,10 +6951,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488296</v>
+        <v>488630</v>
       </c>
       <c r="R61" t="n">
-        <v>7145038</v>
+        <v>7145015</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7003,32 +7013,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129727800</v>
+        <v>129716428</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7038,10 +7048,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488375</v>
+        <v>489052</v>
       </c>
       <c r="R62" t="n">
-        <v>7144951</v>
+        <v>7144873</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7076,11 +7086,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7093,44 +7098,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129727791</v>
+        <v>129716423</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7140,10 +7145,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488907</v>
+        <v>488296</v>
       </c>
       <c r="R63" t="n">
-        <v>7144779</v>
+        <v>7145038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7178,11 +7183,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7195,12 +7195,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726773</v>
+        <v>129727795</v>
       </c>
       <c r="B87" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489020</v>
+        <v>488737</v>
       </c>
       <c r="R87" t="n">
-        <v>7144867</v>
+        <v>7144797</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,19 +9652,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9679,19 +9674,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727795</v>
+        <v>129727794</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -9726,10 +9721,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488737</v>
+        <v>488763</v>
       </c>
       <c r="R88" t="n">
-        <v>7144797</v>
+        <v>7144775</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9766,7 +9761,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en levande gammal gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9793,7 +9788,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727794</v>
+        <v>129727960</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -9824,14 +9819,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488763</v>
+        <v>488374</v>
       </c>
       <c r="R89" t="n">
-        <v>7144775</v>
+        <v>7144949</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9868,7 +9863,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9883,19 +9878,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727960</v>
+        <v>129727783</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9926,14 +9921,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488374</v>
+        <v>488709</v>
       </c>
       <c r="R90" t="n">
-        <v>7144949</v>
+        <v>7144911</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9965,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9985,57 +9980,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727783</v>
+        <v>129726769</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>75065</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488709</v>
+        <v>489064</v>
       </c>
       <c r="R91" t="n">
-        <v>7144911</v>
+        <v>7144843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10065,14 +10060,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På levande gran i gammal granskog.</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,48 +10083,63 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726769</v>
+        <v>129726773</v>
       </c>
       <c r="B92" t="n">
-        <v>75065</v>
+        <v>91599</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10134,10 +10149,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489064</v>
+        <v>489020</v>
       </c>
       <c r="R92" t="n">
-        <v>7144843</v>
+        <v>7144867</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10169,7 +10184,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10179,7 +10194,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10190,21 +10205,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B93" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R93" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,9 +10289,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10306,22 +10316,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10329,34 +10339,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R94" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10386,19 +10396,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,12 +10413,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10428,7 +10428,7 @@
         <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>129730439</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>129730469</v>
       </c>
       <c r="B97" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>129730460</v>
       </c>
       <c r="B98" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>129730457</v>
       </c>
       <c r="B99" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730465</v>
+        <v>129730473</v>
       </c>
       <c r="B100" t="n">
-        <v>80215</v>
+        <v>91598</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488705</v>
+        <v>489028</v>
       </c>
       <c r="R100" t="n">
-        <v>7144862</v>
+        <v>7144803</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,10 +11017,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730449</v>
+        <v>129730474</v>
       </c>
       <c r="B101" t="n">
-        <v>80187</v>
+        <v>91598</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11028,21 +11028,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488414</v>
+        <v>488676</v>
       </c>
       <c r="R101" t="n">
-        <v>7144940</v>
+        <v>7144870</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730473</v>
+        <v>129730449</v>
       </c>
       <c r="B102" t="n">
-        <v>91595</v>
+        <v>80190</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489028</v>
+        <v>488414</v>
       </c>
       <c r="R102" t="n">
-        <v>7144803</v>
+        <v>7144940</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730474</v>
+        <v>129730465</v>
       </c>
       <c r="B103" t="n">
-        <v>91595</v>
+        <v>80218</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488676</v>
+        <v>488705</v>
       </c>
       <c r="R103" t="n">
-        <v>7144870</v>
+        <v>7144862</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>129730461</v>
       </c>
       <c r="B104" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>129730451</v>
       </c>
       <c r="B105" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>129730443</v>
       </c>
       <c r="B106" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>129730441</v>
       </c>
       <c r="B107" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>129730454</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>129730452</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>129730450</v>
       </c>
       <c r="B111" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129730448</v>
       </c>
       <c r="B112" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>83057</v>
+        <v>83060</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129730464</v>
       </c>
       <c r="B114" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>129730470</v>
       </c>
       <c r="B115" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730468</v>
+        <v>129730463</v>
       </c>
       <c r="B116" t="n">
-        <v>78094</v>
+        <v>57737</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12508,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488763</v>
+        <v>488546</v>
       </c>
       <c r="R116" t="n">
-        <v>7144808</v>
+        <v>7144950</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12568,6 +12568,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12594,10 +12599,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730463</v>
+        <v>129730468</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>78097</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12605,21 +12610,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12629,10 +12634,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488546</v>
+        <v>488763</v>
       </c>
       <c r="R117" t="n">
-        <v>7144950</v>
+        <v>7144808</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12665,11 +12670,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12699,7 +12699,7 @@
         <v>129730458</v>
       </c>
       <c r="B118" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>129730471</v>
       </c>
       <c r="B119" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>129730476</v>
       </c>
       <c r="B120" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>129730459</v>
       </c>
       <c r="B121" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13084,30 +13084,34 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730478</v>
+        <v>129730456</v>
       </c>
       <c r="B122" t="n">
-        <v>91619</v>
+        <v>91973</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -13115,10 +13119,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488436</v>
+        <v>488467</v>
       </c>
       <c r="R122" t="n">
-        <v>7144967</v>
+        <v>7144951</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13177,34 +13181,30 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730456</v>
+        <v>129730478</v>
       </c>
       <c r="B123" t="n">
-        <v>91970</v>
+        <v>91622</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488467</v>
+        <v>488436</v>
       </c>
       <c r="R123" t="n">
-        <v>7144951</v>
+        <v>7144967</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>80215</v>
+        <v>83055</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R124" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B125" t="n">
-        <v>83052</v>
+        <v>80218</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R125" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13471,7 +13471,7 @@
         <v>129730447</v>
       </c>
       <c r="B126" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>83060</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R127" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B128" t="n">
-        <v>83057</v>
+        <v>79084</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R128" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13762,7 +13762,7 @@
         <v>129730472</v>
       </c>
       <c r="B129" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>129730475</v>
       </c>
       <c r="B130" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>129730440</v>
       </c>
       <c r="B131" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129727955</v>
       </c>
       <c r="B2" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727773</v>
+        <v>129716427</v>
       </c>
       <c r="B3" t="n">
-        <v>91595</v>
+        <v>83047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,41 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488610</v>
+        <v>488400</v>
       </c>
       <c r="R3" t="n">
-        <v>7144833</v>
+        <v>7144977</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,65 +845,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129716427</v>
+        <v>129727773</v>
       </c>
       <c r="B4" t="n">
-        <v>83044</v>
+        <v>91598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488400</v>
+        <v>488610</v>
       </c>
       <c r="R4" t="n">
-        <v>7144977</v>
+        <v>7144833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,69 +949,107 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129726770</v>
+        <v>129727766</v>
       </c>
       <c r="B5" t="n">
-        <v>80187</v>
+        <v>80218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489064</v>
+        <v>488676</v>
       </c>
       <c r="R5" t="n">
-        <v>7144843</v>
+        <v>7144814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,19 +1079,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,43 +1095,54 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726758</v>
+        <v>129726770</v>
       </c>
       <c r="B6" t="n">
-        <v>82918</v>
+        <v>80190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488417</v>
+        <v>489064</v>
       </c>
       <c r="R6" t="n">
-        <v>7145102</v>
+        <v>7144843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,6 +1230,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1233,52 +1261,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129727766</v>
+        <v>129727797</v>
       </c>
       <c r="B7" t="n">
-        <v>80215</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488676</v>
+        <v>488482</v>
       </c>
       <c r="R7" t="n">
-        <v>7144814</v>
+        <v>7144891</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,34 +1345,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1368,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129727797</v>
+        <v>129726758</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>82921</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,34 +1374,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488482</v>
+        <v>488417</v>
       </c>
       <c r="R8" t="n">
-        <v>7144891</v>
+        <v>7145102</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,14 +1431,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran i flerskiktad granskog.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,22 +1458,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129727952</v>
+        <v>129716439</v>
       </c>
       <c r="B9" t="n">
-        <v>91897</v>
+        <v>83047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,34 +1481,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488401</v>
+        <v>488354</v>
       </c>
       <c r="R9" t="n">
-        <v>7144967</v>
+        <v>7144989</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,22 +1555,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129716439</v>
+        <v>129727952</v>
       </c>
       <c r="B10" t="n">
-        <v>83044</v>
+        <v>91900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488354</v>
+        <v>488401</v>
       </c>
       <c r="R10" t="n">
-        <v>7144989</v>
+        <v>7144967</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,64 +1652,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727765</v>
+        <v>129726781</v>
       </c>
       <c r="B11" t="n">
-        <v>80215</v>
+        <v>78097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488701</v>
+        <v>488365</v>
       </c>
       <c r="R11" t="n">
-        <v>7144801</v>
+        <v>7144983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,14 +1732,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,54 +1753,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727776</v>
+        <v>129727782</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488425</v>
+        <v>488694</v>
       </c>
       <c r="R12" t="n">
-        <v>7145015</v>
+        <v>7144925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1846,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726761</v>
+        <v>129727796</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,14 +1904,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488516</v>
+        <v>488507</v>
       </c>
       <c r="R13" t="n">
-        <v>7145014</v>
+        <v>7144870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,19 +1941,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,22 +1963,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727801</v>
+        <v>129727776</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488339</v>
+        <v>488425</v>
       </c>
       <c r="R14" t="n">
-        <v>7144937</v>
+        <v>7145015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,7 +2050,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,45 +2077,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727782</v>
+        <v>129727765</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>80218</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488694</v>
+        <v>488701</v>
       </c>
       <c r="R15" t="n">
-        <v>7144925</v>
+        <v>7144801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2159,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,8 +2168,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2212,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727796</v>
+        <v>129726761</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,14 +2243,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488507</v>
+        <v>488516</v>
       </c>
       <c r="R16" t="n">
-        <v>7144870</v>
+        <v>7145014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,14 +2280,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,22 +2307,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726781</v>
+        <v>129727801</v>
       </c>
       <c r="B17" t="n">
-        <v>78094</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,34 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488365</v>
+        <v>488339</v>
       </c>
       <c r="R17" t="n">
-        <v>7144983</v>
+        <v>7144937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,19 +2387,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,12 +2409,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         <v>129727947</v>
       </c>
       <c r="B18" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129716443</v>
       </c>
       <c r="B19" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129726774</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>129727768</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>129726757</v>
       </c>
       <c r="B22" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129726772</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129727946</v>
+        <v>129727950</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>80190</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,21 +3086,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489112</v>
+        <v>488374</v>
       </c>
       <c r="R24" t="n">
-        <v>7144780</v>
+        <v>7144953</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726762</v>
+        <v>129727946</v>
       </c>
       <c r="B25" t="n">
-        <v>83052</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,34 +3183,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488626</v>
+        <v>489112</v>
       </c>
       <c r="R25" t="n">
-        <v>7145010</v>
+        <v>7144780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,19 +3240,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,22 +3257,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129727950</v>
+        <v>129726762</v>
       </c>
       <c r="B26" t="n">
-        <v>80187</v>
+        <v>83055</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,34 +3280,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488374</v>
+        <v>488626</v>
       </c>
       <c r="R26" t="n">
-        <v>7144953</v>
+        <v>7145010</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3347,9 +3337,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,12 +3364,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
         <v>129727772</v>
       </c>
       <c r="B27" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>129727786</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>129716435</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129727945</v>
+        <v>129727792</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489010</v>
+        <v>488815</v>
       </c>
       <c r="R30" t="n">
-        <v>7144808</v>
+        <v>7144788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,35 +3788,39 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726760</v>
+        <v>129726763</v>
       </c>
       <c r="B31" t="n">
-        <v>88998</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,21 +3828,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3851,10 +3852,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488426</v>
+        <v>488626</v>
       </c>
       <c r="R31" t="n">
-        <v>7145052</v>
+        <v>7145010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3886,7 +3887,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3896,7 +3897,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3923,10 +3924,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726763</v>
+        <v>129716436</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,14 +3955,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488626</v>
+        <v>489031</v>
       </c>
       <c r="R32" t="n">
-        <v>7145010</v>
+        <v>7144903</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,19 +3992,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,22 +4009,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129716436</v>
+        <v>129727945</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>91616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,34 +4032,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489031</v>
+        <v>489010</v>
       </c>
       <c r="R33" t="n">
-        <v>7144903</v>
+        <v>7144808</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4109,28 +4103,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727792</v>
+        <v>129726760</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>89001</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,34 +4133,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488815</v>
+        <v>488426</v>
       </c>
       <c r="R34" t="n">
-        <v>7144788</v>
+        <v>7145052</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4195,14 +4190,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,12 +4217,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4232,7 +4232,7 @@
         <v>129726784</v>
       </c>
       <c r="B35" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>129726771</v>
       </c>
       <c r="B36" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>129727802</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>129726765</v>
       </c>
       <c r="B38" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726782</v>
+        <v>129727959</v>
       </c>
       <c r="B39" t="n">
-        <v>83052</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488365</v>
+        <v>488762</v>
       </c>
       <c r="R39" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,19 +4716,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,22 +4733,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727959</v>
+        <v>129727788</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4786,14 +4776,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488762</v>
+        <v>488989</v>
       </c>
       <c r="R40" t="n">
-        <v>7144801</v>
+        <v>7144826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4828,6 +4818,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4840,22 +4835,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129727788</v>
+        <v>129726782</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>83055</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,34 +4858,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488989</v>
+        <v>488365</v>
       </c>
       <c r="R41" t="n">
-        <v>7144826</v>
+        <v>7144983</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,14 +4915,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4942,22 +4942,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726780</v>
+        <v>129716425</v>
       </c>
       <c r="B42" t="n">
-        <v>83057</v>
+        <v>89001</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,34 +4965,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488414</v>
+        <v>488829</v>
       </c>
       <c r="R42" t="n">
-        <v>7144975</v>
+        <v>7144835</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,19 +5022,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5049,22 +5039,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129716425</v>
+        <v>129726780</v>
       </c>
       <c r="B43" t="n">
-        <v>88998</v>
+        <v>83060</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,34 +5062,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488829</v>
+        <v>488414</v>
       </c>
       <c r="R43" t="n">
-        <v>7144835</v>
+        <v>7144975</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5129,9 +5119,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,12 +5146,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5161,7 +5161,7 @@
         <v>129727948</v>
       </c>
       <c r="B44" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727781</v>
+        <v>129727785</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488586</v>
+        <v>488865</v>
       </c>
       <c r="R45" t="n">
-        <v>7144955</v>
+        <v>7144860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5357,10 +5357,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727785</v>
+        <v>129727777</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488865</v>
+        <v>488483</v>
       </c>
       <c r="R46" t="n">
-        <v>7144860</v>
+        <v>7144992</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5459,10 +5459,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727799</v>
+        <v>129727771</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>80190</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5470,34 +5470,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488408</v>
+        <v>488511</v>
       </c>
       <c r="R47" t="n">
-        <v>7144970</v>
+        <v>7144867</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5534,7 +5541,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5543,8 +5550,34 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5561,10 +5594,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129716437</v>
+        <v>129727770</v>
       </c>
       <c r="B48" t="n">
-        <v>83052</v>
+        <v>80190</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5572,34 +5605,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488533</v>
+        <v>488674</v>
       </c>
       <c r="R48" t="n">
-        <v>7144953</v>
+        <v>7144814</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5634,34 +5674,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129726775</v>
+        <v>129727781</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5689,14 +5760,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488851</v>
+        <v>488586</v>
       </c>
       <c r="R49" t="n">
-        <v>7144825</v>
+        <v>7144955</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5726,19 +5797,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5753,22 +5819,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727777</v>
+        <v>129727799</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,10 +5866,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488483</v>
+        <v>488408</v>
       </c>
       <c r="R50" t="n">
-        <v>7144992</v>
+        <v>7144970</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5867,10 +5933,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727771</v>
+        <v>129716437</v>
       </c>
       <c r="B51" t="n">
-        <v>80187</v>
+        <v>83055</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5878,41 +5944,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488511</v>
+        <v>488533</v>
       </c>
       <c r="R51" t="n">
-        <v>7144867</v>
+        <v>7144953</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5947,65 +6006,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727770</v>
+        <v>129726775</v>
       </c>
       <c r="B52" t="n">
-        <v>80187</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6013,41 +6041,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488674</v>
+        <v>488851</v>
       </c>
       <c r="R52" t="n">
-        <v>7144814</v>
+        <v>7144825</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6077,14 +6098,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6093,89 +6119,63 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129716431</v>
+        <v>129727953</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>91984</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488426</v>
+        <v>488400</v>
       </c>
       <c r="R53" t="n">
-        <v>7145034</v>
+        <v>7144968</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>83060</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R54" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,11 +6307,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6324,57 +6319,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727953</v>
+        <v>129727780</v>
       </c>
       <c r="B55" t="n">
-        <v>91981</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488400</v>
+        <v>488542</v>
       </c>
       <c r="R55" t="n">
-        <v>7144968</v>
+        <v>7144969</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6409,6 +6404,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6421,22 +6421,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716447</v>
+        <v>129716431</v>
       </c>
       <c r="B56" t="n">
-        <v>83057</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488731</v>
+        <v>488426</v>
       </c>
       <c r="R56" t="n">
-        <v>7144891</v>
+        <v>7145034</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
         <v>129727791</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129727800</v>
+        <v>129716430</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6643,23 +6643,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6667,10 +6663,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488375</v>
+        <v>488835</v>
       </c>
       <c r="R58" t="n">
-        <v>7144951</v>
+        <v>7144824</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6705,11 +6701,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6722,22 +6713,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716430</v>
+        <v>129716440</v>
       </c>
       <c r="B59" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6765,10 +6756,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488835</v>
+        <v>488547</v>
       </c>
       <c r="R59" t="n">
-        <v>7144824</v>
+        <v>7144971</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6827,10 +6818,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716440</v>
+        <v>129727800</v>
       </c>
       <c r="B60" t="n">
-        <v>91619</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6838,19 +6829,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6858,10 +6853,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488547</v>
+        <v>488375</v>
       </c>
       <c r="R60" t="n">
-        <v>7144971</v>
+        <v>7144951</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6896,6 +6891,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6908,12 +6908,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
         <v>129716442</v>
       </c>
       <c r="B61" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>129716428</v>
       </c>
       <c r="B62" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>129716423</v>
       </c>
       <c r="B63" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129726764</v>
+        <v>129727793</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7238,14 +7238,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488646</v>
+        <v>488795</v>
       </c>
       <c r="R64" t="n">
-        <v>7144947</v>
+        <v>7144792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,19 +7275,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:36</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7302,22 +7297,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727793</v>
+        <v>129727798</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7349,10 +7344,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488795</v>
+        <v>488442</v>
       </c>
       <c r="R65" t="n">
-        <v>7144792</v>
+        <v>7145001</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7389,7 +7384,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7416,10 +7411,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129727798</v>
+        <v>129726764</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7447,14 +7442,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488442</v>
+        <v>488646</v>
       </c>
       <c r="R66" t="n">
-        <v>7145001</v>
+        <v>7144947</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7484,14 +7479,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal flerskiktad granskog.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,12 +7506,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7521,7 +7521,7 @@
         <v>129716433</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>129727790</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>129716432</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>129727787</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>129727958</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129726778</v>
+        <v>129727951</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>91900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488522</v>
+        <v>489112</v>
       </c>
       <c r="R72" t="n">
-        <v>7144974</v>
+        <v>7144780</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,19 +8086,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8113,22 +8103,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129727951</v>
+        <v>129727954</v>
       </c>
       <c r="B73" t="n">
-        <v>91897</v>
+        <v>91598</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8136,21 +8126,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8160,10 +8150,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489112</v>
+        <v>489143</v>
       </c>
       <c r="R73" t="n">
-        <v>7144780</v>
+        <v>7144773</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8222,10 +8212,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129727954</v>
+        <v>129716429</v>
       </c>
       <c r="B74" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8233,34 +8223,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>489143</v>
+        <v>488440</v>
       </c>
       <c r="R74" t="n">
-        <v>7144773</v>
+        <v>7144976</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8307,22 +8297,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129716429</v>
+        <v>129726779</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8350,14 +8340,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488440</v>
+        <v>488452</v>
       </c>
       <c r="R75" t="n">
-        <v>7144976</v>
+        <v>7144979</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8387,9 +8377,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8404,22 +8404,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129727778</v>
+        <v>129726778</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8447,14 +8447,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488513</v>
+        <v>488522</v>
       </c>
       <c r="R76" t="n">
-        <v>7144973</v>
+        <v>7144974</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8484,14 +8484,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8506,22 +8511,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726779</v>
+        <v>129727778</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8549,14 +8554,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488452</v>
+        <v>488513</v>
       </c>
       <c r="R77" t="n">
-        <v>7144979</v>
+        <v>7144973</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8586,19 +8591,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:01</t>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
         <v>129716424</v>
       </c>
       <c r="B78" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>129716434</v>
       </c>
       <c r="B79" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>129727957</v>
       </c>
       <c r="B80" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>129727769</v>
       </c>
       <c r="B81" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9051,52 +9051,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129727767</v>
+        <v>129716445</v>
       </c>
       <c r="B82" t="n">
-        <v>80215</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488658</v>
+        <v>488685</v>
       </c>
       <c r="R82" t="n">
-        <v>7144806</v>
+        <v>7144909</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,65 +9124,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129726777</v>
+        <v>129716422</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9217,14 +9179,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488570</v>
+        <v>488767</v>
       </c>
       <c r="R83" t="n">
-        <v>7144960</v>
+        <v>7144853</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9254,19 +9216,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9281,22 +9233,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129716445</v>
+        <v>129726777</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9324,14 +9276,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488685</v>
+        <v>488570</v>
       </c>
       <c r="R84" t="n">
-        <v>7144909</v>
+        <v>7144960</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9361,9 +9313,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9378,12 +9340,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9393,7 +9355,7 @@
         <v>129716441</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9487,45 +9449,52 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129716422</v>
+        <v>129727767</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>80218</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488767</v>
+        <v>488658</v>
       </c>
       <c r="R86" t="n">
-        <v>7144853</v>
+        <v>7144806</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9560,34 +9529,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129727795</v>
+        <v>129726773</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488737</v>
+        <v>489020</v>
       </c>
       <c r="R87" t="n">
-        <v>7144797</v>
+        <v>7144867</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,14 +9652,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På en levande gammal gran.</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9674,22 +9679,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727794</v>
+        <v>129727795</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9721,10 +9726,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488763</v>
+        <v>488737</v>
       </c>
       <c r="R88" t="n">
-        <v>7144775</v>
+        <v>7144797</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9761,7 +9766,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9788,10 +9793,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727960</v>
+        <v>129727794</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9819,14 +9824,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488374</v>
+        <v>488763</v>
       </c>
       <c r="R89" t="n">
-        <v>7144949</v>
+        <v>7144775</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9863,7 +9868,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9878,22 +9883,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727783</v>
+        <v>129727960</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9921,14 +9926,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488709</v>
+        <v>488374</v>
       </c>
       <c r="R90" t="n">
-        <v>7144911</v>
+        <v>7144949</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9965,7 +9970,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9980,57 +9985,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726769</v>
+        <v>129727783</v>
       </c>
       <c r="B91" t="n">
-        <v>75065</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489064</v>
+        <v>488709</v>
       </c>
       <c r="R91" t="n">
-        <v>7144843</v>
+        <v>7144911</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10060,19 +10065,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,63 +10083,48 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726773</v>
+        <v>129726769</v>
       </c>
       <c r="B92" t="n">
-        <v>91599</v>
+        <v>75068</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10149,10 +10134,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489020</v>
+        <v>489064</v>
       </c>
       <c r="R92" t="n">
-        <v>7144867</v>
+        <v>7144843</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10184,7 +10169,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10194,7 +10179,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10205,6 +10190,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>91598</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R93" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,19 +10289,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10339,34 +10329,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R94" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10396,9 +10386,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,22 +10413,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730462</v>
+        <v>129730469</v>
       </c>
       <c r="B95" t="n">
-        <v>92320</v>
+        <v>57841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10436,21 +10436,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>489017</v>
+        <v>488507</v>
       </c>
       <c r="R95" t="n">
-        <v>7144821</v>
+        <v>7144936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,6 +10496,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10522,32 +10527,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B96" t="n">
-        <v>57737</v>
+        <v>92320</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R96" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10593,11 +10598,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,27 +10624,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730469</v>
+        <v>129730439</v>
       </c>
       <c r="B97" t="n">
-        <v>57841</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488507</v>
+        <v>488746</v>
       </c>
       <c r="R97" t="n">
-        <v>7144936</v>
+        <v>7144786</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10920,7 +10920,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730473</v>
+        <v>129730474</v>
       </c>
       <c r="B100" t="n">
         <v>91598</v>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>489028</v>
+        <v>488676</v>
       </c>
       <c r="R100" t="n">
-        <v>7144803</v>
+        <v>7144870</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,7 +11017,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730474</v>
+        <v>129730473</v>
       </c>
       <c r="B101" t="n">
         <v>91598</v>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488676</v>
+        <v>489028</v>
       </c>
       <c r="R101" t="n">
-        <v>7144870</v>
+        <v>7144803</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730467</v>
+        <v>129730464</v>
       </c>
       <c r="B113" t="n">
-        <v>83060</v>
+        <v>57895</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488737</v>
+        <v>488362</v>
       </c>
       <c r="R113" t="n">
-        <v>7144811</v>
+        <v>7144944</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,6 +12272,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12298,10 +12303,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730464</v>
+        <v>129730467</v>
       </c>
       <c r="B114" t="n">
-        <v>57895</v>
+        <v>83060</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12309,21 +12314,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12333,10 +12338,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488362</v>
+        <v>488737</v>
       </c>
       <c r="R114" t="n">
-        <v>7144944</v>
+        <v>7144811</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12369,11 +12374,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B124" t="n">
-        <v>83055</v>
+        <v>80218</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R124" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B125" t="n">
-        <v>80218</v>
+        <v>83055</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R125" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13759,7 +13759,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730472</v>
+        <v>129730475</v>
       </c>
       <c r="B129" t="n">
         <v>91598</v>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488622</v>
+        <v>488459</v>
       </c>
       <c r="R129" t="n">
-        <v>7144899</v>
+        <v>7144958</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730475</v>
+        <v>129730472</v>
       </c>
       <c r="B130" t="n">
         <v>91598</v>
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488459</v>
+        <v>488622</v>
       </c>
       <c r="R130" t="n">
-        <v>7144958</v>
+        <v>7144899</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727772</v>
+        <v>129727786</v>
       </c>
       <c r="B27" t="n">
-        <v>80190</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,41 +3387,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488470</v>
+        <v>489035</v>
       </c>
       <c r="R27" t="n">
-        <v>7144960</v>
+        <v>7144832</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,7 +3451,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,34 +3460,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3511,10 +3478,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727786</v>
+        <v>129727772</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>80190</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,34 +3489,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489035</v>
+        <v>488470</v>
       </c>
       <c r="R28" t="n">
-        <v>7144832</v>
+        <v>7144960</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3586,7 +3560,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,8 +3569,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129727792</v>
+        <v>129727945</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>91616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,34 +3726,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488815</v>
+        <v>489010</v>
       </c>
       <c r="R30" t="n">
-        <v>7144788</v>
+        <v>7144808</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,39 +3791,35 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726763</v>
+        <v>129726760</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>89001</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,21 +3827,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3852,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488626</v>
+        <v>488426</v>
       </c>
       <c r="R31" t="n">
-        <v>7145010</v>
+        <v>7145052</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3887,7 +3886,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3897,7 +3896,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3924,7 +3923,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129716436</v>
+        <v>129727792</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -3959,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489031</v>
+        <v>488815</v>
       </c>
       <c r="R32" t="n">
-        <v>7144903</v>
+        <v>7144788</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,6 +3996,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4009,22 +4013,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129727945</v>
+        <v>129726763</v>
       </c>
       <c r="B33" t="n">
-        <v>91616</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,37 +4036,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489010</v>
+        <v>488626</v>
       </c>
       <c r="R33" t="n">
-        <v>7144808</v>
+        <v>7145010</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4092,40 +4093,49 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129726760</v>
+        <v>129716436</v>
       </c>
       <c r="B34" t="n">
-        <v>89001</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,34 +4143,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488426</v>
+        <v>489031</v>
       </c>
       <c r="R34" t="n">
-        <v>7145052</v>
+        <v>7144903</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,19 +4200,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4217,22 +4217,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726784</v>
+        <v>129726765</v>
       </c>
       <c r="B35" t="n">
-        <v>83047</v>
+        <v>82921</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,21 +4240,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488335</v>
+        <v>488725</v>
       </c>
       <c r="R35" t="n">
-        <v>7144978</v>
+        <v>7144925</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726771</v>
+        <v>129726784</v>
       </c>
       <c r="B36" t="n">
-        <v>91622</v>
+        <v>83047</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,19 +4347,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4367,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>489056</v>
+        <v>488335</v>
       </c>
       <c r="R36" t="n">
-        <v>7144853</v>
+        <v>7144978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4406,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4416,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129727802</v>
+        <v>129726771</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>91622</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,34 +4454,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488268</v>
+        <v>489056</v>
       </c>
       <c r="R37" t="n">
-        <v>7145078</v>
+        <v>7144853</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,14 +4507,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4529,22 +4534,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726765</v>
+        <v>129727802</v>
       </c>
       <c r="B38" t="n">
-        <v>82921</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4552,34 +4557,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488725</v>
+        <v>488268</v>
       </c>
       <c r="R38" t="n">
-        <v>7144925</v>
+        <v>7145078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,19 +4614,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,22 +4636,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129727959</v>
+        <v>129716425</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>89001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488762</v>
+        <v>488829</v>
       </c>
       <c r="R39" t="n">
-        <v>7144801</v>
+        <v>7144835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4733,19 +4733,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727788</v>
+        <v>129727959</v>
       </c>
       <c r="B40" t="n">
         <v>79084</v>
@@ -4776,14 +4776,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488989</v>
+        <v>488762</v>
       </c>
       <c r="R40" t="n">
-        <v>7144826</v>
+        <v>7144801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4818,11 +4818,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4835,22 +4830,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129726782</v>
+        <v>129727788</v>
       </c>
       <c r="B41" t="n">
-        <v>83055</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4858,34 +4853,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488365</v>
+        <v>488989</v>
       </c>
       <c r="R41" t="n">
-        <v>7144983</v>
+        <v>7144826</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4915,19 +4910,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4942,22 +4932,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129716425</v>
+        <v>129726782</v>
       </c>
       <c r="B42" t="n">
-        <v>89001</v>
+        <v>83055</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,34 +4955,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488829</v>
+        <v>488365</v>
       </c>
       <c r="R42" t="n">
-        <v>7144835</v>
+        <v>7144983</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5022,9 +5012,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5039,12 +5039,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129727780</v>
+        <v>129716431</v>
       </c>
       <c r="B55" t="n">
         <v>79084</v>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488542</v>
+        <v>488426</v>
       </c>
       <c r="R55" t="n">
-        <v>7144969</v>
+        <v>7145034</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6404,11 +6404,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6421,19 +6416,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129716431</v>
+        <v>129727780</v>
       </c>
       <c r="B56" t="n">
         <v>79084</v>
@@ -6468,10 +6463,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488426</v>
+        <v>488542</v>
       </c>
       <c r="R56" t="n">
-        <v>7145034</v>
+        <v>7144969</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6506,6 +6501,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,12 +6518,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129727793</v>
+        <v>129726764</v>
       </c>
       <c r="B64" t="n">
         <v>79084</v>
@@ -7238,14 +7238,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488795</v>
+        <v>488646</v>
       </c>
       <c r="R64" t="n">
-        <v>7144792</v>
+        <v>7144947</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7275,14 +7275,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7297,19 +7302,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129727798</v>
+        <v>129727793</v>
       </c>
       <c r="B65" t="n">
         <v>79084</v>
@@ -7344,10 +7349,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488442</v>
+        <v>488795</v>
       </c>
       <c r="R65" t="n">
-        <v>7145001</v>
+        <v>7144792</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7384,7 +7389,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På flera granar i gammal flerskiktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7411,7 +7416,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129726764</v>
+        <v>129727798</v>
       </c>
       <c r="B66" t="n">
         <v>79084</v>
@@ -7442,14 +7447,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488646</v>
+        <v>488442</v>
       </c>
       <c r="R66" t="n">
-        <v>7144947</v>
+        <v>7145001</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7479,19 +7484,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:36</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,12 +7506,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129716434</v>
+        <v>129727769</v>
       </c>
       <c r="B79" t="n">
-        <v>91598</v>
+        <v>80190</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,34 +8733,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488618</v>
+        <v>488758</v>
       </c>
       <c r="R79" t="n">
-        <v>7144922</v>
+        <v>7144774</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8795,31 +8802,62 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129727957</v>
+        <v>129716434</v>
       </c>
       <c r="B80" t="n">
         <v>91598</v>
@@ -8850,14 +8888,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488591</v>
+        <v>488618</v>
       </c>
       <c r="R80" t="n">
-        <v>7144844</v>
+        <v>7144922</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8904,22 +8942,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727769</v>
+        <v>129727957</v>
       </c>
       <c r="B81" t="n">
-        <v>80190</v>
+        <v>91598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8927,41 +8965,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488758</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7144774</v>
+        <v>7144844</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8996,55 +9027,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B93" t="n">
-        <v>91598</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R93" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,9 +10289,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10306,22 +10316,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>91598</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10329,34 +10339,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R94" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10386,19 +10396,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,12 +10413,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129730464</v>
+        <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>57895</v>
+        <v>83060</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488362</v>
+        <v>488737</v>
       </c>
       <c r="R113" t="n">
-        <v>7144944</v>
+        <v>7144811</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12272,11 +12272,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>2st</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12303,10 +12298,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129730467</v>
+        <v>129730464</v>
       </c>
       <c r="B114" t="n">
-        <v>83060</v>
+        <v>57895</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12314,21 +12309,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12338,10 +12333,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488737</v>
+        <v>488362</v>
       </c>
       <c r="R114" t="n">
-        <v>7144811</v>
+        <v>7144944</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12374,6 +12369,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>80218</v>
+        <v>83055</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R124" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B125" t="n">
-        <v>83055</v>
+        <v>80218</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R125" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129727955</v>
       </c>
       <c r="B2" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129716427</v>
+        <v>129727773</v>
       </c>
       <c r="B3" t="n">
-        <v>83047</v>
+        <v>91601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488400</v>
+        <v>488610</v>
       </c>
       <c r="R3" t="n">
-        <v>7144977</v>
+        <v>7144833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,34 +852,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129727773</v>
+        <v>129716427</v>
       </c>
       <c r="B4" t="n">
-        <v>91598</v>
+        <v>83050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,41 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488610</v>
+        <v>488400</v>
       </c>
       <c r="R4" t="n">
-        <v>7144833</v>
+        <v>7144977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,107 +980,69 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727766</v>
+        <v>129726770</v>
       </c>
       <c r="B5" t="n">
-        <v>80218</v>
+        <v>80193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488676</v>
+        <v>489064</v>
       </c>
       <c r="R5" t="n">
-        <v>7144814</v>
+        <v>7144843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,14 +1072,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,54 +1093,43 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726770</v>
+        <v>129726758</v>
       </c>
       <c r="B6" t="n">
-        <v>80190</v>
+        <v>82924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1150,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489064</v>
+        <v>488417</v>
       </c>
       <c r="R6" t="n">
-        <v>7144843</v>
+        <v>7145102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,21 +1217,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1264,7 +1236,7 @@
         <v>129727797</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,45 +1335,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129726758</v>
+        <v>129727766</v>
       </c>
       <c r="B8" t="n">
-        <v>82921</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488417</v>
+        <v>488676</v>
       </c>
       <c r="R8" t="n">
-        <v>7145102</v>
+        <v>7144814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,19 +1410,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:54</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,28 +1426,54 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129716439</v>
+        <v>129727952</v>
       </c>
       <c r="B9" t="n">
-        <v>83047</v>
+        <v>91903</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,34 +1481,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488354</v>
+        <v>488401</v>
       </c>
       <c r="R9" t="n">
-        <v>7144989</v>
+        <v>7144967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,22 +1555,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129727952</v>
+        <v>129716439</v>
       </c>
       <c r="B10" t="n">
-        <v>91900</v>
+        <v>83050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488401</v>
+        <v>488354</v>
       </c>
       <c r="R10" t="n">
-        <v>7144967</v>
+        <v>7144989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,22 +1652,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129726781</v>
+        <v>129727776</v>
       </c>
       <c r="B11" t="n">
-        <v>78097</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,34 +1675,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488365</v>
+        <v>488425</v>
       </c>
       <c r="R11" t="n">
-        <v>7144983</v>
+        <v>7145015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,19 +1732,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,22 +1754,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727782</v>
+        <v>129726761</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,14 +1797,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488694</v>
+        <v>488516</v>
       </c>
       <c r="R12" t="n">
-        <v>7144925</v>
+        <v>7145014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,14 +1834,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxt garnlav på björk.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,22 +1861,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727796</v>
+        <v>129727801</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488507</v>
+        <v>488339</v>
       </c>
       <c r="R13" t="n">
-        <v>7144870</v>
+        <v>7144937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727776</v>
+        <v>129727782</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488425</v>
+        <v>488694</v>
       </c>
       <c r="R14" t="n">
-        <v>7145015</v>
+        <v>7144925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,52 +2077,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727765</v>
+        <v>129727796</v>
       </c>
       <c r="B15" t="n">
-        <v>80218</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488701</v>
+        <v>488507</v>
       </c>
       <c r="R15" t="n">
-        <v>7144801</v>
+        <v>7144870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2152,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,34 +2161,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2212,45 +2179,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726761</v>
+        <v>129727765</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>80221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488516</v>
+        <v>488701</v>
       </c>
       <c r="R16" t="n">
-        <v>7145014</v>
+        <v>7144801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,19 +2254,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,28 +2270,54 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129727801</v>
+        <v>129726781</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>78100</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2325,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488339</v>
+        <v>488365</v>
       </c>
       <c r="R17" t="n">
-        <v>7144937</v>
+        <v>7144983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,14 +2382,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,12 +2409,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
         <v>129727947</v>
       </c>
       <c r="B18" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129716443</v>
       </c>
       <c r="B19" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>129726774</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>129727768</v>
       </c>
       <c r="B21" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>129726757</v>
       </c>
       <c r="B22" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129726772</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129727950</v>
       </c>
       <c r="B24" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>129727946</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>129726762</v>
       </c>
       <c r="B26" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129727786</v>
+        <v>129727772</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>80193</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,34 +3387,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489035</v>
+        <v>488470</v>
       </c>
       <c r="R27" t="n">
-        <v>7144832</v>
+        <v>7144960</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,7 +3458,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,8 +3467,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3478,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129727772</v>
+        <v>129716435</v>
       </c>
       <c r="B28" t="n">
-        <v>80190</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,41 +3522,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488470</v>
+        <v>488832</v>
       </c>
       <c r="R28" t="n">
-        <v>7144960</v>
+        <v>7144827</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3558,65 +3589,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B29" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,39 +3624,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R29" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,6 +3686,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3703,12 +3703,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3718,7 +3718,7 @@
         <v>129727945</v>
       </c>
       <c r="B30" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>129726760</v>
       </c>
       <c r="B31" t="n">
-        <v>89001</v>
+        <v>89004</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129727792</v>
+        <v>129726763</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,14 +3954,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488815</v>
+        <v>488626</v>
       </c>
       <c r="R32" t="n">
-        <v>7144788</v>
+        <v>7145010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,14 +3991,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4013,22 +4018,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129726763</v>
+        <v>129716436</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4056,14 +4061,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488626</v>
+        <v>489031</v>
       </c>
       <c r="R33" t="n">
-        <v>7145010</v>
+        <v>7144903</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4093,19 +4098,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4120,22 +4115,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129716436</v>
+        <v>129727792</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4167,10 +4162,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489031</v>
+        <v>488815</v>
       </c>
       <c r="R34" t="n">
-        <v>7144903</v>
+        <v>7144788</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4205,6 +4200,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4217,22 +4217,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129726765</v>
+        <v>129726771</v>
       </c>
       <c r="B35" t="n">
-        <v>82921</v>
+        <v>91625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4240,23 +4240,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4264,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488725</v>
+        <v>489056</v>
       </c>
       <c r="R35" t="n">
-        <v>7144925</v>
+        <v>7144853</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4299,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4309,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726784</v>
+        <v>129726765</v>
       </c>
       <c r="B36" t="n">
-        <v>83047</v>
+        <v>82924</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4371,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488335</v>
+        <v>488725</v>
       </c>
       <c r="R36" t="n">
-        <v>7144978</v>
+        <v>7144925</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4416,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726771</v>
+        <v>129726784</v>
       </c>
       <c r="B37" t="n">
-        <v>91622</v>
+        <v>83050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,19 +4450,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>489056</v>
+        <v>488335</v>
       </c>
       <c r="R37" t="n">
-        <v>7144853</v>
+        <v>7144978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,7 +4549,7 @@
         <v>129727802</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129716425</v>
+        <v>129726780</v>
       </c>
       <c r="B39" t="n">
-        <v>89001</v>
+        <v>83063</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488829</v>
+        <v>488414</v>
       </c>
       <c r="R39" t="n">
-        <v>7144835</v>
+        <v>7144975</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,9 +4716,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4733,22 +4743,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129727959</v>
+        <v>129716425</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>89004</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4756,34 +4766,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488762</v>
+        <v>488829</v>
       </c>
       <c r="R40" t="n">
-        <v>7144801</v>
+        <v>7144835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,22 +4840,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129727788</v>
+        <v>129726782</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>83058</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,34 +4863,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488989</v>
+        <v>488365</v>
       </c>
       <c r="R41" t="n">
-        <v>7144826</v>
+        <v>7144983</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4910,14 +4920,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4932,22 +4947,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129726782</v>
+        <v>129727959</v>
       </c>
       <c r="B42" t="n">
-        <v>83055</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4955,34 +4970,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488365</v>
+        <v>488762</v>
       </c>
       <c r="R42" t="n">
-        <v>7144983</v>
+        <v>7144801</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5012,19 +5027,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5039,22 +5044,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129726780</v>
+        <v>129727788</v>
       </c>
       <c r="B43" t="n">
-        <v>83060</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,34 +5067,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488414</v>
+        <v>488989</v>
       </c>
       <c r="R43" t="n">
-        <v>7144975</v>
+        <v>7144826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5119,19 +5124,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5146,22 +5146,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727948</v>
+        <v>129726775</v>
       </c>
       <c r="B44" t="n">
-        <v>91602</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5169,34 +5169,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488739</v>
+        <v>488851</v>
       </c>
       <c r="R44" t="n">
-        <v>7144803</v>
+        <v>7144825</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5226,9 +5226,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5243,22 +5253,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727785</v>
+        <v>129727777</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,10 +5300,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488865</v>
+        <v>488483</v>
       </c>
       <c r="R45" t="n">
-        <v>7144860</v>
+        <v>7144992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5330,7 +5340,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5357,10 +5367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727777</v>
+        <v>129727771</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>80193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5368,34 +5378,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488483</v>
+        <v>488511</v>
       </c>
       <c r="R46" t="n">
-        <v>7144992</v>
+        <v>7144867</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5449,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5441,8 +5458,34 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5459,10 +5502,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727771</v>
+        <v>129727770</v>
       </c>
       <c r="B47" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488511</v>
+        <v>488674</v>
       </c>
       <c r="R47" t="n">
-        <v>7144867</v>
+        <v>7144814</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5541,7 +5584,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5594,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727770</v>
+        <v>129727948</v>
       </c>
       <c r="B48" t="n">
-        <v>80190</v>
+        <v>91605</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5605,41 +5648,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488674</v>
+        <v>488739</v>
       </c>
       <c r="R48" t="n">
-        <v>7144814</v>
+        <v>7144803</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,55 +5710,24 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5732,7 +5737,7 @@
         <v>129727781</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5831,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727799</v>
+        <v>129727785</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488408</v>
+        <v>488865</v>
       </c>
       <c r="R50" t="n">
-        <v>7144970</v>
+        <v>7144860</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5906,7 +5911,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5933,10 +5938,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129716437</v>
+        <v>129727799</v>
       </c>
       <c r="B51" t="n">
-        <v>83055</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5944,21 +5949,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5968,10 +5973,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488533</v>
+        <v>488408</v>
       </c>
       <c r="R51" t="n">
-        <v>7144953</v>
+        <v>7144970</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,6 +6011,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6018,22 +6028,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129726775</v>
+        <v>129716437</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>83058</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,34 +6051,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488851</v>
+        <v>488533</v>
       </c>
       <c r="R52" t="n">
-        <v>7144825</v>
+        <v>7144953</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6098,19 +6108,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6125,57 +6125,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129727953</v>
+        <v>129716431</v>
       </c>
       <c r="B53" t="n">
-        <v>91984</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488400</v>
+        <v>488426</v>
       </c>
       <c r="R53" t="n">
-        <v>7144968</v>
+        <v>7145034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6222,22 +6222,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129716447</v>
+        <v>129727780</v>
       </c>
       <c r="B54" t="n">
-        <v>83060</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6245,21 +6245,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488731</v>
+        <v>488542</v>
       </c>
       <c r="R54" t="n">
-        <v>7144891</v>
+        <v>7144969</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,6 +6307,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6319,57 +6324,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129716431</v>
+        <v>129727953</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>91987</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488426</v>
+        <v>488400</v>
       </c>
       <c r="R55" t="n">
-        <v>7145034</v>
+        <v>7144968</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,22 +6421,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129727780</v>
+        <v>129716447</v>
       </c>
       <c r="B56" t="n">
-        <v>79084</v>
+        <v>83063</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6439,21 +6444,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6463,10 +6468,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488542</v>
+        <v>488731</v>
       </c>
       <c r="R56" t="n">
-        <v>7144969</v>
+        <v>7144891</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6501,11 +6506,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6518,22 +6518,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129727791</v>
+        <v>129716430</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>91625</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,23 +6541,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6565,10 +6561,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488907</v>
+        <v>488835</v>
       </c>
       <c r="R57" t="n">
-        <v>7144779</v>
+        <v>7144824</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6603,11 +6599,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6620,22 +6611,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129716430</v>
+        <v>129716440</v>
       </c>
       <c r="B58" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,10 +6654,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488835</v>
+        <v>488547</v>
       </c>
       <c r="R58" t="n">
-        <v>7144824</v>
+        <v>7144971</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6725,30 +6716,34 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716440</v>
+        <v>129716428</v>
       </c>
       <c r="B59" t="n">
-        <v>91622</v>
+        <v>92323</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6756,10 +6751,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488547</v>
+        <v>489052</v>
       </c>
       <c r="R59" t="n">
-        <v>7144971</v>
+        <v>7144873</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6818,10 +6813,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129727800</v>
+        <v>129716442</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>91625</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6829,23 +6824,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6853,10 +6844,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488375</v>
+        <v>488630</v>
       </c>
       <c r="R60" t="n">
-        <v>7144951</v>
+        <v>7145015</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6891,11 +6882,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt på gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6908,42 +6894,46 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716442</v>
+        <v>129716423</v>
       </c>
       <c r="B61" t="n">
-        <v>91622</v>
+        <v>92323</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6951,10 +6941,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488630</v>
+        <v>488296</v>
       </c>
       <c r="R61" t="n">
-        <v>7145015</v>
+        <v>7145038</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,32 +7003,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129716428</v>
+        <v>129727791</v>
       </c>
       <c r="B62" t="n">
-        <v>92320</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7048,10 +7038,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>489052</v>
+        <v>488907</v>
       </c>
       <c r="R62" t="n">
-        <v>7144873</v>
+        <v>7144779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7086,6 +7076,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7098,44 +7093,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129716423</v>
+        <v>129727800</v>
       </c>
       <c r="B63" t="n">
-        <v>92320</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7145,10 +7140,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488296</v>
+        <v>488375</v>
       </c>
       <c r="R63" t="n">
-        <v>7145038</v>
+        <v>7144951</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7183,6 +7178,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt på gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7195,12 +7195,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
         <v>129726764</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>129727793</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>129727798</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>129716433</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>129727790</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>129716432</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>129727787</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>129727958</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>129727951</v>
       </c>
       <c r="B72" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>129727954</v>
       </c>
       <c r="B73" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8212,10 +8212,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129716429</v>
+        <v>129726778</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8243,14 +8243,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488440</v>
+        <v>488522</v>
       </c>
       <c r="R74" t="n">
-        <v>7144976</v>
+        <v>7144974</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8280,9 +8280,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8297,22 +8307,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129726779</v>
+        <v>129716429</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8340,14 +8350,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488452</v>
+        <v>488440</v>
       </c>
       <c r="R75" t="n">
-        <v>7144979</v>
+        <v>7144976</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8377,19 +8387,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8404,22 +8404,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129726778</v>
+        <v>129727778</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8447,14 +8447,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488522</v>
+        <v>488513</v>
       </c>
       <c r="R76" t="n">
-        <v>7144974</v>
+        <v>7144973</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8484,19 +8484,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:10</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8511,22 +8506,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129727778</v>
+        <v>129726779</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8554,14 +8549,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488513</v>
+        <v>488452</v>
       </c>
       <c r="R77" t="n">
-        <v>7144973</v>
+        <v>7144979</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8591,14 +8586,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
         <v>129716424</v>
       </c>
       <c r="B78" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727769</v>
+        <v>129726777</v>
       </c>
       <c r="B79" t="n">
-        <v>80190</v>
+        <v>79087</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,41 +8733,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488758</v>
+        <v>488570</v>
       </c>
       <c r="R79" t="n">
-        <v>7144774</v>
+        <v>7144960</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8797,14 +8790,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8813,54 +8811,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716434</v>
+        <v>129716445</v>
       </c>
       <c r="B80" t="n">
-        <v>91598</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8868,21 +8840,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8892,10 +8864,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488618</v>
+        <v>488685</v>
       </c>
       <c r="R80" t="n">
-        <v>7144922</v>
+        <v>7144909</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8954,10 +8926,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129727957</v>
+        <v>129716441</v>
       </c>
       <c r="B81" t="n">
-        <v>91598</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8965,34 +8937,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488591</v>
+        <v>488921</v>
       </c>
       <c r="R81" t="n">
-        <v>7144844</v>
+        <v>7144886</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9039,22 +9011,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129716445</v>
+        <v>129716422</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9086,10 +9058,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488685</v>
+        <v>488767</v>
       </c>
       <c r="R82" t="n">
-        <v>7144909</v>
+        <v>7144853</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9148,45 +9120,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129716422</v>
+        <v>129727767</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>80221</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488767</v>
+        <v>488658</v>
       </c>
       <c r="R83" t="n">
-        <v>7144853</v>
+        <v>7144806</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9221,34 +9200,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129726777</v>
+        <v>129727769</v>
       </c>
       <c r="B84" t="n">
-        <v>79084</v>
+        <v>80193</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9256,34 +9266,41 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488570</v>
+        <v>488758</v>
       </c>
       <c r="R84" t="n">
-        <v>7144960</v>
+        <v>7144774</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9313,19 +9330,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9334,28 +9346,54 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129716441</v>
+        <v>129716434</v>
       </c>
       <c r="B85" t="n">
-        <v>79084</v>
+        <v>91601</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9363,21 +9401,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9387,10 +9425,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488921</v>
+        <v>488618</v>
       </c>
       <c r="R85" t="n">
-        <v>7144886</v>
+        <v>7144922</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9449,52 +9487,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727767</v>
+        <v>129727957</v>
       </c>
       <c r="B86" t="n">
-        <v>80218</v>
+        <v>91601</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488658</v>
+        <v>488591</v>
       </c>
       <c r="R86" t="n">
-        <v>7144806</v>
+        <v>7144844</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9529,65 +9560,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129726773</v>
+        <v>129727795</v>
       </c>
       <c r="B87" t="n">
-        <v>91602</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9595,34 +9595,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>489020</v>
+        <v>488737</v>
       </c>
       <c r="R87" t="n">
-        <v>7144867</v>
+        <v>7144797</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,19 +9652,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På en levande gammal gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9679,22 +9674,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727795</v>
+        <v>129727794</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9726,10 +9721,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488737</v>
+        <v>488763</v>
       </c>
       <c r="R88" t="n">
-        <v>7144797</v>
+        <v>7144775</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9766,7 +9761,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På en levande gammal gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9793,10 +9788,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727794</v>
+        <v>129727960</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9824,14 +9819,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488763</v>
+        <v>488374</v>
       </c>
       <c r="R89" t="n">
-        <v>7144775</v>
+        <v>7144949</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9868,7 +9863,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9883,22 +9878,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727960</v>
+        <v>129727783</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9926,14 +9921,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488374</v>
+        <v>488709</v>
       </c>
       <c r="R90" t="n">
-        <v>7144949</v>
+        <v>7144911</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9965,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9985,57 +9980,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727783</v>
+        <v>129726769</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>75071</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488709</v>
+        <v>489064</v>
       </c>
       <c r="R91" t="n">
-        <v>7144911</v>
+        <v>7144843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10065,14 +10060,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På levande gran i gammal granskog.</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,48 +10083,63 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726769</v>
+        <v>129726773</v>
       </c>
       <c r="B92" t="n">
-        <v>75068</v>
+        <v>91605</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10134,10 +10149,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489064</v>
+        <v>489020</v>
       </c>
       <c r="R92" t="n">
-        <v>7144843</v>
+        <v>7144867</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10169,7 +10184,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10179,7 +10194,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10190,21 +10205,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10221,10 +10221,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129726783</v>
+        <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>79084</v>
+        <v>91601</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10232,34 +10232,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488353</v>
+        <v>488750</v>
       </c>
       <c r="R93" t="n">
-        <v>7144965</v>
+        <v>7144804</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10289,19 +10289,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10316,22 +10306,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129727956</v>
+        <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>91598</v>
+        <v>79087</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10339,34 +10329,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488750</v>
+        <v>488353</v>
       </c>
       <c r="R94" t="n">
-        <v>7144804</v>
+        <v>7144965</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10396,9 +10386,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10413,39 +10413,39 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730469</v>
+        <v>129730439</v>
       </c>
       <c r="B95" t="n">
-        <v>57841</v>
+        <v>57740</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488507</v>
+        <v>488746</v>
       </c>
       <c r="R95" t="n">
-        <v>7144936</v>
+        <v>7144786</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,10 +10527,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730462</v>
+        <v>129730469</v>
       </c>
       <c r="B96" t="n">
-        <v>92320</v>
+        <v>57844</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10538,21 +10538,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10562,10 +10562,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>489017</v>
+        <v>488507</v>
       </c>
       <c r="R96" t="n">
-        <v>7144821</v>
+        <v>7144936</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10598,6 +10598,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10624,32 +10629,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B97" t="n">
-        <v>57737</v>
+        <v>92323</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10659,10 +10664,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R97" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10695,11 +10700,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10729,7 +10729,7 @@
         <v>129730460</v>
       </c>
       <c r="B98" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>129730457</v>
       </c>
       <c r="B99" t="n">
-        <v>91973</v>
+        <v>91976</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10920,10 +10920,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129730474</v>
+        <v>129730449</v>
       </c>
       <c r="B100" t="n">
-        <v>91598</v>
+        <v>80193</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10931,21 +10931,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488676</v>
+        <v>488414</v>
       </c>
       <c r="R100" t="n">
-        <v>7144870</v>
+        <v>7144940</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11020,7 +11020,7 @@
         <v>129730473</v>
       </c>
       <c r="B101" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730449</v>
+        <v>129730474</v>
       </c>
       <c r="B102" t="n">
-        <v>80190</v>
+        <v>91601</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11125,21 +11125,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488414</v>
+        <v>488676</v>
       </c>
       <c r="R102" t="n">
-        <v>7144940</v>
+        <v>7144870</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11214,7 +11214,7 @@
         <v>129730465</v>
       </c>
       <c r="B103" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730461</v>
+        <v>129730443</v>
       </c>
       <c r="B104" t="n">
-        <v>91602</v>
+        <v>57898</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488464</v>
+        <v>488348</v>
       </c>
       <c r="R104" t="n">
-        <v>7144953</v>
+        <v>7144901</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730451</v>
+        <v>129730461</v>
       </c>
       <c r="B105" t="n">
-        <v>80189</v>
+        <v>91605</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488709</v>
+        <v>488464</v>
       </c>
       <c r="R105" t="n">
-        <v>7144786</v>
+        <v>7144953</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730443</v>
+        <v>129730451</v>
       </c>
       <c r="B106" t="n">
-        <v>57895</v>
+        <v>80192</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11513,21 +11513,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488348</v>
+        <v>488709</v>
       </c>
       <c r="R106" t="n">
-        <v>7144901</v>
+        <v>7144786</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11599,32 +11599,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129730441</v>
+        <v>129730454</v>
       </c>
       <c r="B107" t="n">
-        <v>56927</v>
+        <v>57740</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488667</v>
+        <v>488746</v>
       </c>
       <c r="R107" t="n">
-        <v>7144793</v>
+        <v>7144785</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Höna</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både färska och äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11701,32 +11701,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129730454</v>
+        <v>129730441</v>
       </c>
       <c r="B108" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11736,10 +11736,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488746</v>
+        <v>488667</v>
       </c>
       <c r="R108" t="n">
-        <v>7144785</v>
+        <v>7144793</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både färska och äldre</t>
+          <t>Höna</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11806,7 +11806,7 @@
         <v>129730477</v>
       </c>
       <c r="B109" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>129730452</v>
       </c>
       <c r="B110" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>129730450</v>
       </c>
       <c r="B111" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>129730448</v>
       </c>
       <c r="B112" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>83060</v>
+        <v>83063</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>129730464</v>
       </c>
       <c r="B114" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>129730470</v>
       </c>
       <c r="B115" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>129730463</v>
       </c>
       <c r="B116" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>129730468</v>
       </c>
       <c r="B117" t="n">
-        <v>78097</v>
+        <v>78100</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12696,10 +12696,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730458</v>
+        <v>129730471</v>
       </c>
       <c r="B118" t="n">
-        <v>91602</v>
+        <v>91601</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12707,21 +12707,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>489058</v>
+        <v>488625</v>
       </c>
       <c r="R118" t="n">
-        <v>7144802</v>
+        <v>7144878</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12793,10 +12793,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730471</v>
+        <v>129730458</v>
       </c>
       <c r="B119" t="n">
-        <v>91598</v>
+        <v>91605</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12804,21 +12804,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12828,10 +12828,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488625</v>
+        <v>489058</v>
       </c>
       <c r="R119" t="n">
-        <v>7144878</v>
+        <v>7144802</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,7 +12893,7 @@
         <v>129730476</v>
       </c>
       <c r="B120" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12987,10 +12987,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730459</v>
+        <v>129730478</v>
       </c>
       <c r="B121" t="n">
-        <v>91602</v>
+        <v>91625</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12998,23 +12998,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13022,10 +13018,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488604</v>
+        <v>488436</v>
       </c>
       <c r="R121" t="n">
-        <v>7144985</v>
+        <v>7144967</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13087,7 +13083,7 @@
         <v>129730456</v>
       </c>
       <c r="B122" t="n">
-        <v>91973</v>
+        <v>91976</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13181,10 +13177,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730478</v>
+        <v>129730459</v>
       </c>
       <c r="B123" t="n">
-        <v>91622</v>
+        <v>91605</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13192,19 +13188,23 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488436</v>
+        <v>488604</v>
       </c>
       <c r="R123" t="n">
-        <v>7144967</v>
+        <v>7144985</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13277,7 +13277,7 @@
         <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>129730446</v>
       </c>
       <c r="B125" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>129730447</v>
       </c>
       <c r="B126" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>129730466</v>
       </c>
       <c r="B127" t="n">
-        <v>83060</v>
+        <v>83063</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>129730453</v>
       </c>
       <c r="B128" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13759,10 +13759,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730475</v>
+        <v>129730472</v>
       </c>
       <c r="B129" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488459</v>
+        <v>488622</v>
       </c>
       <c r="R129" t="n">
-        <v>7144958</v>
+        <v>7144899</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13856,10 +13856,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730472</v>
+        <v>129730475</v>
       </c>
       <c r="B130" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488622</v>
+        <v>488459</v>
       </c>
       <c r="R130" t="n">
-        <v>7144899</v>
+        <v>7144958</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13956,7 +13956,7 @@
         <v>129730440</v>
       </c>
       <c r="B131" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726765</v>
+        <v>129727802</v>
       </c>
       <c r="B36" t="n">
-        <v>82924</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,34 +4343,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488725</v>
+        <v>488268</v>
       </c>
       <c r="R36" t="n">
-        <v>7144925</v>
+        <v>7145078</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,19 +4400,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,22 +4422,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726784</v>
+        <v>129726765</v>
       </c>
       <c r="B37" t="n">
-        <v>83050</v>
+        <v>82924</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4445,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4469,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488335</v>
+        <v>488725</v>
       </c>
       <c r="R37" t="n">
-        <v>7144978</v>
+        <v>7144925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4504,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4514,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,10 +4541,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129727802</v>
+        <v>129726784</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>83050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,34 +4552,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488268</v>
+        <v>488335</v>
       </c>
       <c r="R38" t="n">
-        <v>7145078</v>
+        <v>7144978</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,14 +4609,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,12 +4636,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726775</v>
+        <v>129727781</v>
       </c>
       <c r="B44" t="n">
         <v>79087</v>
@@ -5189,14 +5189,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488851</v>
+        <v>488586</v>
       </c>
       <c r="R44" t="n">
-        <v>7144825</v>
+        <v>7144955</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5226,19 +5226,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5253,19 +5248,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727777</v>
+        <v>129727785</v>
       </c>
       <c r="B45" t="n">
         <v>79087</v>
@@ -5300,10 +5295,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488483</v>
+        <v>488865</v>
       </c>
       <c r="R45" t="n">
-        <v>7144992</v>
+        <v>7144860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5340,7 +5335,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5367,10 +5362,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727771</v>
+        <v>129727799</v>
       </c>
       <c r="B46" t="n">
-        <v>80193</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,41 +5373,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488511</v>
+        <v>488408</v>
       </c>
       <c r="R46" t="n">
-        <v>7144867</v>
+        <v>7144970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5449,7 +5437,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5458,34 +5446,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5502,10 +5464,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727770</v>
+        <v>129716437</v>
       </c>
       <c r="B47" t="n">
-        <v>80193</v>
+        <v>83058</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5513,41 +5475,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488674</v>
+        <v>488533</v>
       </c>
       <c r="R47" t="n">
-        <v>7144814</v>
+        <v>7144953</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5582,65 +5537,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727948</v>
+        <v>129726775</v>
       </c>
       <c r="B48" t="n">
-        <v>91605</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5648,34 +5572,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488739</v>
+        <v>488851</v>
       </c>
       <c r="R48" t="n">
-        <v>7144803</v>
+        <v>7144825</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,9 +5629,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,19 +5656,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727781</v>
+        <v>129727777</v>
       </c>
       <c r="B49" t="n">
         <v>79087</v>
@@ -5769,10 +5703,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488586</v>
+        <v>488483</v>
       </c>
       <c r="R49" t="n">
-        <v>7144955</v>
+        <v>7144992</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,10 +5770,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727785</v>
+        <v>129727771</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5847,34 +5781,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488865</v>
+        <v>488511</v>
       </c>
       <c r="R50" t="n">
-        <v>7144860</v>
+        <v>7144867</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5911,7 +5852,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5920,8 +5861,34 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5938,10 +5905,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727799</v>
+        <v>129727770</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,34 +5916,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488408</v>
+        <v>488674</v>
       </c>
       <c r="R51" t="n">
-        <v>7144970</v>
+        <v>7144814</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6013,7 +5987,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6022,8 +5996,34 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6040,10 +6040,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129716437</v>
+        <v>129727948</v>
       </c>
       <c r="B52" t="n">
-        <v>83058</v>
+        <v>91605</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,34 +6051,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488533</v>
+        <v>488739</v>
       </c>
       <c r="R52" t="n">
-        <v>7144953</v>
+        <v>7144803</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6125,12 +6125,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129726777</v>
+        <v>129727769</v>
       </c>
       <c r="B79" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,34 +8733,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488570</v>
+        <v>488758</v>
       </c>
       <c r="R79" t="n">
-        <v>7144960</v>
+        <v>7144774</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8790,19 +8797,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8811,28 +8813,54 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716445</v>
+        <v>129716434</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>91601</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8840,21 +8868,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8864,10 +8892,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488685</v>
+        <v>488618</v>
       </c>
       <c r="R80" t="n">
-        <v>7144909</v>
+        <v>7144922</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8926,10 +8954,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129716441</v>
+        <v>129727957</v>
       </c>
       <c r="B81" t="n">
-        <v>79087</v>
+        <v>91601</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,34 +8965,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488921</v>
+        <v>488591</v>
       </c>
       <c r="R81" t="n">
-        <v>7144886</v>
+        <v>7144844</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9011,19 +9039,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129716422</v>
+        <v>129726777</v>
       </c>
       <c r="B82" t="n">
         <v>79087</v>
@@ -9054,14 +9082,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488767</v>
+        <v>488570</v>
       </c>
       <c r="R82" t="n">
-        <v>7144853</v>
+        <v>7144960</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9091,9 +9119,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9108,64 +9146,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129727767</v>
+        <v>129716445</v>
       </c>
       <c r="B83" t="n">
-        <v>80221</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488658</v>
+        <v>488685</v>
       </c>
       <c r="R83" t="n">
-        <v>7144806</v>
+        <v>7144909</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9200,65 +9231,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På en levande sälg.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129727769</v>
+        <v>129716441</v>
       </c>
       <c r="B84" t="n">
-        <v>80193</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9266,41 +9266,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488758</v>
+        <v>488921</v>
       </c>
       <c r="R84" t="n">
-        <v>7144774</v>
+        <v>7144886</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9335,65 +9328,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129716434</v>
+        <v>129716422</v>
       </c>
       <c r="B85" t="n">
-        <v>91601</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9401,21 +9363,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9425,10 +9387,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488618</v>
+        <v>488767</v>
       </c>
       <c r="R85" t="n">
-        <v>7144922</v>
+        <v>7144853</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9487,45 +9449,52 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129727957</v>
+        <v>129727767</v>
       </c>
       <c r="B86" t="n">
-        <v>91601</v>
+        <v>80221</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488591</v>
+        <v>488658</v>
       </c>
       <c r="R86" t="n">
-        <v>7144844</v>
+        <v>7144806</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9560,24 +9529,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129727794</v>
+        <v>129726773</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>91605</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9697,34 +9697,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488763</v>
+        <v>489020</v>
       </c>
       <c r="R88" t="n">
-        <v>7144775</v>
+        <v>7144867</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9754,14 +9754,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9776,19 +9781,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727960</v>
+        <v>129727794</v>
       </c>
       <c r="B89" t="n">
         <v>79087</v>
@@ -9819,14 +9824,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488374</v>
+        <v>488763</v>
       </c>
       <c r="R89" t="n">
-        <v>7144949</v>
+        <v>7144775</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9863,7 +9868,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9878,19 +9883,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727783</v>
+        <v>129727960</v>
       </c>
       <c r="B90" t="n">
         <v>79087</v>
@@ -9921,14 +9926,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488709</v>
+        <v>488374</v>
       </c>
       <c r="R90" t="n">
-        <v>7144911</v>
+        <v>7144949</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9965,7 +9970,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På levande gran i gammal granskog.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9980,57 +9985,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129726769</v>
+        <v>129727783</v>
       </c>
       <c r="B91" t="n">
-        <v>75071</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>489064</v>
+        <v>488709</v>
       </c>
       <c r="R91" t="n">
-        <v>7144843</v>
+        <v>7144911</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10060,19 +10065,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:03</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,63 +10083,48 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726773</v>
+        <v>129726769</v>
       </c>
       <c r="B92" t="n">
-        <v>91605</v>
+        <v>75071</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10149,10 +10134,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489020</v>
+        <v>489064</v>
       </c>
       <c r="R92" t="n">
-        <v>7144867</v>
+        <v>7144843</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10184,7 +10169,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10194,7 +10179,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10205,6 +10190,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11308,10 +11308,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129730443</v>
+        <v>129730461</v>
       </c>
       <c r="B104" t="n">
-        <v>57898</v>
+        <v>91605</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11319,21 +11319,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488348</v>
+        <v>488464</v>
       </c>
       <c r="R104" t="n">
-        <v>7144901</v>
+        <v>7144953</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129730461</v>
+        <v>129730451</v>
       </c>
       <c r="B105" t="n">
-        <v>91605</v>
+        <v>80192</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488464</v>
+        <v>488709</v>
       </c>
       <c r="R105" t="n">
-        <v>7144953</v>
+        <v>7144786</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129730451</v>
+        <v>129730443</v>
       </c>
       <c r="B106" t="n">
-        <v>80192</v>
+        <v>57898</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11513,21 +11513,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488709</v>
+        <v>488348</v>
       </c>
       <c r="R106" t="n">
-        <v>7144786</v>
+        <v>7144901</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730463</v>
+        <v>129730468</v>
       </c>
       <c r="B116" t="n">
-        <v>57740</v>
+        <v>78100</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12508,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488546</v>
+        <v>488763</v>
       </c>
       <c r="R116" t="n">
-        <v>7144950</v>
+        <v>7144808</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12568,11 +12568,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12599,10 +12594,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730468</v>
+        <v>129730463</v>
       </c>
       <c r="B117" t="n">
-        <v>78100</v>
+        <v>57740</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12610,21 +12605,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12634,10 +12629,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488763</v>
+        <v>488546</v>
       </c>
       <c r="R117" t="n">
-        <v>7144808</v>
+        <v>7144950</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12670,6 +12665,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13759,32 +13759,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129730472</v>
+        <v>129730440</v>
       </c>
       <c r="B129" t="n">
-        <v>91601</v>
+        <v>56930</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1108</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13794,10 +13794,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>488622</v>
+        <v>489134</v>
       </c>
       <c r="R129" t="n">
-        <v>7144899</v>
+        <v>7144763</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13830,6 +13830,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13856,7 +13861,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129730475</v>
+        <v>129730472</v>
       </c>
       <c r="B130" t="n">
         <v>91601</v>
@@ -13891,10 +13896,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>488459</v>
+        <v>488622</v>
       </c>
       <c r="R130" t="n">
-        <v>7144958</v>
+        <v>7144899</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13953,32 +13958,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129730440</v>
+        <v>129730475</v>
       </c>
       <c r="B131" t="n">
-        <v>56930</v>
+        <v>91601</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13988,10 +13993,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>489134</v>
+        <v>488459</v>
       </c>
       <c r="R131" t="n">
-        <v>7144763</v>
+        <v>7144958</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14024,11 +14029,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129727802</v>
+        <v>129726765</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>82924</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,34 +4343,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488268</v>
+        <v>488725</v>
       </c>
       <c r="R36" t="n">
-        <v>7145078</v>
+        <v>7144925</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,14 +4400,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4422,22 +4427,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726765</v>
+        <v>129726784</v>
       </c>
       <c r="B37" t="n">
-        <v>82924</v>
+        <v>83050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4445,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4469,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488725</v>
+        <v>488335</v>
       </c>
       <c r="R37" t="n">
-        <v>7144925</v>
+        <v>7144978</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4504,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4514,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4541,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129726784</v>
+        <v>129727802</v>
       </c>
       <c r="B38" t="n">
-        <v>83050</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4552,34 +4557,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488335</v>
+        <v>488268</v>
       </c>
       <c r="R38" t="n">
-        <v>7144978</v>
+        <v>7145078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,19 +4614,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:39</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,12 +4636,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129727781</v>
+        <v>129726775</v>
       </c>
       <c r="B44" t="n">
         <v>79087</v>
@@ -5189,14 +5189,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488586</v>
+        <v>488851</v>
       </c>
       <c r="R44" t="n">
-        <v>7144955</v>
+        <v>7144825</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5226,14 +5226,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5248,19 +5253,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727785</v>
+        <v>129727777</v>
       </c>
       <c r="B45" t="n">
         <v>79087</v>
@@ -5295,10 +5300,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488865</v>
+        <v>488483</v>
       </c>
       <c r="R45" t="n">
-        <v>7144860</v>
+        <v>7144992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5335,7 +5340,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5362,10 +5367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727799</v>
+        <v>129727771</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5373,34 +5378,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488408</v>
+        <v>488511</v>
       </c>
       <c r="R46" t="n">
-        <v>7144970</v>
+        <v>7144867</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5437,7 +5449,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5446,8 +5458,34 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5464,10 +5502,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129716437</v>
+        <v>129727770</v>
       </c>
       <c r="B47" t="n">
-        <v>83058</v>
+        <v>80193</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5475,34 +5513,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488533</v>
+        <v>488674</v>
       </c>
       <c r="R47" t="n">
-        <v>7144953</v>
+        <v>7144814</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5537,34 +5582,65 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129726775</v>
+        <v>129727948</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>91605</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5572,34 +5648,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488851</v>
+        <v>488739</v>
       </c>
       <c r="R48" t="n">
-        <v>7144825</v>
+        <v>7144803</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5629,19 +5705,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5656,19 +5722,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727777</v>
+        <v>129727781</v>
       </c>
       <c r="B49" t="n">
         <v>79087</v>
@@ -5703,10 +5769,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488483</v>
+        <v>488586</v>
       </c>
       <c r="R49" t="n">
-        <v>7144992</v>
+        <v>7144955</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5770,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727771</v>
+        <v>129727785</v>
       </c>
       <c r="B50" t="n">
-        <v>80193</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5781,41 +5847,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488511</v>
+        <v>488865</v>
       </c>
       <c r="R50" t="n">
-        <v>7144867</v>
+        <v>7144860</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5852,7 +5911,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På en levande gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5861,34 +5920,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5905,10 +5938,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727770</v>
+        <v>129727799</v>
       </c>
       <c r="B51" t="n">
-        <v>80193</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5916,41 +5949,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488674</v>
+        <v>488408</v>
       </c>
       <c r="R51" t="n">
-        <v>7144814</v>
+        <v>7144970</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5987,7 +6013,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5996,34 +6022,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6040,10 +6040,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129727948</v>
+        <v>129716437</v>
       </c>
       <c r="B52" t="n">
-        <v>91605</v>
+        <v>83058</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,34 +6051,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488739</v>
+        <v>488533</v>
       </c>
       <c r="R52" t="n">
-        <v>7144803</v>
+        <v>7144953</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6125,12 +6125,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -10425,32 +10425,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129730439</v>
+        <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488746</v>
+        <v>489017</v>
       </c>
       <c r="R95" t="n">
-        <v>7144786</v>
+        <v>7144821</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10527,27 +10522,27 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129730469</v>
+        <v>129730439</v>
       </c>
       <c r="B96" t="n">
-        <v>57844</v>
+        <v>57740</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488507</v>
+        <v>488746</v>
       </c>
       <c r="R96" t="n">
-        <v>7144936</v>
+        <v>7144786</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10602,7 +10597,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>Väldigt rikligt med ringhack på gammal gran. Kraftig utveckling av sav. Både äldre och färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10629,10 +10624,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129730462</v>
+        <v>129730469</v>
       </c>
       <c r="B97" t="n">
-        <v>92323</v>
+        <v>57844</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10640,21 +10635,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10664,10 +10659,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>489017</v>
+        <v>488507</v>
       </c>
       <c r="R97" t="n">
-        <v>7144821</v>
+        <v>7144936</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10700,6 +10695,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11017,32 +11017,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730473</v>
+        <v>129730465</v>
       </c>
       <c r="B101" t="n">
-        <v>91601</v>
+        <v>80221</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>489028</v>
+        <v>488705</v>
       </c>
       <c r="R101" t="n">
-        <v>7144803</v>
+        <v>7144862</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730474</v>
+        <v>129730473</v>
       </c>
       <c r="B102" t="n">
         <v>91601</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488676</v>
+        <v>489028</v>
       </c>
       <c r="R102" t="n">
-        <v>7144870</v>
+        <v>7144803</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730465</v>
+        <v>129730474</v>
       </c>
       <c r="B103" t="n">
-        <v>80221</v>
+        <v>91601</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488705</v>
+        <v>488676</v>
       </c>
       <c r="R103" t="n">
-        <v>7144862</v>
+        <v>7144870</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13565,10 +13565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129730466</v>
+        <v>129730453</v>
       </c>
       <c r="B127" t="n">
-        <v>83063</v>
+        <v>79087</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13576,21 +13576,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>489083</v>
+        <v>488401</v>
       </c>
       <c r="R127" t="n">
-        <v>7144799</v>
+        <v>7144950</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13662,10 +13662,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129730453</v>
+        <v>129730466</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>83063</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13673,21 +13673,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>488401</v>
+        <v>489083</v>
       </c>
       <c r="R128" t="n">
-        <v>7144950</v>
+        <v>7144799</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129727955</v>
+        <v>129716427</v>
       </c>
       <c r="B2" t="n">
-        <v>91601</v>
+        <v>83051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489154</v>
+        <v>488400</v>
       </c>
       <c r="R2" t="n">
-        <v>7144751</v>
+        <v>7144977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129727773</v>
+        <v>129727955</v>
       </c>
       <c r="B3" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,23 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488610</v>
+        <v>489154</v>
       </c>
       <c r="R3" t="n">
-        <v>7144833</v>
+        <v>7144751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,65 +845,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129716427</v>
+        <v>129727773</v>
       </c>
       <c r="B4" t="n">
-        <v>83050</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488400</v>
+        <v>488610</v>
       </c>
       <c r="R4" t="n">
-        <v>7144977</v>
+        <v>7144833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,24 +949,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
         <v>129726770</v>
       </c>
       <c r="B5" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129726758</v>
       </c>
       <c r="B6" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129727797</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>129727766</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>129727952</v>
       </c>
       <c r="B9" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>129716439</v>
       </c>
       <c r="B10" t="n">
-        <v>83050</v>
+        <v>83051</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>129727776</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>129726761</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>129727801</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129727782</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>129727796</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>129727765</v>
       </c>
       <c r="B16" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727947</v>
+        <v>129727768</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2432,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488803</v>
+        <v>488790</v>
       </c>
       <c r="R18" t="n">
-        <v>7144779</v>
+        <v>7144786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,6 +2506,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i en grov gammal gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2502,26 +2519,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129716443</v>
+        <v>129727947</v>
       </c>
       <c r="B19" t="n">
-        <v>91601</v>
+        <v>91606</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,34 +2571,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488470</v>
+        <v>488803</v>
       </c>
       <c r="R19" t="n">
-        <v>7144975</v>
+        <v>7144779</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,22 +2645,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129726774</v>
+        <v>129716443</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,34 +2668,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489025</v>
+        <v>488470</v>
       </c>
       <c r="R20" t="n">
-        <v>7144875</v>
+        <v>7144975</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,19 +2725,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,22 +2742,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129727768</v>
+        <v>129726774</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,46 +2765,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488790</v>
+        <v>489025</v>
       </c>
       <c r="R21" t="n">
-        <v>7144786</v>
+        <v>7144875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,14 +2822,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i en grov gammal gran.</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,41 +2845,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
         <v>129726757</v>
       </c>
       <c r="B22" t="n">
-        <v>83050</v>
+        <v>83051</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>129726772</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129727950</v>
       </c>
       <c r="B24" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>129727946</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>129726762</v>
       </c>
       <c r="B26" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>129727772</v>
       </c>
       <c r="B27" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129716435</v>
+        <v>129727786</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,39 +3522,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488832</v>
+        <v>489035</v>
       </c>
       <c r="R28" t="n">
-        <v>7144827</v>
+        <v>7144832</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,6 +3584,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3601,22 +3601,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129727786</v>
+        <v>129716435</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,34 +3624,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489035</v>
+        <v>488832</v>
       </c>
       <c r="R29" t="n">
-        <v>7144832</v>
+        <v>7144827</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,11 +3691,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På stående döda granar med potentiella födosökspår efter tretåig hackspett (barkskalade stammar).</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3703,22 +3703,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129727945</v>
+        <v>129726763</v>
       </c>
       <c r="B30" t="n">
-        <v>91619</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489010</v>
+        <v>488626</v>
       </c>
       <c r="R30" t="n">
-        <v>7144808</v>
+        <v>7145010</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,40 +3783,49 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129726760</v>
+        <v>129716436</v>
       </c>
       <c r="B31" t="n">
-        <v>89004</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,34 +3833,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488426</v>
+        <v>489031</v>
       </c>
       <c r="R31" t="n">
-        <v>7145052</v>
+        <v>7144903</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3884,19 +3890,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3911,22 +3907,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129726763</v>
+        <v>129727792</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,14 +3950,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488626</v>
+        <v>488815</v>
       </c>
       <c r="R32" t="n">
-        <v>7145010</v>
+        <v>7144788</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,19 +3987,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en gammal levande gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4018,22 +4009,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129716436</v>
+        <v>129726760</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>89005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,34 +4032,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489031</v>
+        <v>488426</v>
       </c>
       <c r="R33" t="n">
-        <v>7144903</v>
+        <v>7145052</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4098,9 +4089,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,22 +4116,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129727792</v>
+        <v>129727945</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>91620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4138,34 +4139,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488815</v>
+        <v>489010</v>
       </c>
       <c r="R34" t="n">
-        <v>7144788</v>
+        <v>7144808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,29 +4204,25 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På en gammal levande gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4232,7 +4232,7 @@
         <v>129726771</v>
       </c>
       <c r="B35" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129726765</v>
+        <v>129726784</v>
       </c>
       <c r="B36" t="n">
-        <v>82924</v>
+        <v>83051</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488725</v>
+        <v>488335</v>
       </c>
       <c r="R36" t="n">
-        <v>7144925</v>
+        <v>7144978</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129726784</v>
+        <v>129726765</v>
       </c>
       <c r="B37" t="n">
-        <v>83050</v>
+        <v>82925</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488335</v>
+        <v>488725</v>
       </c>
       <c r="R37" t="n">
-        <v>7144978</v>
+        <v>7144925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,7 +4549,7 @@
         <v>129727802</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129726780</v>
+        <v>129716425</v>
       </c>
       <c r="B39" t="n">
-        <v>83063</v>
+        <v>89005</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488414</v>
+        <v>488829</v>
       </c>
       <c r="R39" t="n">
-        <v>7144975</v>
+        <v>7144835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,19 +4716,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,22 +4733,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129716425</v>
+        <v>129726780</v>
       </c>
       <c r="B40" t="n">
-        <v>89004</v>
+        <v>83064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,34 +4756,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488829</v>
+        <v>488414</v>
       </c>
       <c r="R40" t="n">
-        <v>7144835</v>
+        <v>7144975</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4823,9 +4813,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4840,12 +4840,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
         <v>129726782</v>
       </c>
       <c r="B41" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>129727959</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>129727788</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129726775</v>
+        <v>129727771</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>80194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5169,34 +5169,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488851</v>
+        <v>488511</v>
       </c>
       <c r="R44" t="n">
-        <v>7144825</v>
+        <v>7144867</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5226,19 +5233,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:46</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5247,28 +5249,54 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129727777</v>
+        <v>129727948</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>91606</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,34 +5304,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488483</v>
+        <v>488739</v>
       </c>
       <c r="R45" t="n">
-        <v>7144992</v>
+        <v>7144803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5338,11 +5366,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5355,22 +5378,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129727771</v>
+        <v>129727770</v>
       </c>
       <c r="B46" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5409,10 +5432,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488511</v>
+        <v>488674</v>
       </c>
       <c r="R46" t="n">
-        <v>7144867</v>
+        <v>7144814</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5449,7 +5472,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>Gott om skrovellav på en flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5502,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129727770</v>
+        <v>129727781</v>
       </c>
       <c r="B47" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5513,41 +5536,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488674</v>
+        <v>488586</v>
       </c>
       <c r="R47" t="n">
-        <v>7144814</v>
+        <v>7144955</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5584,7 +5600,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en flerstammig sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,34 +5609,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5637,10 +5627,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129727948</v>
+        <v>129727785</v>
       </c>
       <c r="B48" t="n">
-        <v>91605</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5648,34 +5638,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488739</v>
+        <v>488865</v>
       </c>
       <c r="R48" t="n">
-        <v>7144803</v>
+        <v>7144860</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5710,6 +5700,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På en levande gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5722,22 +5717,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129727781</v>
+        <v>129727799</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,10 +5764,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488586</v>
+        <v>488408</v>
       </c>
       <c r="R49" t="n">
-        <v>7144955</v>
+        <v>7144970</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,10 +5831,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129727785</v>
+        <v>129716437</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>83059</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5847,21 +5842,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5871,10 +5866,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488865</v>
+        <v>488533</v>
       </c>
       <c r="R50" t="n">
-        <v>7144860</v>
+        <v>7144953</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5909,11 +5904,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På en levande gran.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5926,22 +5916,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129727799</v>
+        <v>129726775</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,14 +5959,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488408</v>
+        <v>488851</v>
       </c>
       <c r="R51" t="n">
-        <v>7144970</v>
+        <v>7144825</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,14 +5996,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,22 +6023,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129716437</v>
+        <v>129727777</v>
       </c>
       <c r="B52" t="n">
-        <v>83058</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,21 +6046,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488533</v>
+        <v>488483</v>
       </c>
       <c r="R52" t="n">
-        <v>7144953</v>
+        <v>7144992</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,6 +6108,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6125,12 +6125,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
         <v>129716431</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>129727780</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>129727953</v>
       </c>
       <c r="B55" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>129716447</v>
       </c>
       <c r="B56" t="n">
-        <v>83063</v>
+        <v>83064</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6530,30 +6530,34 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129716430</v>
+        <v>129716428</v>
       </c>
       <c r="B57" t="n">
-        <v>91625</v>
+        <v>92324</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6561,10 +6565,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488835</v>
+        <v>489052</v>
       </c>
       <c r="R57" t="n">
-        <v>7144824</v>
+        <v>7144873</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6623,30 +6627,34 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129716440</v>
+        <v>129716423</v>
       </c>
       <c r="B58" t="n">
-        <v>91625</v>
+        <v>92324</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6654,10 +6662,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488547</v>
+        <v>488296</v>
       </c>
       <c r="R58" t="n">
-        <v>7144971</v>
+        <v>7145038</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6716,34 +6724,30 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129716428</v>
+        <v>129716430</v>
       </c>
       <c r="B59" t="n">
-        <v>92323</v>
+        <v>91626</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6751,10 +6755,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>489052</v>
+        <v>488835</v>
       </c>
       <c r="R59" t="n">
-        <v>7144873</v>
+        <v>7144824</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6813,10 +6817,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129716442</v>
+        <v>129716440</v>
       </c>
       <c r="B60" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,10 +6848,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488630</v>
+        <v>488547</v>
       </c>
       <c r="R60" t="n">
-        <v>7145015</v>
+        <v>7144971</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6906,34 +6910,30 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129716423</v>
+        <v>129716442</v>
       </c>
       <c r="B61" t="n">
-        <v>92323</v>
+        <v>91626</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488296</v>
+        <v>488630</v>
       </c>
       <c r="R61" t="n">
-        <v>7145038</v>
+        <v>7145015</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7006,7 +7006,7 @@
         <v>129727791</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>129727800</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>129726764</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>129727793</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>129727798</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>129716433</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>129727790</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>129716432</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>129727787</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>129727958</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129727951</v>
+        <v>129727954</v>
       </c>
       <c r="B72" t="n">
-        <v>91903</v>
+        <v>91602</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8029,21 +8029,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>489112</v>
+        <v>489143</v>
       </c>
       <c r="R72" t="n">
-        <v>7144780</v>
+        <v>7144773</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8115,10 +8115,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129727954</v>
+        <v>129726778</v>
       </c>
       <c r="B73" t="n">
-        <v>91601</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8126,34 +8126,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>489143</v>
+        <v>488522</v>
       </c>
       <c r="R73" t="n">
-        <v>7144773</v>
+        <v>7144974</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8183,9 +8183,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8200,22 +8210,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129726778</v>
+        <v>129716429</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8243,14 +8253,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488522</v>
+        <v>488440</v>
       </c>
       <c r="R74" t="n">
-        <v>7144974</v>
+        <v>7144976</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8280,19 +8290,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8307,22 +8307,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129716429</v>
+        <v>129727778</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488440</v>
+        <v>488513</v>
       </c>
       <c r="R75" t="n">
-        <v>7144976</v>
+        <v>7144973</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8392,6 +8392,11 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8404,22 +8409,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129727778</v>
+        <v>129726779</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8447,14 +8452,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488513</v>
+        <v>488452</v>
       </c>
       <c r="R76" t="n">
-        <v>7144973</v>
+        <v>7144979</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8484,14 +8489,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8506,22 +8516,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129726779</v>
+        <v>129727951</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>91904</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,34 +8539,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488452</v>
+        <v>489112</v>
       </c>
       <c r="R77" t="n">
-        <v>7144979</v>
+        <v>7144780</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8586,19 +8596,9 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8613,12 +8613,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
         <v>129716424</v>
       </c>
       <c r="B78" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129727769</v>
+        <v>129716434</v>
       </c>
       <c r="B79" t="n">
-        <v>80193</v>
+        <v>91602</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,41 +8733,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488758</v>
+        <v>488618</v>
       </c>
       <c r="R79" t="n">
-        <v>7144774</v>
+        <v>7144922</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8802,65 +8795,34 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På en gammal levande sälg.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129716434</v>
+        <v>129727769</v>
       </c>
       <c r="B80" t="n">
-        <v>91601</v>
+        <v>80194</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8868,34 +8830,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488618</v>
+        <v>488758</v>
       </c>
       <c r="R80" t="n">
-        <v>7144922</v>
+        <v>7144774</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8930,24 +8899,55 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På en gammal levande sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8957,7 +8957,7 @@
         <v>129727957</v>
       </c>
       <c r="B81" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>129726777</v>
       </c>
       <c r="B82" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>129716445</v>
       </c>
       <c r="B83" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>129716441</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>129716422</v>
       </c>
       <c r="B85" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>129727767</v>
       </c>
       <c r="B86" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>129727795</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129726773</v>
+        <v>129727794</v>
       </c>
       <c r="B88" t="n">
-        <v>91605</v>
+        <v>79088</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9697,34 +9697,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>489020</v>
+        <v>488763</v>
       </c>
       <c r="R88" t="n">
-        <v>7144867</v>
+        <v>7144775</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9754,19 +9754,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:53</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:53</t>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9781,22 +9776,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129727794</v>
+        <v>129727960</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9824,14 +9819,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488763</v>
+        <v>488374</v>
       </c>
       <c r="R89" t="n">
-        <v>7144775</v>
+        <v>7144949</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9868,7 +9863,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9883,22 +9878,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129727960</v>
+        <v>129727783</v>
       </c>
       <c r="B90" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9926,14 +9921,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488374</v>
+        <v>488709</v>
       </c>
       <c r="R90" t="n">
-        <v>7144949</v>
+        <v>7144911</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9970,7 +9965,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På levande gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9985,57 +9980,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129727783</v>
+        <v>129726769</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>75071</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488709</v>
+        <v>489064</v>
       </c>
       <c r="R91" t="n">
-        <v>7144911</v>
+        <v>7144843</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10065,14 +10060,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På levande gran i gammal granskog.</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10083,48 +10083,63 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129726769</v>
+        <v>129726773</v>
       </c>
       <c r="B92" t="n">
-        <v>75071</v>
+        <v>91606</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10134,10 +10149,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>489064</v>
+        <v>489020</v>
       </c>
       <c r="R92" t="n">
-        <v>7144843</v>
+        <v>7144867</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10169,7 +10184,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10179,7 +10194,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10190,21 +10205,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10224,7 +10224,7 @@
         <v>129727956</v>
       </c>
       <c r="B93" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>129726783</v>
       </c>
       <c r="B94" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>129730462</v>
       </c>
       <c r="B95" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>129730460</v>
       </c>
       <c r="B98" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>129730457</v>
       </c>
       <c r="B99" t="n">
-        <v>91976</v>
+        <v>91977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>129730449</v>
       </c>
       <c r="B100" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129730465</v>
+        <v>129730473</v>
       </c>
       <c r="B101" t="n">
-        <v>80221</v>
+        <v>91602</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488705</v>
+        <v>489028</v>
       </c>
       <c r="R101" t="n">
-        <v>7144862</v>
+        <v>7144803</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129730473</v>
+        <v>129730474</v>
       </c>
       <c r="B102" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>489028</v>
+        <v>488676</v>
       </c>
       <c r="R102" t="n">
-        <v>7144803</v>
+        <v>7144870</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129730474</v>
+        <v>129730465</v>
       </c>
       <c r="B103" t="n">
-        <v>91601</v>
+        <v>80222</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488676</v>
+        <v>488705</v>
       </c>
       <c r="R103" t="n">
-        <v>7144870</v>
+        <v>7144862</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>129730461</v>
       </c>
       <c r="B104" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>129730451</v>
       </c>
       <c r="B105" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11803,10 +11803,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129730477</v>
+        <v>129730452</v>
       </c>
       <c r="B109" t="n">
-        <v>91619</v>
+        <v>79088</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11814,21 +11814,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488797</v>
+        <v>488434</v>
       </c>
       <c r="R109" t="n">
-        <v>7144807</v>
+        <v>7144959</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11874,6 +11874,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11900,10 +11905,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129730452</v>
+        <v>129730477</v>
       </c>
       <c r="B110" t="n">
-        <v>79087</v>
+        <v>91620</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11911,21 +11916,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11935,10 +11940,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488434</v>
+        <v>488797</v>
       </c>
       <c r="R110" t="n">
-        <v>7144959</v>
+        <v>7144807</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11971,11 +11976,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12107,7 +12107,7 @@
         <v>129730448</v>
       </c>
       <c r="B112" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>129730467</v>
       </c>
       <c r="B113" t="n">
-        <v>83063</v>
+        <v>83064</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>129730470</v>
       </c>
       <c r="B115" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129730468</v>
+        <v>129730463</v>
       </c>
       <c r="B116" t="n">
-        <v>78100</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12508,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488763</v>
+        <v>488546</v>
       </c>
       <c r="R116" t="n">
-        <v>7144808</v>
+        <v>7144950</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12568,6 +12568,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12594,10 +12599,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129730463</v>
+        <v>129730468</v>
       </c>
       <c r="B117" t="n">
-        <v>57740</v>
+        <v>78100</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12605,21 +12610,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12629,10 +12634,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488546</v>
+        <v>488763</v>
       </c>
       <c r="R117" t="n">
-        <v>7144950</v>
+        <v>7144808</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12665,11 +12670,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12696,10 +12696,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129730471</v>
+        <v>129730458</v>
       </c>
       <c r="B118" t="n">
-        <v>91601</v>
+        <v>91606</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12707,21 +12707,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488625</v>
+        <v>489058</v>
       </c>
       <c r="R118" t="n">
-        <v>7144878</v>
+        <v>7144802</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12793,10 +12793,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129730458</v>
+        <v>129730471</v>
       </c>
       <c r="B119" t="n">
-        <v>91605</v>
+        <v>91602</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12804,21 +12804,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12828,10 +12828,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>489058</v>
+        <v>488625</v>
       </c>
       <c r="R119" t="n">
-        <v>7144802</v>
+        <v>7144878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12893,7 +12893,7 @@
         <v>129730476</v>
       </c>
       <c r="B120" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12987,30 +12987,34 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129730478</v>
+        <v>129730456</v>
       </c>
       <c r="B121" t="n">
-        <v>91625</v>
+        <v>91977</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13018,10 +13022,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488436</v>
+        <v>488467</v>
       </c>
       <c r="R121" t="n">
-        <v>7144967</v>
+        <v>7144951</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13080,32 +13084,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129730456</v>
+        <v>129730459</v>
       </c>
       <c r="B122" t="n">
-        <v>91976</v>
+        <v>91606</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13115,10 +13119,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488467</v>
+        <v>488604</v>
       </c>
       <c r="R122" t="n">
-        <v>7144951</v>
+        <v>7144985</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13177,10 +13181,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129730459</v>
+        <v>129730478</v>
       </c>
       <c r="B123" t="n">
-        <v>91605</v>
+        <v>91626</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13188,23 +13192,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13212,10 +13212,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488604</v>
+        <v>488436</v>
       </c>
       <c r="R123" t="n">
-        <v>7144985</v>
+        <v>7144967</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B124" t="n">
-        <v>83058</v>
+        <v>80222</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R124" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B125" t="n">
-        <v>80221</v>
+        <v>83059</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R125" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13471,7 +13471,7 @@
         <v>129730447</v>
       </c>
       <c r="B126" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>129730453</v>
       </c>
       <c r="B127" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>129730466</v>
       </c>
       <c r="B128" t="n">
-        <v>83063</v>
+        <v>83064</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>129730472</v>
       </c>
       <c r="B130" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>129730475</v>
       </c>
       <c r="B131" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -1664,45 +1664,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727776</v>
+        <v>129727765</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>80222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488425</v>
+        <v>488701</v>
       </c>
       <c r="R11" t="n">
-        <v>7145015</v>
+        <v>7144801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1746,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar i gammal granskog.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,8 +1755,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1766,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726761</v>
+        <v>129727776</v>
       </c>
       <c r="B12" t="n">
         <v>79088</v>
@@ -1797,14 +1830,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488516</v>
+        <v>488425</v>
       </c>
       <c r="R12" t="n">
-        <v>7145014</v>
+        <v>7145015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,19 +1867,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,19 +1889,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129727801</v>
+        <v>129726761</v>
       </c>
       <c r="B13" t="n">
         <v>79088</v>
@@ -1904,14 +1932,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488339</v>
+        <v>488516</v>
       </c>
       <c r="R13" t="n">
-        <v>7144937</v>
+        <v>7145014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,14 +1969,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,19 +1996,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727782</v>
+        <v>129727801</v>
       </c>
       <c r="B14" t="n">
         <v>79088</v>
@@ -2010,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488694</v>
+        <v>488339</v>
       </c>
       <c r="R14" t="n">
-        <v>7144925</v>
+        <v>7144937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2083,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,7 +2110,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727796</v>
+        <v>129727782</v>
       </c>
       <c r="B15" t="n">
         <v>79088</v>
@@ -2112,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488507</v>
+        <v>488694</v>
       </c>
       <c r="R15" t="n">
-        <v>7144870</v>
+        <v>7144925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2185,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,52 +2212,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727765</v>
+        <v>129727796</v>
       </c>
       <c r="B16" t="n">
-        <v>80222</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488701</v>
+        <v>488507</v>
       </c>
       <c r="R16" t="n">
-        <v>7144801</v>
+        <v>7144870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,7 +2287,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,34 +2296,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727768</v>
+        <v>129727947</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>91606</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,46 +2432,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Hemhöjden sv, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488790</v>
+        <v>488803</v>
       </c>
       <c r="R18" t="n">
-        <v>7144786</v>
+        <v>7144779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,11 +2494,6 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i en grov gammal gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2519,51 +2502,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129727947</v>
+        <v>129716443</v>
       </c>
       <c r="B19" t="n">
-        <v>91606</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,34 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hemhöjden sv, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488803</v>
+        <v>488470</v>
       </c>
       <c r="R19" t="n">
-        <v>7144779</v>
+        <v>7144975</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,22 +2603,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129716443</v>
+        <v>129726774</v>
       </c>
       <c r="B20" t="n">
-        <v>91602</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,34 +2626,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488470</v>
+        <v>489025</v>
       </c>
       <c r="R20" t="n">
-        <v>7144975</v>
+        <v>7144875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,9 +2683,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,22 +2710,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726774</v>
+        <v>129727768</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,34 +2733,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489025</v>
+        <v>488790</v>
       </c>
       <c r="R21" t="n">
-        <v>7144875</v>
+        <v>7144786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,19 +2802,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:52</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i en grov gammal gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,16 +2820,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -13274,32 +13274,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129730446</v>
+        <v>129730455</v>
       </c>
       <c r="B124" t="n">
-        <v>80222</v>
+        <v>83059</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488412</v>
+        <v>488791</v>
       </c>
       <c r="R124" t="n">
-        <v>7144940</v>
+        <v>7144807</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13371,32 +13371,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129730455</v>
+        <v>129730446</v>
       </c>
       <c r="B125" t="n">
-        <v>83059</v>
+        <v>80222</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488791</v>
+        <v>488412</v>
       </c>
       <c r="R125" t="n">
-        <v>7144807</v>
+        <v>7144940</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 52745-2025 artfynd.xlsx
+++ b/artfynd/A 52745-2025 artfynd.xlsx
@@ -1664,52 +1664,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129727765</v>
+        <v>129727776</v>
       </c>
       <c r="B11" t="n">
-        <v>80222</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488701</v>
+        <v>488425</v>
       </c>
       <c r="R11" t="n">
-        <v>7144801</v>
+        <v>7145015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en levande sälg.</t>
+          <t>På flera granar i gammal granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,34 +1748,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1799,7 +1766,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129727776</v>
+        <v>129726761</v>
       </c>
       <c r="B12" t="n">
         <v>79088</v>
@@ -1830,14 +1797,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488425</v>
+        <v>488516</v>
       </c>
       <c r="R12" t="n">
-        <v>7145015</v>
+        <v>7145014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,14 +1834,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På flera granar i gammal granskog.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,19 +1861,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726761</v>
+        <v>129727801</v>
       </c>
       <c r="B13" t="n">
         <v>79088</v>
@@ -1932,14 +1904,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488516</v>
+        <v>488339</v>
       </c>
       <c r="R13" t="n">
-        <v>7145014</v>
+        <v>7144937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,19 +1941,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,19 +1963,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129727801</v>
+        <v>129727782</v>
       </c>
       <c r="B14" t="n">
         <v>79088</v>
@@ -2043,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488339</v>
+        <v>488694</v>
       </c>
       <c r="R14" t="n">
-        <v>7144937</v>
+        <v>7144925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,7 +2050,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>Långväxt garnlav på björk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129727782</v>
+        <v>129727796</v>
       </c>
       <c r="B15" t="n">
         <v>79088</v>
@@ -2145,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488694</v>
+        <v>488507</v>
       </c>
       <c r="R15" t="n">
-        <v>7144925</v>
+        <v>7144870</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2152,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på björk.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,45 +2179,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129727796</v>
+        <v>129727765</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>80222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488507</v>
+        <v>488701</v>
       </c>
       <c r="R16" t="n">
-        <v>7144870</v>
+        <v>7144801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,7 +2261,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en levande sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,8 +2270,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129727947</v>
+        <v>129727768</v>
       </c>
       <c r="B18" t="n">
-        <v>91606</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2432,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">